--- a/Distributions.xlsx
+++ b/Distributions.xlsx
@@ -5,23 +5,20 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micha\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aaltofi-my.sharepoint.com/personal/samuel_salin_aalto_fi/Documents/Desktop/Risk Elicitation/RE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF9BAEC0-F383-4CDE-82D9-9380EBF509C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BBF9AF74AC20D3FF2286BA73C3D10CC99D880FBC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B475AB59-9C80-4B51-ABA7-F0F6F2694E65}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{609E4B8F-B91C-401D-B3BD-10B7A23FA221}"/>
+    <workbookView xWindow="-5160" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="All" sheetId="4" r:id="rId1"/>
-    <sheet name="Volatility" sheetId="3" r:id="rId2"/>
-    <sheet name="Skewness" sheetId="1" r:id="rId3"/>
+    <sheet name="All" sheetId="1" r:id="rId1"/>
+    <sheet name="Volatility" sheetId="2" r:id="rId2"/>
+    <sheet name="Skewness" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -33,64 +30,12 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="24">
-  <si>
-    <t>D6</t>
-  </si>
-  <si>
-    <t>D7</t>
-  </si>
-  <si>
-    <t>Mean</t>
-  </si>
-  <si>
-    <t>Vola</t>
-  </si>
-  <si>
-    <t>Skewness</t>
-  </si>
-  <si>
-    <t>Kurtosis</t>
-  </si>
-  <si>
-    <t>D8</t>
-  </si>
-  <si>
-    <t>D9</t>
-  </si>
-  <si>
-    <t>D10</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="28">
   <si>
     <t>D1</t>
   </si>
@@ -107,6 +52,33 @@
     <t>D5</t>
   </si>
   <si>
+    <t>D6</t>
+  </si>
+  <si>
+    <t>D7</t>
+  </si>
+  <si>
+    <t>D8</t>
+  </si>
+  <si>
+    <t>D9</t>
+  </si>
+  <si>
+    <t>D10</t>
+  </si>
+  <si>
+    <t>Mean</t>
+  </si>
+  <si>
+    <t>Vola</t>
+  </si>
+  <si>
+    <t>Skewness</t>
+  </si>
+  <si>
+    <t>Kurtosis</t>
+  </si>
+  <si>
     <t>Min</t>
   </si>
   <si>
@@ -119,16 +91,16 @@
     <t>F(out)</t>
   </si>
   <si>
-    <t>Situation</t>
+    <t>Tilt</t>
   </si>
   <si>
     <t>Max F(out)</t>
   </si>
   <si>
-    <t>Tilt</t>
+    <t>Variation 1: Random allocation of outcomes to situations by alternative (e.g., column B independent of column C)</t>
   </si>
   <si>
-    <t>Variation 1: Random allocation of outcomes to situations by alternative (e.g., column B independent of column C)</t>
+    <t>Situation</t>
   </si>
   <si>
     <t>Variation 2.1: Random allocation of outcomes to situations by state (e.g., same-row observations in column B and column C form an outcome pair that cannot be broken up, so that the structure of dependence is fixed)</t>
@@ -136,12 +108,24 @@
   <si>
     <t>Variation 2.2: Random allocation of outcomes to situations by state (e.g., same-row observations in column B and column C form an outcome pair that cannot be broken up, so that the structure of dependence is fixed)</t>
   </si>
+  <si>
+    <t>Round Thresholds: FREQ_THRES_L / TAIL_THRES_L / TAIL_THRES_H per distribution (same threshold used for both alternatives in a round that draws this distribution; edit the numbers below directly - no code changes needed)</t>
+  </si>
+  <si>
+    <t>FREQ_THRES_L</t>
+  </si>
+  <si>
+    <t>TAIL_THRES_L</t>
+  </si>
+  <si>
+    <t>TAIL_THRES_H</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -156,6 +140,15 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
     </font>
   </fonts>
   <fills count="3">
@@ -193,7 +186,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -205,15 +198,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -547,57 +539,57 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86B127F1-FF9E-40AD-BAC8-A5D0CABA3A66}">
-  <dimension ref="A2:AB102"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A2:AB109"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="198.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="12"/>
+      <c r="D2" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="12"/>
+      <c r="F2" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="12"/>
+      <c r="H2" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" s="12"/>
+      <c r="J2" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="K2" s="12"/>
+      <c r="L2" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="M2" s="12"/>
+      <c r="N2" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="O2" s="12"/>
+      <c r="P2" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q2" s="12"/>
+      <c r="R2" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="S2" s="12"/>
+      <c r="T2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="U2" s="7"/>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="U2" s="12"/>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
       <c r="B3" s="1">
         <v>0</v>
       </c>
@@ -635,10 +627,10 @@
         <v>1.05</v>
       </c>
       <c r="N3" s="1">
-        <v>-0.15000000000000002</v>
+        <v>-0.15</v>
       </c>
       <c r="O3" s="1">
-        <v>5.0000000000000044E-2</v>
+        <v>5.0000000000000037E-2</v>
       </c>
       <c r="P3" s="1">
         <v>-1.1499999999999999</v>
@@ -650,7 +642,7 @@
         <v>0.95</v>
       </c>
       <c r="S3" s="1">
-        <v>1.1500000000000001</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="T3" s="1">
         <v>-1.25</v>
@@ -659,7 +651,7 @@
         <v>-1.05</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
       <c r="B4" s="1">
         <v>0.2</v>
       </c>
@@ -679,13 +671,13 @@
         <v>-1.4</v>
       </c>
       <c r="H4" s="1">
-        <v>0.30000000000000004</v>
+        <v>0.3</v>
       </c>
       <c r="I4" s="1">
         <v>0.7</v>
       </c>
       <c r="J4" s="1">
-        <v>-1.9000000000000001</v>
+        <v>-1.9</v>
       </c>
       <c r="K4" s="1">
         <v>-1.5</v>
@@ -703,7 +695,7 @@
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="P4" s="1">
-        <v>-1.1400000000000001</v>
+        <v>-1.1399999999999999</v>
       </c>
       <c r="Q4" s="1">
         <v>-0.94</v>
@@ -712,16 +704,16 @@
         <v>0.96</v>
       </c>
       <c r="S4" s="1">
-        <v>1.1600000000000001</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="T4" s="1">
-        <v>-1.2400000000000002</v>
+        <v>-1.24</v>
       </c>
       <c r="U4" s="1">
         <v>-1.04</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
       <c r="B5" s="1">
         <v>0.4</v>
       </c>
@@ -732,7 +724,7 @@
         <v>-0.6</v>
       </c>
       <c r="E5" s="1">
-        <v>-0.30000000000000004</v>
+        <v>-0.3</v>
       </c>
       <c r="F5" s="1">
         <v>-1.6</v>
@@ -747,10 +739,10 @@
         <v>0.79999999999999993</v>
       </c>
       <c r="J5" s="1">
-        <v>-1.7000000000000002</v>
+        <v>-1.7</v>
       </c>
       <c r="K5" s="1">
-        <v>-1.4000000000000001</v>
+        <v>-1.4</v>
       </c>
       <c r="L5" s="1">
         <v>0.87</v>
@@ -774,7 +766,7 @@
         <v>0.97</v>
       </c>
       <c r="S5" s="1">
-        <v>1.1700000000000002</v>
+        <v>1.17</v>
       </c>
       <c r="T5" s="1">
         <v>-1.23</v>
@@ -783,7 +775,7 @@
         <v>-1.03</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
       <c r="B6" s="1">
         <v>0.60000000000000009</v>
       </c>
@@ -794,13 +786,13 @@
         <v>-0.39999999999999991</v>
       </c>
       <c r="E6" s="1">
-        <v>-0.20000000000000007</v>
+        <v>-0.20000000000000009</v>
       </c>
       <c r="F6" s="1">
         <v>-1.4</v>
       </c>
       <c r="G6" s="1">
-        <v>-1.2000000000000002</v>
+        <v>-1.2</v>
       </c>
       <c r="H6" s="1">
         <v>0.70000000000000007</v>
@@ -812,7 +804,7 @@
         <v>-1.5</v>
       </c>
       <c r="K6" s="1">
-        <v>-1.3000000000000003</v>
+        <v>-1.3</v>
       </c>
       <c r="L6" s="1">
         <v>0.88</v>
@@ -836,16 +828,16 @@
         <v>0.98</v>
       </c>
       <c r="S6" s="1">
-        <v>1.1800000000000002</v>
+        <v>1.18</v>
       </c>
       <c r="T6" s="1">
-        <v>-1.2200000000000002</v>
+        <v>-1.22</v>
       </c>
       <c r="U6" s="1">
         <v>-1.02</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
       <c r="B7" s="1">
         <v>0.8</v>
       </c>
@@ -853,10 +845,10 @@
         <v>0.89999999999999991</v>
       </c>
       <c r="D7" s="1">
-        <v>-0.19999999999999996</v>
+        <v>-0.2</v>
       </c>
       <c r="E7" s="1">
-        <v>-0.10000000000000009</v>
+        <v>-0.1000000000000001</v>
       </c>
       <c r="F7" s="1">
         <v>-1.2</v>
@@ -874,7 +866,7 @@
         <v>-1.3</v>
       </c>
       <c r="K7" s="1">
-        <v>-1.2000000000000002</v>
+        <v>-1.2</v>
       </c>
       <c r="L7" s="1">
         <v>0.89</v>
@@ -883,13 +875,13 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="N7" s="1">
-        <v>-0.10999999999999999</v>
+        <v>-0.11</v>
       </c>
       <c r="O7" s="1">
         <v>9.000000000000008E-2</v>
       </c>
       <c r="P7" s="1">
-        <v>-1.1099999999999999</v>
+        <v>-1.1100000000000001</v>
       </c>
       <c r="Q7" s="1">
         <v>-0.90999999999999992</v>
@@ -898,7 +890,7 @@
         <v>0.99</v>
       </c>
       <c r="S7" s="1">
-        <v>1.1900000000000002</v>
+        <v>1.19</v>
       </c>
       <c r="T7" s="1">
         <v>-1.21</v>
@@ -907,7 +899,7 @@
         <v>-1.01</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
       <c r="B8" s="1">
         <v>1</v>
       </c>
@@ -930,7 +922,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="I8" s="1">
-        <v>1.0999999999999999</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="J8" s="1">
         <v>-1.1000000000000001</v>
@@ -951,7 +943,7 @@
         <v>0.1100000000000001</v>
       </c>
       <c r="P8" s="1">
-        <v>-1.0899999999999999</v>
+        <v>-1.0900000000000001</v>
       </c>
       <c r="Q8" s="1">
         <v>-0.8899999999999999</v>
@@ -960,7 +952,7 @@
         <v>1.01</v>
       </c>
       <c r="S8" s="1">
-        <v>1.2100000000000002</v>
+        <v>1.21</v>
       </c>
       <c r="T8" s="1">
         <v>-1.19</v>
@@ -969,15 +961,15 @@
         <v>-0.98999999999999988</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
       <c r="B9" s="1">
         <v>1.2</v>
       </c>
       <c r="C9" s="1">
-        <v>1.0999999999999999</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="D9" s="1">
-        <v>0.19999999999999996</v>
+        <v>0.2</v>
       </c>
       <c r="E9" s="1">
         <v>9.9999999999999867E-2</v>
@@ -998,7 +990,7 @@
         <v>-0.9</v>
       </c>
       <c r="K9" s="1">
-        <v>-1.0000000000000002</v>
+        <v>-1</v>
       </c>
       <c r="L9" s="1">
         <v>0.92</v>
@@ -1022,16 +1014,16 @@
         <v>1.02</v>
       </c>
       <c r="S9" s="1">
-        <v>1.2200000000000002</v>
+        <v>1.22</v>
       </c>
       <c r="T9" s="1">
-        <v>-1.1800000000000002</v>
+        <v>-1.18</v>
       </c>
       <c r="U9" s="1">
         <v>-0.97999999999999987</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
       <c r="B10" s="1">
         <v>1.4</v>
       </c>
@@ -1042,7 +1034,7 @@
         <v>0.39999999999999991</v>
       </c>
       <c r="E10" s="1">
-        <v>0.19999999999999996</v>
+        <v>0.2</v>
       </c>
       <c r="F10" s="1">
         <v>-0.60000000000000009</v>
@@ -1066,16 +1058,16 @@
         <v>0.93</v>
       </c>
       <c r="M10" s="1">
-        <v>1.1300000000000001</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="N10" s="1">
         <v>-6.9999999999999951E-2</v>
       </c>
       <c r="O10" s="1">
-        <v>0.13000000000000012</v>
+        <v>0.13000000000000009</v>
       </c>
       <c r="P10" s="1">
-        <v>-1.0699999999999998</v>
+        <v>-1.07</v>
       </c>
       <c r="Q10" s="1">
         <v>-0.86999999999999988</v>
@@ -1084,7 +1076,7 @@
         <v>1.03</v>
       </c>
       <c r="S10" s="1">
-        <v>1.2300000000000002</v>
+        <v>1.23</v>
       </c>
       <c r="T10" s="1">
         <v>-1.17</v>
@@ -1093,9 +1085,9 @@
         <v>-0.96999999999999986</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
       <c r="B11" s="1">
-        <v>1.5999999999999999</v>
+        <v>1.6</v>
       </c>
       <c r="C11" s="1">
         <v>1.3</v>
@@ -1104,10 +1096,10 @@
         <v>0.59999999999999987</v>
       </c>
       <c r="E11" s="1">
-        <v>0.30000000000000004</v>
+        <v>0.3</v>
       </c>
       <c r="F11" s="1">
-        <v>-0.40000000000000013</v>
+        <v>-0.40000000000000008</v>
       </c>
       <c r="G11" s="1">
         <v>-0.7</v>
@@ -1116,7 +1108,7 @@
         <v>1.7</v>
       </c>
       <c r="I11" s="1">
-        <v>1.4000000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="J11" s="1">
         <v>-0.50000000000000011</v>
@@ -1128,13 +1120,13 @@
         <v>0.94000000000000006</v>
       </c>
       <c r="M11" s="1">
-        <v>1.1400000000000001</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="N11" s="1">
         <v>-5.9999999999999942E-2</v>
       </c>
       <c r="O11" s="1">
-        <v>0.14000000000000012</v>
+        <v>0.1400000000000001</v>
       </c>
       <c r="P11" s="1">
         <v>-1.06</v>
@@ -1146,30 +1138,30 @@
         <v>1.04</v>
       </c>
       <c r="S11" s="1">
-        <v>1.2400000000000002</v>
+        <v>1.24</v>
       </c>
       <c r="T11" s="1">
-        <v>-1.1600000000000001</v>
+        <v>-1.1599999999999999</v>
       </c>
       <c r="U11" s="1">
         <v>-0.95999999999999985</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
       <c r="B12" s="1">
-        <v>1.7999999999999998</v>
+        <v>1.8</v>
       </c>
       <c r="C12" s="1">
-        <v>1.4000000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="D12" s="1">
         <v>0.79999999999999982</v>
       </c>
       <c r="E12" s="1">
-        <v>0.40000000000000013</v>
+        <v>0.40000000000000008</v>
       </c>
       <c r="F12" s="1">
-        <v>-0.20000000000000018</v>
+        <v>-0.20000000000000021</v>
       </c>
       <c r="G12" s="1">
         <v>-0.59999999999999987</v>
@@ -1178,10 +1170,10 @@
         <v>1.9</v>
       </c>
       <c r="I12" s="1">
-        <v>1.5000000000000002</v>
+        <v>1.5</v>
       </c>
       <c r="J12" s="1">
-        <v>-0.30000000000000016</v>
+        <v>-0.30000000000000021</v>
       </c>
       <c r="K12" s="1">
         <v>-0.69999999999999984</v>
@@ -1190,16 +1182,16 @@
         <v>0.95000000000000007</v>
       </c>
       <c r="M12" s="1">
-        <v>1.1500000000000001</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="N12" s="1">
         <v>-4.9999999999999933E-2</v>
       </c>
       <c r="O12" s="1">
-        <v>0.15000000000000013</v>
+        <v>0.15000000000000011</v>
       </c>
       <c r="P12" s="1">
-        <v>-1.0499999999999998</v>
+        <v>-1.05</v>
       </c>
       <c r="Q12" s="1">
         <v>-0.84999999999999987</v>
@@ -1208,7 +1200,7 @@
         <v>1.05</v>
       </c>
       <c r="S12" s="1">
-        <v>1.2500000000000002</v>
+        <v>1.25</v>
       </c>
       <c r="T12" s="1">
         <v>-1.1499999999999999</v>
@@ -1217,12 +1209,12 @@
         <v>-0.94999999999999984</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
       <c r="B13" s="1">
-        <v>1.9999999999999998</v>
+        <v>2</v>
       </c>
       <c r="C13" s="1">
-        <v>1.5000000000000002</v>
+        <v>1.5</v>
       </c>
       <c r="D13" s="1">
         <v>0.99999999999999978</v>
@@ -1237,10 +1229,10 @@
         <v>-0.49999999999999978</v>
       </c>
       <c r="H13" s="1">
-        <v>2.0999999999999996</v>
+        <v>2.1</v>
       </c>
       <c r="I13" s="1">
-        <v>1.6000000000000003</v>
+        <v>1.6</v>
       </c>
       <c r="J13" s="1">
         <v>-0.1</v>
@@ -1279,9 +1271,9 @@
         <v>-2.1</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B15" s="1">
         <f t="shared" ref="B15:U15" si="0">AVERAGE(B3:B13)</f>
@@ -1301,7 +1293,7 @@
       </c>
       <c r="F15" s="1">
         <f t="shared" si="0"/>
-        <v>-1</v>
+        <v>-1.0000000000000002</v>
       </c>
       <c r="G15" s="1">
         <f t="shared" si="0"/>
@@ -1321,7 +1313,7 @@
       </c>
       <c r="K15" s="1">
         <f t="shared" si="0"/>
-        <v>-1.1000000000000001</v>
+        <v>-1.0999999999999999</v>
       </c>
       <c r="L15" s="1">
         <f t="shared" si="0"/>
@@ -1341,7 +1333,7 @@
       </c>
       <c r="P15" s="1">
         <f t="shared" si="0"/>
-        <v>-1</v>
+        <v>-1.0000000000000002</v>
       </c>
       <c r="Q15" s="1">
         <f t="shared" si="0"/>
@@ -1353,7 +1345,7 @@
       </c>
       <c r="S15" s="1">
         <f t="shared" si="0"/>
-        <v>1.1000000000000001</v>
+        <v>1.0999999999999999</v>
       </c>
       <c r="T15" s="1">
         <f t="shared" si="0"/>
@@ -1364,17 +1356,17 @@
         <v>-1.0999999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B16" s="4">
         <f t="shared" ref="B16:U16" si="1">_xlfn.STDEV.P(B3:B13)</f>
-        <v>0.63245553203367566</v>
+        <v>0.63245553203367588</v>
       </c>
       <c r="C16" s="4">
         <f t="shared" si="1"/>
-        <v>0.31622776601683822</v>
+        <v>0.31622776601683783</v>
       </c>
       <c r="D16" s="4">
         <f t="shared" si="1"/>
@@ -1386,7 +1378,7 @@
       </c>
       <c r="F16" s="4">
         <f t="shared" si="1"/>
-        <v>0.63245553203367588</v>
+        <v>0.63245553203367566</v>
       </c>
       <c r="G16" s="4">
         <f t="shared" si="1"/>
@@ -1398,7 +1390,7 @@
       </c>
       <c r="I16" s="4">
         <f t="shared" si="1"/>
-        <v>0.31622776601683822</v>
+        <v>0.31622776601683783</v>
       </c>
       <c r="J16" s="4">
         <f t="shared" si="1"/>
@@ -1426,7 +1418,7 @@
       </c>
       <c r="P16" s="1">
         <f t="shared" si="1"/>
-        <v>0.31780497164141375</v>
+        <v>0.31780497164141358</v>
       </c>
       <c r="Q16" s="1">
         <f t="shared" si="1"/>
@@ -1449,17 +1441,17 @@
         <v>0.31780497164141486</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B17" s="1">
         <f t="shared" ref="B17:U17" si="2">_xlfn.SKEW.P(B3:B13)</f>
-        <v>-4.0371746350005691E-16</v>
+        <v>0</v>
       </c>
       <c r="C17" s="1">
         <f t="shared" si="2"/>
-        <v>6.0557619525008534E-16</v>
+        <v>-2.0185873175002846E-16</v>
       </c>
       <c r="D17" s="1">
         <f t="shared" si="2"/>
@@ -1467,31 +1459,31 @@
       </c>
       <c r="E17" s="1">
         <f t="shared" si="2"/>
-        <v>6.0557619525008534E-16</v>
+        <v>5.2483270255007403E-16</v>
       </c>
       <c r="F17" s="1">
         <f t="shared" si="2"/>
-        <v>-2.8260222445003984E-16</v>
+        <v>7.6706318065010816E-16</v>
       </c>
       <c r="G17" s="1">
         <f t="shared" si="2"/>
-        <v>7.6706318065010816E-16</v>
+        <v>8.4780667335011958E-16</v>
       </c>
       <c r="H17" s="1">
         <f t="shared" si="2"/>
-        <v>1.2111523905001707E-16</v>
+        <v>5.2483270255007403E-16</v>
       </c>
       <c r="I17" s="1">
         <f t="shared" si="2"/>
-        <v>2.2204460492503131E-15</v>
+        <v>1.170780644150165E-15</v>
       </c>
       <c r="J17" s="1">
         <f t="shared" si="2"/>
-        <v>-8.4780667335011958E-16</v>
+        <v>-7.2669143430010251E-16</v>
       </c>
       <c r="K17" s="1">
         <f t="shared" si="2"/>
-        <v>1.2111523905001707E-15</v>
+        <v>-5.2483270255007403E-16</v>
       </c>
       <c r="L17" s="4">
         <f t="shared" si="2"/>
@@ -1511,7 +1503,7 @@
       </c>
       <c r="P17" s="4">
         <f t="shared" si="2"/>
-        <v>2.7945403348921518</v>
+        <v>2.7945403348921536</v>
       </c>
       <c r="Q17" s="4">
         <f t="shared" si="2"/>
@@ -1523,7 +1515,7 @@
       </c>
       <c r="S17" s="4">
         <f t="shared" si="2"/>
-        <v>-2.7945403348921518</v>
+        <v>-2.7945403348921505</v>
       </c>
       <c r="T17" s="4">
         <f t="shared" si="2"/>
@@ -1534,13 +1526,13 @@
         <v>-2.7945403348921518</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B18" s="1">
         <f t="shared" ref="B18:U18" si="3">KURT(B3:B13)</f>
-        <v>-1.2000000000000011</v>
+        <v>-1.2000000000000015</v>
       </c>
       <c r="C18" s="1">
         <f t="shared" si="3"/>
@@ -1552,19 +1544,19 @@
       </c>
       <c r="E18" s="1">
         <f t="shared" si="3"/>
-        <v>-1.200000000000002</v>
+        <v>-1.1999999999999997</v>
       </c>
       <c r="F18" s="1">
         <f t="shared" si="3"/>
-        <v>-1.200000000000002</v>
+        <v>-1.2000000000000011</v>
       </c>
       <c r="G18" s="1">
         <f t="shared" si="3"/>
-        <v>-1.200000000000002</v>
+        <v>-1.1999999999999997</v>
       </c>
       <c r="H18" s="1">
         <f t="shared" si="3"/>
-        <v>-1.200000000000002</v>
+        <v>-1.2000000000000015</v>
       </c>
       <c r="I18" s="1">
         <f t="shared" si="3"/>
@@ -1576,7 +1568,7 @@
       </c>
       <c r="K18" s="1">
         <f t="shared" si="3"/>
-        <v>-1.2000000000000002</v>
+        <v>-1.2000000000000011</v>
       </c>
       <c r="L18" s="1">
         <f t="shared" si="3"/>
@@ -1596,7 +1588,7 @@
       </c>
       <c r="P18" s="1">
         <f t="shared" si="3"/>
-        <v>10.711250530993684</v>
+        <v>10.711250530993702</v>
       </c>
       <c r="Q18" s="1">
         <f t="shared" si="3"/>
@@ -1619,7 +1611,7 @@
         <v>10.711250530993691</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>14</v>
       </c>
@@ -1673,7 +1665,7 @@
       </c>
       <c r="N19" s="1">
         <f t="shared" si="4"/>
-        <v>-0.15000000000000002</v>
+        <v>-0.15</v>
       </c>
       <c r="O19" s="1">
         <f t="shared" si="4"/>
@@ -1704,17 +1696,17 @@
         <v>-2.1</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>15</v>
       </c>
       <c r="B20" s="1">
         <f t="shared" ref="B20:U20" si="5">MAX(B3:B13)</f>
-        <v>1.9999999999999998</v>
+        <v>2</v>
       </c>
       <c r="C20" s="1">
         <f t="shared" si="5"/>
-        <v>1.5000000000000002</v>
+        <v>1.5</v>
       </c>
       <c r="D20" s="1">
         <f t="shared" si="5"/>
@@ -1734,11 +1726,11 @@
       </c>
       <c r="H20" s="1">
         <f t="shared" si="5"/>
-        <v>2.0999999999999996</v>
+        <v>2.1</v>
       </c>
       <c r="I20" s="1">
         <f t="shared" si="5"/>
-        <v>1.6000000000000003</v>
+        <v>1.6</v>
       </c>
       <c r="J20" s="1">
         <f t="shared" si="5"/>
@@ -1754,7 +1746,7 @@
       </c>
       <c r="M20" s="1">
         <f t="shared" si="5"/>
-        <v>1.1500000000000001</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="N20" s="1">
         <f t="shared" si="5"/>
@@ -1762,7 +1754,7 @@
       </c>
       <c r="O20" s="1">
         <f t="shared" si="5"/>
-        <v>0.15000000000000013</v>
+        <v>0.15000000000000011</v>
       </c>
       <c r="P20" s="1">
         <f t="shared" si="5"/>
@@ -1778,7 +1770,7 @@
       </c>
       <c r="S20" s="1">
         <f t="shared" si="5"/>
-        <v>1.2500000000000002</v>
+        <v>1.25</v>
       </c>
       <c r="T20" s="1">
         <f t="shared" si="5"/>
@@ -1789,13 +1781,13 @@
         <v>-0.94999999999999984</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>16</v>
       </c>
       <c r="B21" s="1">
         <f>CORREL(B3:B13,C3:C13)</f>
-        <v>0.99999999999999989</v>
+        <v>1</v>
       </c>
       <c r="D21" s="1">
         <f>CORREL(D3:D13,E3:E13)</f>
@@ -1811,7 +1803,7 @@
       </c>
       <c r="J21" s="1">
         <f>CORREL(J3:J13,K3:K13)</f>
-        <v>1.0000000000000002</v>
+        <v>0.99999999999999989</v>
       </c>
       <c r="L21" s="1">
         <f>CORREL(L3:L13,M3:M13)</f>
@@ -1827,101 +1819,101 @@
       </c>
       <c r="R21" s="1">
         <f>CORREL(R3:R13,S3:S13)</f>
-        <v>-0.98019801980198029</v>
+        <v>-0.98019801980198007</v>
       </c>
       <c r="T21" s="1">
         <f>CORREL(T3:T13,U3:U13)</f>
         <v>-0.98019801980197996</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>17</v>
       </c>
-      <c r="B22" cm="1">
+      <c r="B22">
         <f t="array" ref="B22">SUMPRODUCT((B3:B13&gt;C3:C13)*1)</f>
         <v>5</v>
       </c>
-      <c r="C22" cm="1">
+      <c r="C22">
         <f t="array" ref="C22">SUMPRODUCT((B3:B13&lt;C3:C13)*1)</f>
         <v>5</v>
       </c>
-      <c r="D22" cm="1">
+      <c r="D22">
         <f t="array" ref="D22">SUMPRODUCT((D3:D13&gt;E3:E13)*1)</f>
         <v>5</v>
       </c>
-      <c r="E22" cm="1">
+      <c r="E22">
         <f t="array" ref="E22">SUMPRODUCT((D3:D13&lt;E3:E13)*1)</f>
         <v>5</v>
       </c>
-      <c r="F22" cm="1">
+      <c r="F22">
         <f t="array" ref="F22">SUMPRODUCT((F3:F13&gt;G3:G13)*1)</f>
         <v>5</v>
       </c>
-      <c r="G22" cm="1">
+      <c r="G22">
         <f t="array" ref="G22">SUMPRODUCT((F3:F13&lt;G3:G13)*1)</f>
         <v>5</v>
       </c>
-      <c r="H22" cm="1">
+      <c r="H22">
         <f t="array" ref="H22">SUMPRODUCT((H3:H13&gt;I3:I13)*1)</f>
         <v>5</v>
       </c>
-      <c r="I22" cm="1">
+      <c r="I22">
         <f t="array" ref="I22">SUMPRODUCT((H3:H13&lt;I3:I13)*1)</f>
         <v>5</v>
       </c>
-      <c r="J22" cm="1">
+      <c r="J22">
         <f t="array" ref="J22">SUMPRODUCT((J3:J13&gt;K3:K13)*1)</f>
         <v>5</v>
       </c>
-      <c r="K22" cm="1">
+      <c r="K22">
         <f t="array" ref="K22">SUMPRODUCT((J3:J13&lt;K3:K13)*1)</f>
         <v>5</v>
       </c>
-      <c r="L22" cm="1">
+      <c r="L22">
         <f t="array" ref="L22">SUMPRODUCT((L3:L13&gt;M3:M13)*1)</f>
         <v>1</v>
       </c>
-      <c r="M22" cm="1">
+      <c r="M22">
         <f t="array" ref="M22">SUMPRODUCT((L3:L13&lt;M3:M13)*1)</f>
         <v>10</v>
       </c>
-      <c r="N22" cm="1">
+      <c r="N22">
         <f t="array" ref="N22">SUMPRODUCT((N3:N13&gt;O3:O13)*1)</f>
         <v>1</v>
       </c>
-      <c r="O22" cm="1">
+      <c r="O22">
         <f t="array" ref="O22">SUMPRODUCT((N3:N13&lt;O3:O13)*1)</f>
         <v>10</v>
       </c>
-      <c r="P22" cm="1">
+      <c r="P22">
         <f t="array" ref="P22">SUMPRODUCT((P3:P13&gt;Q3:Q13)*1)</f>
         <v>1</v>
       </c>
-      <c r="Q22" cm="1">
+      <c r="Q22">
         <f t="array" ref="Q22">SUMPRODUCT((P3:P13&lt;Q3:Q13)*1)</f>
         <v>10</v>
       </c>
-      <c r="R22" cm="1">
+      <c r="R22">
         <f t="array" ref="R22">SUMPRODUCT((R3:R13&gt;S3:S13)*1)</f>
         <v>1</v>
       </c>
-      <c r="S22" cm="1">
+      <c r="S22">
         <f t="array" ref="S22">SUMPRODUCT((R3:R13&lt;S3:S13)*1)</f>
         <v>10</v>
       </c>
-      <c r="T22" cm="1">
+      <c r="T22">
         <f t="array" ref="T22">SUMPRODUCT((T3:T13&gt;U3:U13)*1)</f>
         <v>1</v>
       </c>
-      <c r="U22" cm="1">
+      <c r="U22">
         <f t="array" ref="U22">SUMPRODUCT((T3:T13&lt;U3:U13)*1)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B23" s="6" t="str">
         <f>IF(B22&gt;C22,"A",IF(C22&gt;B22,"B","Equal"))</f>
@@ -1964,7 +1956,7 @@
         <v>B</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>19</v>
       </c>
@@ -2009,160 +2001,160 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A26" s="8" t="s">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A26" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A28" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C28" s="12"/>
+      <c r="D28" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E28" s="12"/>
+      <c r="F28" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G28" s="12"/>
+      <c r="H28" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="I28" s="12"/>
+      <c r="J28" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="K28" s="12"/>
+      <c r="L28" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="M28" s="12"/>
+      <c r="N28" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="O28" s="12"/>
+      <c r="P28" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q28" s="12"/>
+      <c r="R28" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="S28" s="12"/>
+      <c r="T28" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="I28" s="7"/>
-      <c r="J28" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="K28" s="7"/>
-      <c r="L28" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="M28" s="7"/>
-      <c r="N28" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="O28" s="7"/>
-      <c r="P28" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q28" s="7"/>
-      <c r="R28" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="S28" s="7"/>
-      <c r="T28" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="U28" s="7"/>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="U28" s="12"/>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>1</v>
       </c>
-      <c r="B29" s="1" cm="1">
+      <c r="B29" s="1">
         <f t="array" aca="1" ref="B29:B39" ca="1">_xlfn.SORTBY(B3:B13,_xlfn.RANDARRAY(ROWS(B3:B13)))</f>
+        <v>1.2</v>
+      </c>
+      <c r="C29" s="1">
+        <f t="array" aca="1" ref="C29:C39" ca="1">_xlfn.SORTBY(C3:C13,_xlfn.RANDARRAY(ROWS(C3:C13)))</f>
+        <v>0.6</v>
+      </c>
+      <c r="D29" s="1">
+        <f t="array" aca="1" ref="D29:D39" ca="1">_xlfn.SORTBY(D3:D13,_xlfn.RANDARRAY(ROWS(D3:D13)))</f>
         <v>0</v>
       </c>
-      <c r="C29" s="1" cm="1">
-        <f t="array" aca="1" ref="C29:C39" ca="1">_xlfn.SORTBY(C3:C13,_xlfn.RANDARRAY(ROWS(C3:C13)))</f>
-        <v>0.99999999999999989</v>
-      </c>
-      <c r="D29" s="1" cm="1">
-        <f t="array" aca="1" ref="D29:D39" ca="1">_xlfn.SORTBY(D3:D13,_xlfn.RANDARRAY(ROWS(D3:D13)))</f>
+      <c r="E29" s="1">
+        <f t="array" aca="1" ref="E29:E39" ca="1">_xlfn.SORTBY(E3:E13,_xlfn.RANDARRAY(ROWS(E3:E13)))</f>
+        <v>-0.20000000000000009</v>
+      </c>
+      <c r="F29" s="1">
+        <f t="array" aca="1" ref="F29:F39" ca="1">_xlfn.SORTBY(F3:F13,_xlfn.RANDARRAY(ROWS(F3:F13)))</f>
+        <v>-0.20000000000000021</v>
+      </c>
+      <c r="G29" s="1">
+        <f t="array" aca="1" ref="G29:G39" ca="1">_xlfn.SORTBY(G3:G13,_xlfn.RANDARRAY(ROWS(G3:G13)))</f>
+        <v>-1.1000000000000001</v>
+      </c>
+      <c r="H29" s="1">
+        <f t="array" aca="1" ref="H29:H39" ca="1">_xlfn.SORTBY(H3:H13,_xlfn.RANDARRAY(ROWS(H3:H13)))</f>
+        <v>1.9</v>
+      </c>
+      <c r="I29" s="1">
+        <f t="array" aca="1" ref="I29:I39" ca="1">_xlfn.SORTBY(I3:I13,_xlfn.RANDARRAY(ROWS(I3:I13)))</f>
+        <v>0.79999999999999993</v>
+      </c>
+      <c r="J29" s="1">
+        <f t="array" aca="1" ref="J29:J39" ca="1">_xlfn.SORTBY(J3:J13,_xlfn.RANDARRAY(ROWS(J3:J13)))</f>
+        <v>-0.70000000000000007</v>
+      </c>
+      <c r="K29" s="1">
+        <f t="array" aca="1" ref="K29:K39" ca="1">_xlfn.SORTBY(K3:K13,_xlfn.RANDARRAY(ROWS(K3:K13)))</f>
         <v>-1</v>
       </c>
-      <c r="E29" s="1" cm="1">
-        <f t="array" aca="1" ref="E29:E39" ca="1">_xlfn.SORTBY(E3:E13,_xlfn.RANDARRAY(ROWS(E3:E13)))</f>
-        <v>-0.20000000000000007</v>
-      </c>
-      <c r="F29" s="1" cm="1">
-        <f t="array" aca="1" ref="F29:F39" ca="1">_xlfn.SORTBY(F3:F13,_xlfn.RANDARRAY(ROWS(F3:F13)))</f>
-        <v>-1.8</v>
-      </c>
-      <c r="G29" s="1" cm="1">
-        <f t="array" aca="1" ref="G29:G39" ca="1">_xlfn.SORTBY(G3:G13,_xlfn.RANDARRAY(ROWS(G3:G13)))</f>
-        <v>-1.2000000000000002</v>
-      </c>
-      <c r="H29" s="1" cm="1">
-        <f t="array" aca="1" ref="H29:H39" ca="1">_xlfn.SORTBY(H3:H13,_xlfn.RANDARRAY(ROWS(H3:H13)))</f>
-        <v>0.5</v>
-      </c>
-      <c r="I29" s="1" cm="1">
-        <f t="array" aca="1" ref="I29:I39" ca="1">_xlfn.SORTBY(I3:I13,_xlfn.RANDARRAY(ROWS(I3:I13)))</f>
-        <v>1.3</v>
-      </c>
-      <c r="J29" s="1" cm="1">
-        <f t="array" aca="1" ref="J29:J39" ca="1">_xlfn.SORTBY(J3:J13,_xlfn.RANDARRAY(ROWS(J3:J13)))</f>
-        <v>-0.30000000000000016</v>
-      </c>
-      <c r="K29" s="1" cm="1">
-        <f t="array" aca="1" ref="K29:K39" ca="1">_xlfn.SORTBY(K3:K13,_xlfn.RANDARRAY(ROWS(K3:K13)))</f>
-        <v>-0.59999999999999976</v>
-      </c>
-      <c r="L29" s="1" cm="1">
+      <c r="L29" s="1">
         <f t="array" aca="1" ref="L29:L39" ca="1">_xlfn.SORTBY(L3:L13,_xlfn.RANDARRAY(ROWS(L3:L13)))</f>
-        <v>0.95000000000000007</v>
-      </c>
-      <c r="M29" s="1" cm="1">
+        <v>2</v>
+      </c>
+      <c r="M29" s="1">
         <f t="array" aca="1" ref="M29:M39" ca="1">_xlfn.SORTBY(M3:M13,_xlfn.RANDARRAY(ROWS(M3:M13)))</f>
-        <v>1.05</v>
-      </c>
-      <c r="N29" s="1" cm="1">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="N29" s="1">
         <f t="array" aca="1" ref="N29:N39" ca="1">_xlfn.SORTBY(N3:N13,_xlfn.RANDARRAY(ROWS(N3:N13)))</f>
-        <v>-6.9999999999999951E-2</v>
-      </c>
-      <c r="O29" s="1" cm="1">
+        <v>-0.12</v>
+      </c>
+      <c r="O29" s="1">
         <f t="array" aca="1" ref="O29:O39" ca="1">_xlfn.SORTBY(O3:O13,_xlfn.RANDARRAY(ROWS(O3:O13)))</f>
-        <v>-1</v>
-      </c>
-      <c r="P29" s="1" cm="1">
+        <v>0.15000000000000011</v>
+      </c>
+      <c r="P29" s="1">
         <f t="array" aca="1" ref="P29:P39" ca="1">_xlfn.SORTBY(P3:P13,_xlfn.RANDARRAY(ROWS(P3:P13)))</f>
-        <v>-1.1099999999999999</v>
-      </c>
-      <c r="Q29" s="1" cm="1">
+        <v>-1.08</v>
+      </c>
+      <c r="Q29" s="1">
         <f t="array" aca="1" ref="Q29:Q39" ca="1">_xlfn.SORTBY(Q3:Q13,_xlfn.RANDARRAY(ROWS(Q3:Q13)))</f>
-        <v>-0.85999999999999988</v>
-      </c>
-      <c r="R29" s="1" cm="1">
+        <v>-2</v>
+      </c>
+      <c r="R29" s="1">
         <f t="array" aca="1" ref="R29:R39" ca="1">_xlfn.SORTBY(R3:R13,_xlfn.RANDARRAY(ROWS(R3:R13)))</f>
-        <v>1.04</v>
-      </c>
-      <c r="S29" s="1" cm="1">
+        <v>2.1</v>
+      </c>
+      <c r="S29" s="1">
         <f t="array" aca="1" ref="S29:S39" ca="1">_xlfn.SORTBY(S3:S13,_xlfn.RANDARRAY(ROWS(S3:S13)))</f>
-        <v>1.1500000000000001</v>
-      </c>
-      <c r="T29" s="1" cm="1">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="T29" s="1">
         <f t="array" aca="1" ref="T29:T39" ca="1">_xlfn.SORTBY(T3:T13,_xlfn.RANDARRAY(ROWS(T3:T13)))</f>
-        <v>-1.2400000000000002</v>
-      </c>
-      <c r="U29" s="1" cm="1">
+        <v>-0.1</v>
+      </c>
+      <c r="U29" s="1">
         <f t="array" aca="1" ref="U29:U39" ca="1">_xlfn.SORTBY(U3:U13,_xlfn.RANDARRAY(ROWS(U3:U13)))</f>
-        <v>-1.02</v>
-      </c>
-    </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+        <v>-0.95999999999999985</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>2</v>
       </c>
       <c r="B30" s="1">
         <f ca="1"/>
-        <v>1.9999999999999998</v>
+        <v>0</v>
       </c>
       <c r="C30" s="1">
         <f ca="1"/>
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="D30" s="1">
         <f ca="1"/>
-        <v>-0.6</v>
+        <v>0.2</v>
       </c>
       <c r="E30" s="1">
         <f ca="1"/>
-        <v>9.9999999999999867E-2</v>
+        <v>-0.4</v>
       </c>
       <c r="F30" s="1">
         <f ca="1"/>
@@ -2170,96 +2162,96 @@
       </c>
       <c r="G30" s="1">
         <f ca="1"/>
-        <v>-1.3</v>
+        <v>-0.8</v>
       </c>
       <c r="H30" s="1">
         <f ca="1"/>
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="I30" s="1">
         <f ca="1"/>
-        <v>0.79999999999999993</v>
+        <v>1.4</v>
       </c>
       <c r="J30" s="1">
         <f ca="1"/>
-        <v>-2.1</v>
+        <v>-1.1000000000000001</v>
       </c>
       <c r="K30" s="1">
         <f ca="1"/>
-        <v>-1.6</v>
+        <v>-0.9</v>
       </c>
       <c r="L30" s="1">
         <f ca="1"/>
-        <v>0.93</v>
+        <v>0.86</v>
       </c>
       <c r="M30" s="1">
         <f ca="1"/>
-        <v>1.1500000000000001</v>
+        <v>0</v>
       </c>
       <c r="N30" s="1">
         <f ca="1"/>
-        <v>-8.9999999999999969E-2</v>
+        <v>-0.14000000000000001</v>
       </c>
       <c r="O30" s="1">
         <f ca="1"/>
-        <v>5.0000000000000044E-2</v>
+        <v>6.0000000000000053E-2</v>
       </c>
       <c r="P30" s="1">
         <f ca="1"/>
-        <v>-1.1400000000000001</v>
+        <v>-1.06</v>
       </c>
       <c r="Q30" s="1">
         <f ca="1"/>
-        <v>-0.91999999999999993</v>
+        <v>-0.94</v>
       </c>
       <c r="R30" s="1">
         <f ca="1"/>
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="S30" s="1">
         <f ca="1"/>
-        <v>1.1600000000000001</v>
+        <v>1.22</v>
       </c>
       <c r="T30" s="1">
         <f ca="1"/>
-        <v>-1.25</v>
+        <v>-1.1499999999999999</v>
       </c>
       <c r="U30" s="1">
         <f ca="1"/>
-        <v>-0.97999999999999987</v>
-      </c>
-    </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+        <v>-1.05</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>3</v>
       </c>
       <c r="B31" s="1">
         <f ca="1"/>
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="C31" s="1">
         <f ca="1"/>
-        <v>0.79999999999999993</v>
+        <v>1.5</v>
       </c>
       <c r="D31" s="1">
         <f ca="1"/>
-        <v>0.19999999999999996</v>
+        <v>0.59999999999999987</v>
       </c>
       <c r="E31" s="1">
         <f ca="1"/>
-        <v>0.19999999999999996</v>
+        <v>-0.1000000000000001</v>
       </c>
       <c r="F31" s="1">
         <f ca="1"/>
-        <v>-0.8</v>
+        <v>-1</v>
       </c>
       <c r="G31" s="1">
         <f ca="1"/>
-        <v>-0.49999999999999978</v>
+        <v>-1.3</v>
       </c>
       <c r="H31" s="1">
         <f ca="1"/>
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="I31" s="1">
         <f ca="1"/>
@@ -2267,23 +2259,23 @@
       </c>
       <c r="J31" s="1">
         <f ca="1"/>
-        <v>-0.50000000000000011</v>
+        <v>-1.3</v>
       </c>
       <c r="K31" s="1">
         <f ca="1"/>
-        <v>-1.4000000000000001</v>
+        <v>-1.1000000000000001</v>
       </c>
       <c r="L31" s="1">
         <f ca="1"/>
-        <v>0.87</v>
+        <v>0.92</v>
       </c>
       <c r="M31" s="1">
         <f ca="1"/>
-        <v>1.1100000000000001</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="N31" s="1">
         <f ca="1"/>
-        <v>-0.14000000000000001</v>
+        <v>-0.11</v>
       </c>
       <c r="O31" s="1">
         <f ca="1"/>
@@ -2291,30 +2283,30 @@
       </c>
       <c r="P31" s="1">
         <f ca="1"/>
-        <v>-1.1299999999999999</v>
+        <v>-1.05</v>
       </c>
       <c r="Q31" s="1">
         <f ca="1"/>
-        <v>-0.95</v>
+        <v>-0.87999999999999989</v>
       </c>
       <c r="R31" s="1">
         <f ca="1"/>
-        <v>0.95</v>
+        <v>1.01</v>
       </c>
       <c r="S31" s="1">
         <f ca="1"/>
-        <v>1.2300000000000002</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="T31" s="1">
         <f ca="1"/>
-        <v>-1.1600000000000001</v>
+        <v>-1.19</v>
       </c>
       <c r="U31" s="1">
         <f ca="1"/>
-        <v>-0.95999999999999985</v>
-      </c>
-    </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+        <v>-2.1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>4</v>
       </c>
@@ -2324,136 +2316,136 @@
       </c>
       <c r="C32" s="1">
         <f ca="1"/>
-        <v>1.3</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="D32" s="1">
         <f ca="1"/>
-        <v>0.59999999999999987</v>
+        <v>0.99999999999999978</v>
       </c>
       <c r="E32" s="1">
         <f ca="1"/>
-        <v>0.50000000000000022</v>
+        <v>9.9999999999999867E-2</v>
       </c>
       <c r="F32" s="1">
         <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="G32" s="1">
+        <f ca="1"/>
+        <v>-0.90000000000000013</v>
+      </c>
+      <c r="H32" s="1">
+        <f ca="1"/>
+        <v>0.1</v>
+      </c>
+      <c r="I32" s="1">
+        <f ca="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="J32" s="1">
+        <f ca="1"/>
+        <v>-0.9</v>
+      </c>
+      <c r="K32" s="1">
+        <f ca="1"/>
         <v>-1.6</v>
       </c>
-      <c r="G32" s="1">
-        <f ca="1"/>
-        <v>-0.7</v>
-      </c>
-      <c r="H32" s="1">
-        <f ca="1"/>
-        <v>1.5</v>
-      </c>
-      <c r="I32" s="1">
-        <f ca="1"/>
-        <v>0.99999999999999989</v>
-      </c>
-      <c r="J32" s="1">
-        <f ca="1"/>
-        <v>-0.70000000000000007</v>
-      </c>
-      <c r="K32" s="1">
-        <f ca="1"/>
-        <v>-1.2000000000000002</v>
-      </c>
       <c r="L32" s="1">
         <f ca="1"/>
-        <v>0.89</v>
+        <v>0.94000000000000006</v>
       </c>
       <c r="M32" s="1">
         <f ca="1"/>
-        <v>1.1300000000000001</v>
+        <v>1.07</v>
       </c>
       <c r="N32" s="1">
         <f ca="1"/>
-        <v>-4.9999999999999933E-2</v>
+        <v>-7.999999999999996E-2</v>
       </c>
       <c r="O32" s="1">
         <f ca="1"/>
-        <v>6.0000000000000053E-2</v>
+        <v>0.13000000000000009</v>
       </c>
       <c r="P32" s="1">
         <f ca="1"/>
-        <v>-1.1200000000000001</v>
+        <v>-1.1100000000000001</v>
       </c>
       <c r="Q32" s="1">
         <f ca="1"/>
-        <v>-0.8899999999999999</v>
+        <v>-0.90999999999999992</v>
       </c>
       <c r="R32" s="1">
         <f ca="1"/>
-        <v>1.05</v>
+        <v>0.97</v>
       </c>
       <c r="S32" s="1">
         <f ca="1"/>
-        <v>1.1700000000000002</v>
+        <v>1.25</v>
       </c>
       <c r="T32" s="1">
         <f ca="1"/>
-        <v>-1.2200000000000002</v>
+        <v>-1.21</v>
       </c>
       <c r="U32" s="1">
         <f ca="1"/>
-        <v>-1.03</v>
-      </c>
-    </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+        <v>-1.02</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>5</v>
       </c>
       <c r="B33" s="1">
         <f ca="1"/>
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="C33" s="1">
         <f ca="1"/>
-        <v>1.4000000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="D33" s="1">
         <f ca="1"/>
-        <v>0</v>
+        <v>0.79999999999999982</v>
       </c>
       <c r="E33" s="1">
         <f ca="1"/>
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="F33" s="1">
         <f ca="1"/>
-        <v>-2</v>
+        <v>-0.40000000000000008</v>
       </c>
       <c r="G33" s="1">
         <f ca="1"/>
-        <v>-1.1000000000000001</v>
+        <v>-1.4</v>
       </c>
       <c r="H33" s="1">
         <f ca="1"/>
-        <v>1.7</v>
+        <v>0.70000000000000007</v>
       </c>
       <c r="I33" s="1">
         <f ca="1"/>
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J33" s="1">
         <f ca="1"/>
-        <v>-1.9000000000000001</v>
+        <v>-1.5</v>
       </c>
       <c r="K33" s="1">
         <f ca="1"/>
-        <v>-0.9</v>
+        <v>-0.79999999999999993</v>
       </c>
       <c r="L33" s="1">
         <f ca="1"/>
-        <v>0.94000000000000006</v>
+        <v>0.85</v>
       </c>
       <c r="M33" s="1">
         <f ca="1"/>
-        <v>1.07</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="N33" s="1">
         <f ca="1"/>
-        <v>-0.15000000000000002</v>
+        <v>-0.13</v>
       </c>
       <c r="O33" s="1">
         <f ca="1"/>
@@ -2461,137 +2453,137 @@
       </c>
       <c r="P33" s="1">
         <f ca="1"/>
-        <v>-1.06</v>
+        <v>-1.1200000000000001</v>
       </c>
       <c r="Q33" s="1">
         <f ca="1"/>
-        <v>-0.94</v>
+        <v>-0.86999999999999988</v>
       </c>
       <c r="R33" s="1">
         <f ca="1"/>
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="S33" s="1">
         <f ca="1"/>
-        <v>1.2100000000000002</v>
+        <v>1.18</v>
       </c>
       <c r="T33" s="1">
         <f ca="1"/>
-        <v>-1.1800000000000002</v>
+        <v>-1.25</v>
       </c>
       <c r="U33" s="1">
         <f ca="1"/>
-        <v>-2.1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+        <v>-1.01</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>6</v>
       </c>
       <c r="B34" s="1">
         <f ca="1"/>
-        <v>0.60000000000000009</v>
+        <v>1.8</v>
       </c>
       <c r="C34" s="1">
         <f ca="1"/>
-        <v>1.2</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="D34" s="1">
         <f ca="1"/>
-        <v>0.79999999999999982</v>
+        <v>-0.39999999999999991</v>
       </c>
       <c r="E34" s="1">
         <f ca="1"/>
-        <v>0</v>
+        <v>0.40000000000000008</v>
       </c>
       <c r="F34" s="1">
         <f ca="1"/>
-        <v>-0.20000000000000018</v>
+        <v>-1.2</v>
       </c>
       <c r="G34" s="1">
         <f ca="1"/>
+        <v>-0.7</v>
+      </c>
+      <c r="H34" s="1">
+        <f ca="1"/>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="I34" s="1">
+        <f ca="1"/>
+        <v>1.5</v>
+      </c>
+      <c r="J34" s="1">
+        <f ca="1"/>
+        <v>-1.9</v>
+      </c>
+      <c r="K34" s="1">
+        <f ca="1"/>
         <v>-1.4</v>
       </c>
-      <c r="H34" s="1">
-        <f ca="1"/>
-        <v>2.0999999999999996</v>
-      </c>
-      <c r="I34" s="1">
-        <f ca="1"/>
-        <v>1.6000000000000003</v>
-      </c>
-      <c r="J34" s="1">
-        <f ca="1"/>
-        <v>-1.1000000000000001</v>
-      </c>
-      <c r="K34" s="1">
-        <f ca="1"/>
-        <v>-0.79999999999999993</v>
-      </c>
       <c r="L34" s="1">
         <f ca="1"/>
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="M34" s="1">
         <f ca="1"/>
-        <v>1.1400000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="N34" s="1">
         <f ca="1"/>
-        <v>-7.999999999999996E-2</v>
+        <v>-4.9999999999999933E-2</v>
       </c>
       <c r="O34" s="1">
         <f ca="1"/>
-        <v>7.0000000000000062E-2</v>
+        <v>0.1400000000000001</v>
       </c>
       <c r="P34" s="1">
         <f ca="1"/>
-        <v>-1.0899999999999999</v>
+        <v>-1.0900000000000001</v>
       </c>
       <c r="Q34" s="1">
         <f ca="1"/>
-        <v>-0.84999999999999987</v>
+        <v>-0.8899999999999999</v>
       </c>
       <c r="R34" s="1">
         <f ca="1"/>
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="S34" s="1">
         <f ca="1"/>
-        <v>1.1800000000000002</v>
+        <v>1.23</v>
       </c>
       <c r="T34" s="1">
         <f ca="1"/>
-        <v>-1.17</v>
+        <v>-1.24</v>
       </c>
       <c r="U34" s="1">
         <f ca="1"/>
-        <v>-0.94999999999999984</v>
-      </c>
-    </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
+        <v>-0.97999999999999987</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>7</v>
       </c>
       <c r="B35" s="1">
         <f ca="1"/>
-        <v>1.4</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="C35" s="1">
         <f ca="1"/>
-        <v>1.0999999999999999</v>
+        <v>0.79999999999999993</v>
       </c>
       <c r="D35" s="1">
         <f ca="1"/>
-        <v>-0.8</v>
+        <v>0.39999999999999991</v>
       </c>
       <c r="E35" s="1">
         <f ca="1"/>
-        <v>0.30000000000000004</v>
+        <v>0.2</v>
       </c>
       <c r="F35" s="1">
         <f ca="1"/>
-        <v>-0.60000000000000009</v>
+        <v>-1.8</v>
       </c>
       <c r="G35" s="1">
         <f ca="1"/>
@@ -2599,391 +2591,391 @@
       </c>
       <c r="H35" s="1">
         <f ca="1"/>
-        <v>1.1000000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="I35" s="1">
         <f ca="1"/>
-        <v>1.5000000000000002</v>
+        <v>1.6</v>
       </c>
       <c r="J35" s="1">
         <f ca="1"/>
-        <v>-0.1</v>
+        <v>-2.1</v>
       </c>
       <c r="K35" s="1">
         <f ca="1"/>
-        <v>-1.5</v>
+        <v>-1.3</v>
       </c>
       <c r="L35" s="1">
         <f ca="1"/>
-        <v>0.92</v>
+        <v>0.87</v>
       </c>
       <c r="M35" s="1">
         <f ca="1"/>
-        <v>1.06</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="N35" s="1">
         <f ca="1"/>
-        <v>-0.12</v>
+        <v>-0.15</v>
       </c>
       <c r="O35" s="1">
         <f ca="1"/>
-        <v>0.15000000000000013</v>
+        <v>9.000000000000008E-2</v>
       </c>
       <c r="P35" s="1">
         <f ca="1"/>
-        <v>-1.0699999999999998</v>
+        <v>-1.07</v>
       </c>
       <c r="Q35" s="1">
         <f ca="1"/>
-        <v>-0.92999999999999994</v>
+        <v>-0.91999999999999993</v>
       </c>
       <c r="R35" s="1">
         <f ca="1"/>
-        <v>2.1</v>
+        <v>1.04</v>
       </c>
       <c r="S35" s="1">
         <f ca="1"/>
-        <v>1.2500000000000002</v>
+        <v>1.17</v>
       </c>
       <c r="T35" s="1">
         <f ca="1"/>
-        <v>-1.21</v>
+        <v>-1.18</v>
       </c>
       <c r="U35" s="1">
         <f ca="1"/>
-        <v>-0.96999999999999986</v>
-      </c>
-    </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+        <v>-0.98999999999999988</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>8</v>
       </c>
       <c r="B36" s="1">
         <f ca="1"/>
-        <v>1.5999999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="C36" s="1">
         <f ca="1"/>
-        <v>0.7</v>
+        <v>0.99999999999999989</v>
       </c>
       <c r="D36" s="1">
         <f ca="1"/>
-        <v>0.99999999999999978</v>
+        <v>-0.8</v>
       </c>
       <c r="E36" s="1">
         <f ca="1"/>
-        <v>-0.10000000000000009</v>
+        <v>-0.3</v>
       </c>
       <c r="F36" s="1">
         <f ca="1"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="G36" s="1">
         <f ca="1"/>
-        <v>-0.59999999999999987</v>
+        <v>-0.49999999999999978</v>
       </c>
       <c r="H36" s="1">
         <f ca="1"/>
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="I36" s="1">
         <f ca="1"/>
-        <v>0.89999999999999991</v>
+        <v>0.99999999999999989</v>
       </c>
       <c r="J36" s="1">
         <f ca="1"/>
-        <v>-0.9</v>
+        <v>-0.50000000000000011</v>
       </c>
       <c r="K36" s="1">
         <f ca="1"/>
-        <v>-1.1000000000000001</v>
+        <v>-0.59999999999999976</v>
       </c>
       <c r="L36" s="1">
         <f ca="1"/>
-        <v>0.85</v>
+        <v>0.89</v>
       </c>
       <c r="M36" s="1">
         <f ca="1"/>
-        <v>1.0900000000000001</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="N36" s="1">
         <f ca="1"/>
-        <v>1</v>
+        <v>-6.9999999999999951E-2</v>
       </c>
       <c r="O36" s="1">
         <f ca="1"/>
-        <v>9.000000000000008E-2</v>
+        <v>5.0000000000000037E-2</v>
       </c>
       <c r="P36" s="1">
         <f ca="1"/>
-        <v>-1.1499999999999999</v>
+        <v>-1.1299999999999999</v>
       </c>
       <c r="Q36" s="1">
         <f ca="1"/>
-        <v>-0.87999999999999989</v>
+        <v>-0.85999999999999988</v>
       </c>
       <c r="R36" s="1">
         <f ca="1"/>
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="S36" s="1">
         <f ca="1"/>
-        <v>0.1</v>
+        <v>1.24</v>
       </c>
       <c r="T36" s="1">
         <f ca="1"/>
-        <v>-0.1</v>
+        <v>-1.1599999999999999</v>
       </c>
       <c r="U36" s="1">
         <f ca="1"/>
-        <v>-1.05</v>
-      </c>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+        <v>-1.04</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>9</v>
       </c>
       <c r="B37" s="1">
         <f ca="1"/>
+        <v>1.6</v>
+      </c>
+      <c r="C37" s="1">
+        <f ca="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="D37" s="1">
+        <f ca="1"/>
+        <v>-1</v>
+      </c>
+      <c r="E37" s="1">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="F37" s="1">
+        <f ca="1"/>
+        <v>-0.8</v>
+      </c>
+      <c r="G37" s="1">
+        <f ca="1"/>
+        <v>-1.2</v>
+      </c>
+      <c r="H37" s="1">
+        <f ca="1"/>
+        <v>0.9</v>
+      </c>
+      <c r="I37" s="1">
+        <f ca="1"/>
+        <v>0.89999999999999991</v>
+      </c>
+      <c r="J37" s="1">
+        <f ca="1"/>
+        <v>-0.30000000000000021</v>
+      </c>
+      <c r="K37" s="1">
+        <f ca="1"/>
+        <v>-0.69999999999999984</v>
+      </c>
+      <c r="L37" s="1">
+        <f ca="1"/>
+        <v>0.95000000000000007</v>
+      </c>
+      <c r="M37" s="1">
+        <f ca="1"/>
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="N37" s="1">
+        <f ca="1"/>
         <v>1</v>
       </c>
-      <c r="C37" s="1">
-        <f ca="1"/>
-        <v>0.89999999999999991</v>
-      </c>
-      <c r="D37" s="1">
-        <f ca="1"/>
-        <v>0.39999999999999991</v>
-      </c>
-      <c r="E37" s="1">
-        <f ca="1"/>
-        <v>0.40000000000000013</v>
-      </c>
-      <c r="F37" s="1">
-        <f ca="1"/>
-        <v>-1.2</v>
-      </c>
-      <c r="G37" s="1">
-        <f ca="1"/>
-        <v>-1</v>
-      </c>
-      <c r="H37" s="1">
-        <f ca="1"/>
-        <v>0.30000000000000004</v>
-      </c>
-      <c r="I37" s="1">
-        <f ca="1"/>
-        <v>1.0999999999999999</v>
-      </c>
-      <c r="J37" s="1">
-        <f ca="1"/>
-        <v>-1.7000000000000002</v>
-      </c>
-      <c r="K37" s="1">
-        <f ca="1"/>
-        <v>-1.0000000000000002</v>
-      </c>
-      <c r="L37" s="1">
-        <f ca="1"/>
-        <v>0.91</v>
-      </c>
-      <c r="M37" s="1">
-        <f ca="1"/>
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="N37" s="1">
-        <f ca="1"/>
-        <v>-5.9999999999999942E-2</v>
-      </c>
       <c r="O37" s="1">
         <f ca="1"/>
         <v>0.1100000000000001</v>
       </c>
       <c r="P37" s="1">
         <f ca="1"/>
-        <v>-1.08</v>
+        <v>-1.1399999999999999</v>
       </c>
       <c r="Q37" s="1">
         <f ca="1"/>
-        <v>-2</v>
+        <v>-0.95</v>
       </c>
       <c r="R37" s="1">
         <f ca="1"/>
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="S37" s="1">
         <f ca="1"/>
-        <v>1.2400000000000002</v>
+        <v>1.19</v>
       </c>
       <c r="T37" s="1">
         <f ca="1"/>
-        <v>-1.19</v>
+        <v>-1.22</v>
       </c>
       <c r="U37" s="1">
         <f ca="1"/>
-        <v>-1.01</v>
-      </c>
-    </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
+        <v>-0.96999999999999986</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>10</v>
       </c>
       <c r="B38" s="1">
         <f ca="1"/>
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="C38" s="1">
         <f ca="1"/>
-        <v>1.5000000000000002</v>
+        <v>0.7</v>
       </c>
       <c r="D38" s="1">
         <f ca="1"/>
-        <v>-0.19999999999999996</v>
+        <v>-0.2</v>
       </c>
       <c r="E38" s="1">
         <f ca="1"/>
-        <v>-0.5</v>
+        <v>0.3</v>
       </c>
       <c r="F38" s="1">
         <f ca="1"/>
-        <v>-0.40000000000000013</v>
+        <v>-0.60000000000000009</v>
       </c>
       <c r="G38" s="1">
         <f ca="1"/>
-        <v>-0.8</v>
+        <v>-1</v>
       </c>
       <c r="H38" s="1">
         <f ca="1"/>
-        <v>0.70000000000000007</v>
+        <v>1.5</v>
       </c>
       <c r="I38" s="1">
         <f ca="1"/>
-        <v>0.6</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="J38" s="1">
         <f ca="1"/>
-        <v>-1.3</v>
+        <v>-0.1</v>
       </c>
       <c r="K38" s="1">
         <f ca="1"/>
-        <v>-0.69999999999999984</v>
+        <v>-1.2</v>
       </c>
       <c r="L38" s="1">
         <f ca="1"/>
-        <v>2</v>
+        <v>0.88</v>
       </c>
       <c r="M38" s="1">
         <f ca="1"/>
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N38" s="1">
         <f ca="1"/>
-        <v>-0.13</v>
+        <v>-5.9999999999999942E-2</v>
       </c>
       <c r="O38" s="1">
         <f ca="1"/>
-        <v>0.13000000000000012</v>
+        <v>7.0000000000000062E-2</v>
       </c>
       <c r="P38" s="1">
         <f ca="1"/>
-        <v>0</v>
+        <v>-1.1499999999999999</v>
       </c>
       <c r="Q38" s="1">
         <f ca="1"/>
-        <v>-0.90999999999999992</v>
+        <v>-0.92999999999999994</v>
       </c>
       <c r="R38" s="1">
         <f ca="1"/>
-        <v>0.98</v>
+        <v>1.03</v>
       </c>
       <c r="S38" s="1">
         <f ca="1"/>
-        <v>1.1900000000000002</v>
+        <v>0.1</v>
       </c>
       <c r="T38" s="1">
         <f ca="1"/>
-        <v>-1.1499999999999999</v>
+        <v>-1.17</v>
       </c>
       <c r="U38" s="1">
         <f ca="1"/>
-        <v>-0.98999999999999988</v>
-      </c>
-    </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
+        <v>-1.03</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>11</v>
       </c>
       <c r="B39" s="1">
         <f ca="1"/>
-        <v>1.7999999999999998</v>
+        <v>1</v>
       </c>
       <c r="C39" s="1">
         <f ca="1"/>
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="D39" s="1">
         <f ca="1"/>
-        <v>-0.39999999999999991</v>
+        <v>-0.6</v>
       </c>
       <c r="E39" s="1">
         <f ca="1"/>
-        <v>-0.30000000000000004</v>
+        <v>0.50000000000000022</v>
       </c>
       <c r="F39" s="1">
         <f ca="1"/>
+        <v>-1.6</v>
+      </c>
+      <c r="G39" s="1">
+        <f ca="1"/>
+        <v>-0.59999999999999987</v>
+      </c>
+      <c r="H39" s="1">
+        <f ca="1"/>
+        <v>0.3</v>
+      </c>
+      <c r="I39" s="1">
+        <f ca="1"/>
+        <v>1.3</v>
+      </c>
+      <c r="J39" s="1">
+        <f ca="1"/>
+        <v>-1.7</v>
+      </c>
+      <c r="K39" s="1">
+        <f ca="1"/>
+        <v>-1.5</v>
+      </c>
+      <c r="L39" s="1">
+        <f ca="1"/>
+        <v>0.91</v>
+      </c>
+      <c r="M39" s="1">
+        <f ca="1"/>
+        <v>1.08</v>
+      </c>
+      <c r="N39" s="1">
+        <f ca="1"/>
+        <v>-8.9999999999999969E-2</v>
+      </c>
+      <c r="O39" s="1">
+        <f ca="1"/>
         <v>-1</v>
       </c>
-      <c r="G39" s="1">
-        <f ca="1"/>
-        <v>-0.90000000000000013</v>
-      </c>
-      <c r="H39" s="1">
-        <f ca="1"/>
-        <v>1.3</v>
-      </c>
-      <c r="I39" s="1">
-        <f ca="1"/>
-        <v>1.4000000000000001</v>
-      </c>
-      <c r="J39" s="1">
-        <f ca="1"/>
-        <v>-1.5</v>
-      </c>
-      <c r="K39" s="1">
-        <f ca="1"/>
-        <v>-1.3000000000000003</v>
-      </c>
-      <c r="L39" s="1">
-        <f ca="1"/>
-        <v>0.88</v>
-      </c>
-      <c r="M39" s="1">
-        <f ca="1"/>
-        <v>1.08</v>
-      </c>
-      <c r="N39" s="1">
-        <f ca="1"/>
-        <v>-0.10999999999999999</v>
-      </c>
-      <c r="O39" s="1">
-        <f ca="1"/>
-        <v>0.14000000000000012</v>
-      </c>
       <c r="P39" s="1">
         <f ca="1"/>
-        <v>-1.0499999999999998</v>
+        <v>0</v>
       </c>
       <c r="Q39" s="1">
         <f ca="1"/>
-        <v>-0.86999999999999988</v>
+        <v>-0.84999999999999987</v>
       </c>
       <c r="R39" s="1">
         <f ca="1"/>
-        <v>1.02</v>
+        <v>0.96</v>
       </c>
       <c r="S39" s="1">
         <f ca="1"/>
-        <v>1.2200000000000002</v>
+        <v>1.21</v>
       </c>
       <c r="T39" s="1">
         <f ca="1"/>
@@ -2991,12 +2983,12 @@
       </c>
       <c r="U39" s="1">
         <f ca="1"/>
-        <v>-1.04</v>
-      </c>
-    </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
+        <v>-0.94999999999999984</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B41" s="1">
         <f t="shared" ref="B41:U41" ca="1" si="6">AVERAGE(B29:B39)</f>
@@ -3004,11 +2996,11 @@
       </c>
       <c r="C41" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0.99999999999999989</v>
       </c>
       <c r="D41" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>-6.0557619525008534E-17</v>
+        <v>0</v>
       </c>
       <c r="E41" s="1">
         <f t="shared" ca="1" si="6"/>
@@ -3020,7 +3012,7 @@
       </c>
       <c r="G41" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>-1.0000000000000002</v>
+        <v>-0.99999999999999989</v>
       </c>
       <c r="H41" s="1">
         <f t="shared" ca="1" si="6"/>
@@ -3028,11 +3020,11 @@
       </c>
       <c r="I41" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>1.1000000000000001</v>
+        <v>1.0999999999999999</v>
       </c>
       <c r="J41" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>-1.1000000000000001</v>
+        <v>-1.0999999999999999</v>
       </c>
       <c r="K41" s="1">
         <f t="shared" ca="1" si="6"/>
@@ -3052,11 +3044,11 @@
       </c>
       <c r="O41" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>8.0743492700011387E-17</v>
+        <v>0</v>
       </c>
       <c r="P41" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-1.0000000000000002</v>
       </c>
       <c r="Q41" s="1">
         <f t="shared" ca="1" si="6"/>
@@ -3068,28 +3060,28 @@
       </c>
       <c r="S41" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>1.1000000000000001</v>
+        <v>1.0999999999999999</v>
       </c>
       <c r="T41" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>-1.0999999999999999</v>
+        <v>-1.1000000000000001</v>
       </c>
       <c r="U41" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>-1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
+        <v>-1.0999999999999999</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B42" s="4">
         <f t="shared" ref="B42:U42" ca="1" si="7">_xlfn.STDEV.P(B29:B39)</f>
-        <v>0.63245553203367555</v>
+        <v>0.63245553203367566</v>
       </c>
       <c r="C42" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>0.31622776601683822</v>
+        <v>0.31622776601683844</v>
       </c>
       <c r="D42" s="4">
         <f t="shared" ca="1" si="7"/>
@@ -3105,7 +3097,7 @@
       </c>
       <c r="G42" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>0.31622776601683766</v>
+        <v>0.31622776601683844</v>
       </c>
       <c r="H42" s="4">
         <f t="shared" ca="1" si="7"/>
@@ -3113,15 +3105,15 @@
       </c>
       <c r="I42" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>0.3162277660168375</v>
+        <v>0.31622776601683783</v>
       </c>
       <c r="J42" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>0.63245553203367566</v>
+        <v>0.63245553203367588</v>
       </c>
       <c r="K42" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>0.31622776601683822</v>
+        <v>0.31622776601683861</v>
       </c>
       <c r="L42" s="1">
         <f t="shared" ca="1" si="7"/>
@@ -3141,7 +3133,7 @@
       </c>
       <c r="P42" s="1">
         <f t="shared" ca="1" si="7"/>
-        <v>0.31780497164141375</v>
+        <v>0.31780497164141358</v>
       </c>
       <c r="Q42" s="1">
         <f t="shared" ca="1" si="7"/>
@@ -3149,72 +3141,72 @@
       </c>
       <c r="R42" s="1">
         <f t="shared" ca="1" si="7"/>
-        <v>0.31780497164141414</v>
+        <v>0.31780497164141486</v>
       </c>
       <c r="S42" s="1">
         <f t="shared" ca="1" si="7"/>
-        <v>0.31780497164141414</v>
+        <v>0.31780497164141486</v>
       </c>
       <c r="T42" s="1">
         <f t="shared" ca="1" si="7"/>
-        <v>0.31780497164141414</v>
+        <v>0.31780497164141375</v>
       </c>
       <c r="U42" s="1">
         <f t="shared" ca="1" si="7"/>
-        <v>0.31780497164141336</v>
-      </c>
-    </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
+        <v>0.31780497164141486</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B43" s="1">
         <f t="shared" ref="B43:U43" ca="1" si="8">_xlfn.SKEW.P(B29:B39)</f>
-        <v>-4.0371746350005691E-16</v>
+        <v>3.0278809762504267E-17</v>
       </c>
       <c r="C43" s="1">
         <f t="shared" ca="1" si="8"/>
-        <v>5.2483270255007403E-16</v>
+        <v>8.4780667335011958E-16</v>
       </c>
       <c r="D43" s="1">
         <f t="shared" ca="1" si="8"/>
-        <v>6.5604087818759253E-17</v>
+        <v>-4.339962732625612E-16</v>
       </c>
       <c r="E43" s="1">
         <f t="shared" ca="1" si="8"/>
-        <v>5.6520444890007968E-16</v>
+        <v>4.0371746350005691E-16</v>
       </c>
       <c r="F43" s="1">
         <f t="shared" ca="1" si="8"/>
-        <v>-2.523234146875356E-16</v>
+        <v>-4.1381040008755832E-16</v>
       </c>
       <c r="G43" s="1">
         <f t="shared" ca="1" si="8"/>
-        <v>2.7629413908285146E-15</v>
+        <v>-2.4223047810003414E-16</v>
       </c>
       <c r="H43" s="1">
         <f t="shared" ca="1" si="8"/>
-        <v>-7.9355713919229936E-16</v>
+        <v>-3.6334571715005125E-16</v>
       </c>
       <c r="I43" s="1">
         <f t="shared" ca="1" si="8"/>
-        <v>1.0092936587501423E-16</v>
+        <v>1.1909665173251679E-15</v>
       </c>
       <c r="J43" s="1">
         <f t="shared" ca="1" si="8"/>
-        <v>-1.3120817563751851E-16</v>
+        <v>-7.5697024406260675E-16</v>
       </c>
       <c r="K43" s="1">
         <f t="shared" ca="1" si="8"/>
-        <v>-1.0092936587501424E-15</v>
+        <v>-5.6520444890007968E-16</v>
       </c>
       <c r="L43" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>2.7945403348921518</v>
+        <v>2.794540334892154</v>
       </c>
       <c r="M43" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>-2.7945403348921536</v>
+        <v>-2.794540334892154</v>
       </c>
       <c r="N43" s="4">
         <f t="shared" ca="1" si="8"/>
@@ -3222,11 +3214,11 @@
       </c>
       <c r="O43" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>-2.7945403348921531</v>
+        <v>-2.7945403348921518</v>
       </c>
       <c r="P43" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>2.7945403348921518</v>
+        <v>2.7945403348921536</v>
       </c>
       <c r="Q43" s="4">
         <f t="shared" ca="1" si="8"/>
@@ -3234,32 +3226,32 @@
       </c>
       <c r="R43" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>2.7945403348921536</v>
+        <v>2.794540334892154</v>
       </c>
       <c r="S43" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>-2.7945403348921514</v>
+        <v>-2.7945403348921505</v>
       </c>
       <c r="T43" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>2.79454033489215</v>
+        <v>2.794540334892154</v>
       </c>
       <c r="U43" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>-2.7945403348921514</v>
-      </c>
-    </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
+        <v>-2.794540334892154</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B44" s="1">
         <f t="shared" ref="B44:U44" ca="1" si="9">KURT(B29:B39)</f>
-        <v>-1.2000000000000011</v>
+        <v>-1.2000000000000015</v>
       </c>
       <c r="C44" s="1">
         <f t="shared" ca="1" si="9"/>
-        <v>-1.1999999999999988</v>
+        <v>-1.200000000000002</v>
       </c>
       <c r="D44" s="1">
         <f t="shared" ca="1" si="9"/>
@@ -3267,7 +3259,7 @@
       </c>
       <c r="E44" s="1">
         <f t="shared" ca="1" si="9"/>
-        <v>-1.2000000000000015</v>
+        <v>-1.1999999999999997</v>
       </c>
       <c r="F44" s="1">
         <f t="shared" ca="1" si="9"/>
@@ -3279,15 +3271,15 @@
       </c>
       <c r="H44" s="1">
         <f t="shared" ca="1" si="9"/>
-        <v>-1.2000000000000015</v>
+        <v>-1.200000000000002</v>
       </c>
       <c r="I44" s="1">
         <f t="shared" ca="1" si="9"/>
-        <v>-1.2000000000000002</v>
+        <v>-1.2000000000000011</v>
       </c>
       <c r="J44" s="1">
         <f t="shared" ca="1" si="9"/>
-        <v>-1.2000000000000015</v>
+        <v>-1.2000000000000011</v>
       </c>
       <c r="K44" s="1">
         <f t="shared" ca="1" si="9"/>
@@ -3295,11 +3287,11 @@
       </c>
       <c r="L44" s="1">
         <f t="shared" ca="1" si="9"/>
-        <v>10.711250530993684</v>
+        <v>10.711250530993706</v>
       </c>
       <c r="M44" s="1">
         <f t="shared" ca="1" si="9"/>
-        <v>10.711250530993702</v>
+        <v>10.711250530993706</v>
       </c>
       <c r="N44" s="1">
         <f t="shared" ca="1" si="9"/>
@@ -3307,19 +3299,19 @@
       </c>
       <c r="O44" s="1">
         <f t="shared" ca="1" si="9"/>
-        <v>10.711250530993706</v>
+        <v>10.711250530993684</v>
       </c>
       <c r="P44" s="1">
         <f t="shared" ca="1" si="9"/>
-        <v>10.711250530993684</v>
+        <v>10.711250530993702</v>
       </c>
       <c r="Q44" s="1">
         <f t="shared" ca="1" si="9"/>
-        <v>10.711250530993702</v>
+        <v>10.711250530993706</v>
       </c>
       <c r="R44" s="1">
         <f t="shared" ca="1" si="9"/>
-        <v>10.711250530993702</v>
+        <v>10.711250530993706</v>
       </c>
       <c r="S44" s="1">
         <f t="shared" ca="1" si="9"/>
@@ -3327,14 +3319,14 @@
       </c>
       <c r="T44" s="1">
         <f t="shared" ca="1" si="9"/>
-        <v>10.711250530993684</v>
+        <v>10.711250530993706</v>
       </c>
       <c r="U44" s="1">
         <f t="shared" ca="1" si="9"/>
-        <v>10.711250530993684</v>
-      </c>
-    </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
+        <v>10.711250530993706</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>14</v>
       </c>
@@ -3388,7 +3380,7 @@
       </c>
       <c r="N45" s="1">
         <f t="shared" ca="1" si="10"/>
-        <v>-0.15000000000000002</v>
+        <v>-0.15</v>
       </c>
       <c r="O45" s="1">
         <f t="shared" ca="1" si="10"/>
@@ -3419,17 +3411,17 @@
         <v>-2.1</v>
       </c>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>15</v>
       </c>
       <c r="B46" s="1">
         <f t="shared" ref="B46:U46" ca="1" si="11">MAX(B29:B39)</f>
-        <v>1.9999999999999998</v>
+        <v>2</v>
       </c>
       <c r="C46" s="1">
         <f t="shared" ca="1" si="11"/>
-        <v>1.5000000000000002</v>
+        <v>1.5</v>
       </c>
       <c r="D46" s="1">
         <f t="shared" ca="1" si="11"/>
@@ -3449,11 +3441,11 @@
       </c>
       <c r="H46" s="1">
         <f t="shared" ca="1" si="11"/>
-        <v>2.0999999999999996</v>
+        <v>2.1</v>
       </c>
       <c r="I46" s="1">
         <f t="shared" ca="1" si="11"/>
-        <v>1.6000000000000003</v>
+        <v>1.6</v>
       </c>
       <c r="J46" s="1">
         <f t="shared" ca="1" si="11"/>
@@ -3469,7 +3461,7 @@
       </c>
       <c r="M46" s="1">
         <f t="shared" ca="1" si="11"/>
-        <v>1.1500000000000001</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="N46" s="1">
         <f t="shared" ca="1" si="11"/>
@@ -3477,7 +3469,7 @@
       </c>
       <c r="O46" s="1">
         <f t="shared" ca="1" si="11"/>
-        <v>0.15000000000000013</v>
+        <v>0.15000000000000011</v>
       </c>
       <c r="P46" s="1">
         <f t="shared" ca="1" si="11"/>
@@ -3493,7 +3485,7 @@
       </c>
       <c r="S46" s="1">
         <f t="shared" ca="1" si="11"/>
-        <v>1.2500000000000002</v>
+        <v>1.25</v>
       </c>
       <c r="T46" s="1">
         <f t="shared" ca="1" si="11"/>
@@ -3504,139 +3496,139 @@
         <v>-0.94999999999999984</v>
       </c>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>16</v>
       </c>
       <c r="B47" s="1">
         <f ca="1">CORREL(B29:B39,C29:C39)</f>
-        <v>-0.58181818181818168</v>
+        <v>0.12727272727272737</v>
       </c>
       <c r="D47" s="1">
         <f ca="1">CORREL(D29:D39,E29:E39)</f>
-        <v>0.23636363636363639</v>
+        <v>-0.29090909090909095</v>
       </c>
       <c r="F47" s="1">
         <f ca="1">CORREL(F29:F39,G29:G39)</f>
-        <v>0.13636363636363655</v>
+        <v>-0.33636363636363636</v>
       </c>
       <c r="H47" s="1">
         <f ca="1">CORREL(H29:H39,I29:I39)</f>
-        <v>0.35454545454545455</v>
+        <v>0.2</v>
       </c>
       <c r="J47" s="1">
         <f ca="1">CORREL(J29:J39,K29:K39)</f>
-        <v>2.7272727272727403E-2</v>
+        <v>0.46363636363636357</v>
       </c>
       <c r="L47" s="1">
         <f ca="1">CORREL(L29:L39,M29:M39)</f>
-        <v>-0.99378937893789376</v>
+        <v>0.18712871287128705</v>
       </c>
       <c r="N47" s="1">
         <f ca="1">CORREL(N29:N39,O29:O39)</f>
-        <v>5.4725472547254676E-2</v>
+        <v>9.9549954995499568E-2</v>
       </c>
       <c r="P47" s="1">
         <f ca="1">CORREL(P29:P39,Q29:Q39)</f>
-        <v>6.9486948694869599E-2</v>
+        <v>0.12934293429342944</v>
       </c>
       <c r="R47" s="1">
         <f ca="1">CORREL(R29:R39,S29:S39)</f>
-        <v>0.13627362736273632</v>
+        <v>2.8352835283528287E-2</v>
       </c>
       <c r="T47" s="1">
         <f ca="1">CORREL(T29:T39,U29:U39)</f>
-        <v>3.4023402340234057E-2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
+        <v>0.1224122412241225</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>17</v>
       </c>
-      <c r="B48" cm="1">
+      <c r="B48">
         <f t="array" aca="1" ref="B48" ca="1">SUMPRODUCT((B29:B39&gt;C29:C39)*1)</f>
+        <v>4</v>
+      </c>
+      <c r="C48">
+        <f t="array" aca="1" ref="C48" ca="1">SUMPRODUCT((B29:B39&lt;C29:C39)*1)</f>
+        <v>7</v>
+      </c>
+      <c r="D48">
+        <f t="array" aca="1" ref="D48" ca="1">SUMPRODUCT((D29:D39&gt;E29:E39)*1)</f>
+        <v>6</v>
+      </c>
+      <c r="E48">
+        <f t="array" aca="1" ref="E48" ca="1">SUMPRODUCT((D29:D39&lt;E29:E39)*1)</f>
         <v>5</v>
       </c>
-      <c r="C48" cm="1">
-        <f t="array" aca="1" ref="C48" ca="1">SUMPRODUCT((B29:B39&lt;C29:C39)*1)</f>
+      <c r="F48">
+        <f t="array" aca="1" ref="F48" ca="1">SUMPRODUCT((F29:F39&gt;G29:G39)*1)</f>
         <v>6</v>
       </c>
-      <c r="D48" cm="1">
-        <f t="array" aca="1" ref="D48" ca="1">SUMPRODUCT((D29:D39&gt;E29:E39)*1)</f>
+      <c r="G48">
+        <f t="array" aca="1" ref="G48" ca="1">SUMPRODUCT((F29:F39&lt;G29:G39)*1)</f>
         <v>5</v>
       </c>
-      <c r="E48" cm="1">
-        <f t="array" aca="1" ref="E48" ca="1">SUMPRODUCT((D29:D39&lt;E29:E39)*1)</f>
+      <c r="H48">
+        <f t="array" aca="1" ref="H48" ca="1">SUMPRODUCT((H29:H39&gt;I29:I39)*1)</f>
+        <v>6</v>
+      </c>
+      <c r="I48">
+        <f t="array" aca="1" ref="I48" ca="1">SUMPRODUCT((H29:H39&lt;I29:I39)*1)</f>
         <v>4</v>
       </c>
-      <c r="F48" cm="1">
-        <f t="array" aca="1" ref="F48" ca="1">SUMPRODUCT((F29:F39&gt;G29:G39)*1)</f>
-        <v>4</v>
-      </c>
-      <c r="G48" cm="1">
-        <f t="array" aca="1" ref="G48" ca="1">SUMPRODUCT((F29:F39&lt;G29:G39)*1)</f>
-        <v>7</v>
-      </c>
-      <c r="H48" cm="1">
-        <f t="array" aca="1" ref="H48" ca="1">SUMPRODUCT((H29:H39&gt;I29:I39)*1)</f>
-        <v>5</v>
-      </c>
-      <c r="I48" cm="1">
-        <f t="array" aca="1" ref="I48" ca="1">SUMPRODUCT((H29:H39&lt;I29:I39)*1)</f>
-        <v>5</v>
-      </c>
-      <c r="J48" cm="1">
+      <c r="J48">
         <f t="array" aca="1" ref="J48" ca="1">SUMPRODUCT((J29:J39&gt;K29:K39)*1)</f>
         <v>5</v>
       </c>
-      <c r="K48" cm="1">
+      <c r="K48">
         <f t="array" aca="1" ref="K48" ca="1">SUMPRODUCT((J29:J39&lt;K29:K39)*1)</f>
         <v>6</v>
       </c>
-      <c r="L48" cm="1">
+      <c r="L48">
         <f t="array" aca="1" ref="L48" ca="1">SUMPRODUCT((L29:L39&gt;M29:M39)*1)</f>
-        <v>1</v>
-      </c>
-      <c r="M48" cm="1">
+        <v>2</v>
+      </c>
+      <c r="M48">
         <f t="array" aca="1" ref="M48" ca="1">SUMPRODUCT((L29:L39&lt;M29:M39)*1)</f>
-        <v>10</v>
-      </c>
-      <c r="N48" cm="1">
+        <v>9</v>
+      </c>
+      <c r="N48">
         <f t="array" aca="1" ref="N48" ca="1">SUMPRODUCT((N29:N39&gt;O29:O39)*1)</f>
         <v>2</v>
       </c>
-      <c r="O48" cm="1">
+      <c r="O48">
         <f t="array" aca="1" ref="O48" ca="1">SUMPRODUCT((N29:N39&lt;O29:O39)*1)</f>
         <v>9</v>
       </c>
-      <c r="P48" cm="1">
+      <c r="P48">
         <f t="array" aca="1" ref="P48" ca="1">SUMPRODUCT((P29:P39&gt;Q29:Q39)*1)</f>
         <v>2</v>
       </c>
-      <c r="Q48" cm="1">
+      <c r="Q48">
         <f t="array" aca="1" ref="Q48" ca="1">SUMPRODUCT((P29:P39&lt;Q29:Q39)*1)</f>
         <v>9</v>
       </c>
-      <c r="R48" cm="1">
+      <c r="R48">
         <f t="array" aca="1" ref="R48" ca="1">SUMPRODUCT((R29:R39&gt;S29:S39)*1)</f>
         <v>2</v>
       </c>
-      <c r="S48" cm="1">
+      <c r="S48">
         <f t="array" aca="1" ref="S48" ca="1">SUMPRODUCT((R29:R39&lt;S29:S39)*1)</f>
         <v>9</v>
       </c>
-      <c r="T48" cm="1">
+      <c r="T48">
         <f t="array" aca="1" ref="T48" ca="1">SUMPRODUCT((T29:T39&gt;U29:U39)*1)</f>
         <v>2</v>
       </c>
-      <c r="U48" cm="1">
+      <c r="U48">
         <f t="array" aca="1" ref="U48" ca="1">SUMPRODUCT((T29:T39&lt;U29:U39)*1)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A49" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B49" s="6" t="str">
         <f ca="1">IF(B48&gt;C48,"A",IF(C48&gt;B48,"B","Equal"))</f>
@@ -3648,11 +3640,11 @@
       </c>
       <c r="F49" s="6" t="str">
         <f ca="1">IF(F48&gt;G48,"A",IF(G48&gt;F48,"B","Equal"))</f>
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="H49" s="6" t="str">
         <f ca="1">IF(H48&gt;I48,"A",IF(I48&gt;H48,"B","Equal"))</f>
-        <v>Equal</v>
+        <v>A</v>
       </c>
       <c r="J49" s="6" t="str">
         <f ca="1">IF(J48&gt;K48,"A",IF(K48&gt;J48,"B","Equal"))</f>
@@ -3679,25 +3671,25 @@
         <v>B</v>
       </c>
     </row>
-    <row r="50" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>19</v>
       </c>
       <c r="B50">
         <f ca="1">MAX(B48:C48)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D50">
         <f ca="1">MAX(D48:E48)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F50">
         <f ca="1">MAX(F48:G48)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H50">
         <f ca="1">MAX(H48:I48)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J50">
         <f ca="1">MAX(J48:K48)</f>
@@ -3705,7 +3697,7 @@
       </c>
       <c r="L50">
         <f ca="1">MAX(L48:M48)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N50">
         <f ca="1">MAX(N48:O48)</f>
@@ -3724,55 +3716,55 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A52" s="8" t="s">
+    <row r="52" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A52" s="7" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="54" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A54" s="2"/>
-      <c r="B54" s="7" t="s">
+      <c r="B54" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C54" s="12"/>
+      <c r="D54" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E54" s="12"/>
+      <c r="F54" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G54" s="12"/>
+      <c r="H54" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="I54" s="12"/>
+      <c r="J54" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="K54" s="12"/>
+      <c r="L54" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="M54" s="12"/>
+      <c r="N54" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="O54" s="12"/>
+      <c r="P54" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q54" s="12"/>
+      <c r="R54" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="S54" s="12"/>
+      <c r="T54" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E54" s="7"/>
-      <c r="F54" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G54" s="7"/>
-      <c r="H54" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="I54" s="7"/>
-      <c r="J54" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="K54" s="7"/>
-      <c r="L54" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="M54" s="7"/>
-      <c r="N54" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="O54" s="7"/>
-      <c r="P54" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q54" s="7"/>
-      <c r="R54" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="S54" s="7"/>
-      <c r="T54" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="U54" s="7"/>
-    </row>
-    <row r="55" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="U54" s="12"/>
+    </row>
+    <row r="55" spans="1:28" x14ac:dyDescent="0.35">
       <c r="B55" s="1">
         <v>0</v>
       </c>
@@ -3783,13 +3775,13 @@
         <v>-1</v>
       </c>
       <c r="E55" s="1">
-        <v>-0.20000000000000007</v>
+        <v>-0.20000000000000009</v>
       </c>
       <c r="F55" s="1">
         <v>-2</v>
       </c>
       <c r="G55" s="1">
-        <v>-1.2000000000000002</v>
+        <v>-1.2</v>
       </c>
       <c r="H55" s="1">
         <v>0.1</v>
@@ -3801,7 +3793,7 @@
         <v>-2.1</v>
       </c>
       <c r="K55" s="1">
-        <v>-1.3000000000000003</v>
+        <v>-1.3</v>
       </c>
       <c r="L55" s="1">
         <v>0.85</v>
@@ -3810,10 +3802,10 @@
         <v>1.05</v>
       </c>
       <c r="N55" s="1">
-        <v>-0.15000000000000002</v>
+        <v>-0.15</v>
       </c>
       <c r="O55" s="1">
-        <v>5.0000000000000044E-2</v>
+        <v>5.0000000000000037E-2</v>
       </c>
       <c r="P55" s="1">
         <v>-1.1499999999999999</v>
@@ -3825,7 +3817,7 @@
         <v>0.95</v>
       </c>
       <c r="S55" s="1">
-        <v>1.1500000000000001</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="T55" s="1">
         <v>-1.25</v>
@@ -3834,13 +3826,13 @@
         <v>-1.05</v>
       </c>
       <c r="V55" s="1"/>
-      <c r="W55" s="9"/>
-      <c r="X55" s="9"/>
-      <c r="Y55" s="9"/>
-      <c r="Z55" s="9"/>
+      <c r="W55" s="1"/>
+      <c r="X55" s="1"/>
+      <c r="Y55" s="1"/>
+      <c r="Z55" s="1"/>
       <c r="AB55" s="1"/>
     </row>
-    <row r="56" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:28" x14ac:dyDescent="0.35">
       <c r="B56" s="1">
         <v>0.2</v>
       </c>
@@ -3851,7 +3843,7 @@
         <v>-0.8</v>
       </c>
       <c r="E56" s="1">
-        <v>-0.10000000000000009</v>
+        <v>-0.1000000000000001</v>
       </c>
       <c r="F56" s="1">
         <v>-1.8</v>
@@ -3860,16 +3852,16 @@
         <v>-1.1000000000000001</v>
       </c>
       <c r="H56" s="1">
-        <v>0.30000000000000004</v>
+        <v>0.3</v>
       </c>
       <c r="I56" s="1">
         <v>0.99999999999999989</v>
       </c>
       <c r="J56" s="1">
-        <v>-1.9000000000000001</v>
+        <v>-1.9</v>
       </c>
       <c r="K56" s="1">
-        <v>-1.2000000000000002</v>
+        <v>-1.2</v>
       </c>
       <c r="L56" s="1">
         <v>0.86</v>
@@ -3884,7 +3876,7 @@
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="P56" s="1">
-        <v>-1.1400000000000001</v>
+        <v>-1.1399999999999999</v>
       </c>
       <c r="Q56" s="1">
         <v>-0.94</v>
@@ -3893,22 +3885,22 @@
         <v>0.96</v>
       </c>
       <c r="S56" s="1">
-        <v>1.1600000000000001</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="T56" s="1">
-        <v>-1.2400000000000002</v>
+        <v>-1.24</v>
       </c>
       <c r="U56" s="1">
         <v>-1.04</v>
       </c>
       <c r="V56" s="1"/>
-      <c r="W56" s="9"/>
-      <c r="X56" s="9"/>
-      <c r="Y56" s="9"/>
-      <c r="Z56" s="9"/>
+      <c r="W56" s="1"/>
+      <c r="X56" s="1"/>
+      <c r="Y56" s="1"/>
+      <c r="Z56" s="1"/>
       <c r="AB56" s="1"/>
     </row>
-    <row r="57" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:28" x14ac:dyDescent="0.35">
       <c r="B57" s="1">
         <v>0.4</v>
       </c>
@@ -3931,10 +3923,10 @@
         <v>0.5</v>
       </c>
       <c r="I57" s="1">
-        <v>1.0999999999999999</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="J57" s="1">
-        <v>-1.7000000000000002</v>
+        <v>-1.7</v>
       </c>
       <c r="K57" s="1">
         <v>-1.1000000000000001</v>
@@ -3961,7 +3953,7 @@
         <v>0.97</v>
       </c>
       <c r="S57" s="1">
-        <v>1.1700000000000002</v>
+        <v>1.17</v>
       </c>
       <c r="T57" s="1">
         <v>-1.23</v>
@@ -3970,18 +3962,18 @@
         <v>-1.03</v>
       </c>
       <c r="V57" s="1"/>
-      <c r="W57" s="9"/>
-      <c r="X57" s="9"/>
-      <c r="Y57" s="9"/>
-      <c r="Z57" s="9"/>
+      <c r="W57" s="1"/>
+      <c r="X57" s="1"/>
+      <c r="Y57" s="1"/>
+      <c r="Z57" s="1"/>
       <c r="AB57" s="1"/>
     </row>
-    <row r="58" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:28" x14ac:dyDescent="0.35">
       <c r="B58" s="1">
         <v>0.60000000000000009</v>
       </c>
       <c r="C58" s="1">
-        <v>1.0999999999999999</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="D58" s="1">
         <v>-0.39999999999999991</v>
@@ -4005,7 +3997,7 @@
         <v>-1.5</v>
       </c>
       <c r="K58" s="1">
-        <v>-1.0000000000000002</v>
+        <v>-1</v>
       </c>
       <c r="L58" s="1">
         <v>0.88</v>
@@ -4029,22 +4021,22 @@
         <v>0.98</v>
       </c>
       <c r="S58" s="1">
-        <v>1.1800000000000002</v>
+        <v>1.18</v>
       </c>
       <c r="T58" s="1">
-        <v>-1.2200000000000002</v>
+        <v>-1.22</v>
       </c>
       <c r="U58" s="1">
         <v>-1.02</v>
       </c>
       <c r="V58" s="1"/>
-      <c r="W58" s="9"/>
-      <c r="X58" s="9"/>
-      <c r="Y58" s="9"/>
-      <c r="Z58" s="9"/>
+      <c r="W58" s="1"/>
+      <c r="X58" s="1"/>
+      <c r="Y58" s="1"/>
+      <c r="Z58" s="1"/>
       <c r="AB58" s="1"/>
     </row>
-    <row r="59" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:28" x14ac:dyDescent="0.35">
       <c r="B59" s="1">
         <v>0.8</v>
       </c>
@@ -4052,10 +4044,10 @@
         <v>1.2</v>
       </c>
       <c r="D59" s="1">
-        <v>-0.19999999999999996</v>
+        <v>-0.2</v>
       </c>
       <c r="E59" s="1">
-        <v>0.19999999999999996</v>
+        <v>0.2</v>
       </c>
       <c r="F59" s="1">
         <v>-1.2</v>
@@ -4082,13 +4074,13 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="N59" s="1">
-        <v>-0.10999999999999999</v>
+        <v>-0.11</v>
       </c>
       <c r="O59" s="1">
         <v>9.000000000000008E-2</v>
       </c>
       <c r="P59" s="1">
-        <v>-1.1099999999999999</v>
+        <v>-1.1100000000000001</v>
       </c>
       <c r="Q59" s="1">
         <v>-0.90999999999999992</v>
@@ -4097,7 +4089,7 @@
         <v>0.99</v>
       </c>
       <c r="S59" s="1">
-        <v>1.1900000000000002</v>
+        <v>1.19</v>
       </c>
       <c r="T59" s="1">
         <v>-1.21</v>
@@ -4106,13 +4098,13 @@
         <v>-1.01</v>
       </c>
       <c r="V59" s="1"/>
-      <c r="W59" s="9"/>
-      <c r="X59" s="9"/>
-      <c r="Y59" s="9"/>
-      <c r="Z59" s="9"/>
+      <c r="W59" s="1"/>
+      <c r="X59" s="1"/>
+      <c r="Y59" s="1"/>
+      <c r="Z59" s="1"/>
       <c r="AB59" s="1"/>
     </row>
-    <row r="60" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:28" x14ac:dyDescent="0.35">
       <c r="B60" s="1">
         <v>1</v>
       </c>
@@ -4123,7 +4115,7 @@
         <v>0</v>
       </c>
       <c r="E60" s="1">
-        <v>0.30000000000000004</v>
+        <v>0.3</v>
       </c>
       <c r="F60" s="1">
         <v>-1</v>
@@ -4135,7 +4127,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="I60" s="1">
-        <v>1.4000000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="J60" s="1">
         <v>-1.1000000000000001</v>
@@ -4156,7 +4148,7 @@
         <v>0.1100000000000001</v>
       </c>
       <c r="P60" s="1">
-        <v>-1.0899999999999999</v>
+        <v>-1.0900000000000001</v>
       </c>
       <c r="Q60" s="1">
         <v>-0.8899999999999999</v>
@@ -4165,7 +4157,7 @@
         <v>1.01</v>
       </c>
       <c r="S60" s="1">
-        <v>1.2100000000000002</v>
+        <v>1.21</v>
       </c>
       <c r="T60" s="1">
         <v>-1.19</v>
@@ -4174,24 +4166,24 @@
         <v>-0.98999999999999988</v>
       </c>
       <c r="V60" s="1"/>
-      <c r="W60" s="9"/>
-      <c r="X60" s="9"/>
-      <c r="Y60" s="9"/>
-      <c r="Z60" s="9"/>
+      <c r="W60" s="1"/>
+      <c r="X60" s="1"/>
+      <c r="Y60" s="1"/>
+      <c r="Z60" s="1"/>
       <c r="AB60" s="1"/>
     </row>
-    <row r="61" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:28" x14ac:dyDescent="0.35">
       <c r="B61" s="1">
         <v>1.2</v>
       </c>
       <c r="C61" s="1">
-        <v>1.4000000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="D61" s="1">
-        <v>0.19999999999999996</v>
+        <v>0.2</v>
       </c>
       <c r="E61" s="1">
-        <v>0.40000000000000013</v>
+        <v>0.40000000000000008</v>
       </c>
       <c r="F61" s="1">
         <v>-0.8</v>
@@ -4203,7 +4195,7 @@
         <v>1.3</v>
       </c>
       <c r="I61" s="1">
-        <v>1.5000000000000002</v>
+        <v>1.5</v>
       </c>
       <c r="J61" s="1">
         <v>-0.9</v>
@@ -4233,27 +4225,27 @@
         <v>1.02</v>
       </c>
       <c r="S61" s="1">
-        <v>1.2200000000000002</v>
+        <v>1.22</v>
       </c>
       <c r="T61" s="1">
-        <v>-1.1800000000000002</v>
+        <v>-1.18</v>
       </c>
       <c r="U61" s="1">
         <v>-0.97999999999999987</v>
       </c>
       <c r="V61" s="1"/>
-      <c r="W61" s="9"/>
-      <c r="X61" s="9"/>
-      <c r="Y61" s="9"/>
-      <c r="Z61" s="9"/>
+      <c r="W61" s="1"/>
+      <c r="X61" s="1"/>
+      <c r="Y61" s="1"/>
+      <c r="Z61" s="1"/>
       <c r="AB61" s="1"/>
     </row>
-    <row r="62" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:28" x14ac:dyDescent="0.35">
       <c r="B62" s="1">
         <v>1.4</v>
       </c>
       <c r="C62" s="1">
-        <v>1.5000000000000002</v>
+        <v>1.5</v>
       </c>
       <c r="D62" s="1">
         <v>0.39999999999999991</v>
@@ -4271,7 +4263,7 @@
         <v>1.5</v>
       </c>
       <c r="I62" s="1">
-        <v>1.6000000000000003</v>
+        <v>1.6</v>
       </c>
       <c r="J62" s="1">
         <v>-0.70000000000000007</v>
@@ -4283,16 +4275,16 @@
         <v>0.93</v>
       </c>
       <c r="M62" s="1">
-        <v>1.1300000000000001</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="N62" s="1">
         <v>-6.9999999999999951E-2</v>
       </c>
       <c r="O62" s="1">
-        <v>0.13000000000000012</v>
+        <v>0.13000000000000009</v>
       </c>
       <c r="P62" s="1">
-        <v>-1.0699999999999998</v>
+        <v>-1.07</v>
       </c>
       <c r="Q62" s="1">
         <v>-0.86999999999999988</v>
@@ -4301,7 +4293,7 @@
         <v>1.03</v>
       </c>
       <c r="S62" s="1">
-        <v>1.2300000000000002</v>
+        <v>1.23</v>
       </c>
       <c r="T62" s="1">
         <v>-1.17</v>
@@ -4310,15 +4302,15 @@
         <v>-0.96999999999999986</v>
       </c>
       <c r="V62" s="1"/>
-      <c r="W62" s="9"/>
-      <c r="X62" s="9"/>
-      <c r="Y62" s="9"/>
-      <c r="Z62" s="9"/>
+      <c r="W62" s="1"/>
+      <c r="X62" s="1"/>
+      <c r="Y62" s="1"/>
+      <c r="Z62" s="1"/>
       <c r="AB62" s="1"/>
     </row>
-    <row r="63" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:28" x14ac:dyDescent="0.35">
       <c r="B63" s="1">
-        <v>1.5999999999999999</v>
+        <v>1.6</v>
       </c>
       <c r="C63" s="1">
         <v>0.5</v>
@@ -4330,7 +4322,7 @@
         <v>-0.5</v>
       </c>
       <c r="F63" s="1">
-        <v>-0.40000000000000013</v>
+        <v>-0.40000000000000008</v>
       </c>
       <c r="G63" s="1">
         <v>-1.5</v>
@@ -4351,13 +4343,13 @@
         <v>0.94000000000000006</v>
       </c>
       <c r="M63" s="1">
-        <v>1.1400000000000001</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="N63" s="1">
         <v>-5.9999999999999942E-2</v>
       </c>
       <c r="O63" s="1">
-        <v>0.14000000000000012</v>
+        <v>0.1400000000000001</v>
       </c>
       <c r="P63" s="1">
         <v>-1.06</v>
@@ -4369,24 +4361,24 @@
         <v>1.04</v>
       </c>
       <c r="S63" s="1">
-        <v>1.2400000000000002</v>
+        <v>1.24</v>
       </c>
       <c r="T63" s="1">
-        <v>-1.1600000000000001</v>
+        <v>-1.1599999999999999</v>
       </c>
       <c r="U63" s="1">
         <v>-0.95999999999999985</v>
       </c>
       <c r="V63" s="1"/>
-      <c r="W63" s="9"/>
-      <c r="X63" s="9"/>
-      <c r="Y63" s="9"/>
-      <c r="Z63" s="9"/>
+      <c r="W63" s="1"/>
+      <c r="X63" s="1"/>
+      <c r="Y63" s="1"/>
+      <c r="Z63" s="1"/>
       <c r="AB63" s="1"/>
     </row>
-    <row r="64" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:28" x14ac:dyDescent="0.35">
       <c r="B64" s="1">
-        <v>1.7999999999999998</v>
+        <v>1.8</v>
       </c>
       <c r="C64" s="1">
         <v>0.6</v>
@@ -4398,7 +4390,7 @@
         <v>-0.4</v>
       </c>
       <c r="F64" s="1">
-        <v>-0.20000000000000018</v>
+        <v>-0.20000000000000021</v>
       </c>
       <c r="G64" s="1">
         <v>-1.4</v>
@@ -4410,7 +4402,7 @@
         <v>0.7</v>
       </c>
       <c r="J64" s="1">
-        <v>-0.30000000000000016</v>
+        <v>-0.30000000000000021</v>
       </c>
       <c r="K64" s="1">
         <v>-1.5</v>
@@ -4419,16 +4411,16 @@
         <v>0.95000000000000007</v>
       </c>
       <c r="M64" s="1">
-        <v>1.1500000000000001</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="N64" s="1">
         <v>-4.9999999999999933E-2</v>
       </c>
       <c r="O64" s="1">
-        <v>0.15000000000000013</v>
+        <v>0.15000000000000011</v>
       </c>
       <c r="P64" s="1">
-        <v>-1.0499999999999998</v>
+        <v>-1.05</v>
       </c>
       <c r="Q64" s="1">
         <v>-0.84999999999999987</v>
@@ -4437,7 +4429,7 @@
         <v>1.05</v>
       </c>
       <c r="S64" s="1">
-        <v>1.2500000000000002</v>
+        <v>1.25</v>
       </c>
       <c r="T64" s="1">
         <v>-1.1499999999999999</v>
@@ -4446,15 +4438,15 @@
         <v>-0.94999999999999984</v>
       </c>
       <c r="V64" s="1"/>
-      <c r="W64" s="9"/>
-      <c r="X64" s="9"/>
-      <c r="Y64" s="9"/>
-      <c r="Z64" s="9"/>
+      <c r="W64" s="1"/>
+      <c r="X64" s="1"/>
+      <c r="Y64" s="1"/>
+      <c r="Z64" s="1"/>
       <c r="AB64" s="1"/>
     </row>
-    <row r="65" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:28" x14ac:dyDescent="0.35">
       <c r="B65" s="1">
-        <v>1.9999999999999998</v>
+        <v>2</v>
       </c>
       <c r="C65" s="1">
         <v>0.7</v>
@@ -4463,7 +4455,7 @@
         <v>0.99999999999999978</v>
       </c>
       <c r="E65" s="1">
-        <v>-0.30000000000000004</v>
+        <v>-0.3</v>
       </c>
       <c r="F65" s="1">
         <v>0</v>
@@ -4472,7 +4464,7 @@
         <v>-1.3</v>
       </c>
       <c r="H65" s="1">
-        <v>2.0999999999999996</v>
+        <v>2.1</v>
       </c>
       <c r="I65" s="1">
         <v>0.79999999999999993</v>
@@ -4481,7 +4473,7 @@
         <v>-0.1</v>
       </c>
       <c r="K65" s="1">
-        <v>-1.4000000000000001</v>
+        <v>-1.4</v>
       </c>
       <c r="L65" s="1">
         <v>2</v>
@@ -4514,21 +4506,15 @@
         <v>-2.1</v>
       </c>
       <c r="V65" s="1"/>
-      <c r="W65" s="9"/>
-      <c r="X65" s="9"/>
-      <c r="Y65" s="9"/>
-      <c r="Z65" s="9"/>
+      <c r="W65" s="1"/>
+      <c r="X65" s="1"/>
+      <c r="Y65" s="1"/>
+      <c r="Z65" s="1"/>
       <c r="AB65" s="1"/>
     </row>
-    <row r="66" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="W66" s="10"/>
-      <c r="X66" s="10"/>
-      <c r="Y66" s="10"/>
-      <c r="Z66" s="10"/>
-    </row>
-    <row r="67" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B67" s="1">
         <f t="shared" ref="B67:U67" si="12">AVERAGE(B55:B65)</f>
@@ -4536,7 +4522,7 @@
       </c>
       <c r="C67" s="1">
         <f t="shared" si="12"/>
-        <v>1</v>
+        <v>0.99999999999999989</v>
       </c>
       <c r="D67" s="1">
         <f t="shared" si="12"/>
@@ -4548,7 +4534,7 @@
       </c>
       <c r="F67" s="1">
         <f t="shared" si="12"/>
-        <v>-1</v>
+        <v>-1.0000000000000002</v>
       </c>
       <c r="G67" s="1">
         <f t="shared" si="12"/>
@@ -4568,7 +4554,7 @@
       </c>
       <c r="K67" s="1">
         <f t="shared" si="12"/>
-        <v>-1.1000000000000001</v>
+        <v>-1.0999999999999999</v>
       </c>
       <c r="L67" s="1">
         <f t="shared" si="12"/>
@@ -4588,7 +4574,7 @@
       </c>
       <c r="P67" s="1">
         <f t="shared" si="12"/>
-        <v>-1</v>
+        <v>-1.0000000000000002</v>
       </c>
       <c r="Q67" s="1">
         <f t="shared" si="12"/>
@@ -4600,7 +4586,7 @@
       </c>
       <c r="S67" s="1">
         <f t="shared" si="12"/>
-        <v>1.1000000000000001</v>
+        <v>1.0999999999999999</v>
       </c>
       <c r="T67" s="1">
         <f t="shared" si="12"/>
@@ -4610,22 +4596,22 @@
         <f t="shared" si="12"/>
         <v>-1.0999999999999999</v>
       </c>
-      <c r="W67" s="9"/>
-      <c r="X67" s="9"/>
-      <c r="Y67" s="9"/>
-      <c r="Z67" s="9"/>
-    </row>
-    <row r="68" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="W67" s="1"/>
+      <c r="X67" s="1"/>
+      <c r="Y67" s="1"/>
+      <c r="Z67" s="1"/>
+    </row>
+    <row r="68" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A68" s="3" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B68" s="4">
         <f t="shared" ref="B68:U68" si="13">_xlfn.STDEV.P(B55:B65)</f>
-        <v>0.63245553203367566</v>
+        <v>0.63245553203367588</v>
       </c>
       <c r="C68" s="4">
         <f t="shared" si="13"/>
-        <v>0.31622776601683783</v>
+        <v>0.31622776601683844</v>
       </c>
       <c r="D68" s="4">
         <f t="shared" si="13"/>
@@ -4637,7 +4623,7 @@
       </c>
       <c r="F68" s="4">
         <f t="shared" si="13"/>
-        <v>0.63245553203367588</v>
+        <v>0.63245553203367566</v>
       </c>
       <c r="G68" s="4">
         <f t="shared" si="13"/>
@@ -4677,7 +4663,7 @@
       </c>
       <c r="P68" s="1">
         <f t="shared" si="13"/>
-        <v>0.31780497164141375</v>
+        <v>0.31780497164141358</v>
       </c>
       <c r="Q68" s="1">
         <f t="shared" si="13"/>
@@ -4699,22 +4685,22 @@
         <f t="shared" si="13"/>
         <v>0.31780497164141486</v>
       </c>
-      <c r="W68" s="9"/>
-      <c r="X68" s="9"/>
-      <c r="Y68" s="9"/>
-      <c r="Z68" s="9"/>
-    </row>
-    <row r="69" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="W68" s="1"/>
+      <c r="X68" s="1"/>
+      <c r="Y68" s="1"/>
+      <c r="Z68" s="1"/>
+    </row>
+    <row r="69" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B69" s="1">
         <f t="shared" ref="B69:U69" si="14">_xlfn.SKEW.P(B55:B65)</f>
-        <v>-4.0371746350005691E-16</v>
+        <v>0</v>
       </c>
       <c r="C69" s="1">
         <f t="shared" si="14"/>
-        <v>5.6520444890007968E-16</v>
+        <v>8.679925465251224E-16</v>
       </c>
       <c r="D69" s="1">
         <f t="shared" si="14"/>
@@ -4722,11 +4708,11 @@
       </c>
       <c r="E69" s="1">
         <f t="shared" si="14"/>
-        <v>5.6520444890007968E-16</v>
+        <v>4.6427508302506544E-16</v>
       </c>
       <c r="F69" s="1">
         <f t="shared" si="14"/>
-        <v>-2.8260222445003984E-16</v>
+        <v>7.6706318065010816E-16</v>
       </c>
       <c r="G69" s="1">
         <f t="shared" si="14"/>
@@ -4734,19 +4720,19 @@
       </c>
       <c r="H69" s="1">
         <f t="shared" si="14"/>
-        <v>1.2111523905001707E-16</v>
+        <v>5.2483270255007403E-16</v>
       </c>
       <c r="I69" s="1">
         <f t="shared" si="14"/>
-        <v>2.1397025565503018E-15</v>
+        <v>1.1909665173251679E-15</v>
       </c>
       <c r="J69" s="1">
         <f t="shared" si="14"/>
-        <v>-8.4780667335011958E-16</v>
+        <v>-7.2669143430010251E-16</v>
       </c>
       <c r="K69" s="1">
         <f t="shared" si="14"/>
-        <v>1.2313382636751737E-15</v>
+        <v>-5.2483270255007403E-16</v>
       </c>
       <c r="L69" s="4">
         <f t="shared" si="14"/>
@@ -4766,7 +4752,7 @@
       </c>
       <c r="P69" s="4">
         <f t="shared" si="14"/>
-        <v>2.7945403348921518</v>
+        <v>2.7945403348921536</v>
       </c>
       <c r="Q69" s="4">
         <f t="shared" si="14"/>
@@ -4778,7 +4764,7 @@
       </c>
       <c r="S69" s="4">
         <f t="shared" si="14"/>
-        <v>-2.7945403348921518</v>
+        <v>-2.7945403348921505</v>
       </c>
       <c r="T69" s="4">
         <f t="shared" si="14"/>
@@ -4788,22 +4774,22 @@
         <f t="shared" si="14"/>
         <v>-2.7945403348921518</v>
       </c>
-      <c r="W69" s="9"/>
-      <c r="X69" s="9"/>
-      <c r="Y69" s="9"/>
-      <c r="Z69" s="9"/>
-    </row>
-    <row r="70" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="W69" s="1"/>
+      <c r="X69" s="1"/>
+      <c r="Y69" s="1"/>
+      <c r="Z69" s="1"/>
+    </row>
+    <row r="70" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B70" s="1">
         <f t="shared" ref="B70:U70" si="15">KURT(B55:B65)</f>
-        <v>-1.2000000000000011</v>
+        <v>-1.2000000000000015</v>
       </c>
       <c r="C70" s="1">
         <f t="shared" si="15"/>
-        <v>-1.1999999999999988</v>
+        <v>-1.200000000000002</v>
       </c>
       <c r="D70" s="1">
         <f t="shared" si="15"/>
@@ -4815,19 +4801,19 @@
       </c>
       <c r="F70" s="1">
         <f t="shared" si="15"/>
-        <v>-1.200000000000002</v>
+        <v>-1.2000000000000011</v>
       </c>
       <c r="G70" s="1">
         <f t="shared" si="15"/>
-        <v>-1.1999999999999988</v>
+        <v>-1.1999999999999997</v>
       </c>
       <c r="H70" s="1">
         <f t="shared" si="15"/>
-        <v>-1.200000000000002</v>
+        <v>-1.2000000000000015</v>
       </c>
       <c r="I70" s="1">
         <f t="shared" si="15"/>
-        <v>-1.2000000000000002</v>
+        <v>-1.2000000000000011</v>
       </c>
       <c r="J70" s="1">
         <f t="shared" si="15"/>
@@ -4835,7 +4821,7 @@
       </c>
       <c r="K70" s="1">
         <f t="shared" si="15"/>
-        <v>-1.2000000000000002</v>
+        <v>-1.2000000000000011</v>
       </c>
       <c r="L70" s="1">
         <f t="shared" si="15"/>
@@ -4855,7 +4841,7 @@
       </c>
       <c r="P70" s="1">
         <f t="shared" si="15"/>
-        <v>10.711250530993684</v>
+        <v>10.711250530993702</v>
       </c>
       <c r="Q70" s="1">
         <f t="shared" si="15"/>
@@ -4877,12 +4863,12 @@
         <f t="shared" si="15"/>
         <v>10.711250530993691</v>
       </c>
-      <c r="W70" s="9"/>
-      <c r="X70" s="9"/>
-      <c r="Y70" s="9"/>
-      <c r="Z70" s="9"/>
-    </row>
-    <row r="71" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="W70" s="1"/>
+      <c r="X70" s="1"/>
+      <c r="Y70" s="1"/>
+      <c r="Z70" s="1"/>
+    </row>
+    <row r="71" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>14</v>
       </c>
@@ -4936,7 +4922,7 @@
       </c>
       <c r="N71" s="1">
         <f t="shared" si="16"/>
-        <v>-0.15000000000000002</v>
+        <v>-0.15</v>
       </c>
       <c r="O71" s="1">
         <f t="shared" si="16"/>
@@ -4966,22 +4952,22 @@
         <f t="shared" si="16"/>
         <v>-2.1</v>
       </c>
-      <c r="W71" s="9"/>
-      <c r="X71" s="9"/>
-      <c r="Y71" s="9"/>
-      <c r="Z71" s="9"/>
-    </row>
-    <row r="72" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="W71" s="1"/>
+      <c r="X71" s="1"/>
+      <c r="Y71" s="1"/>
+      <c r="Z71" s="1"/>
+    </row>
+    <row r="72" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>15</v>
       </c>
       <c r="B72" s="1">
         <f t="shared" ref="B72:U72" si="17">MAX(B55:B65)</f>
-        <v>1.9999999999999998</v>
+        <v>2</v>
       </c>
       <c r="C72" s="1">
         <f t="shared" si="17"/>
-        <v>1.5000000000000002</v>
+        <v>1.5</v>
       </c>
       <c r="D72" s="1">
         <f t="shared" si="17"/>
@@ -5001,11 +4987,11 @@
       </c>
       <c r="H72" s="1">
         <f t="shared" si="17"/>
-        <v>2.0999999999999996</v>
+        <v>2.1</v>
       </c>
       <c r="I72" s="1">
         <f t="shared" si="17"/>
-        <v>1.6000000000000003</v>
+        <v>1.6</v>
       </c>
       <c r="J72" s="1">
         <f t="shared" si="17"/>
@@ -5021,7 +5007,7 @@
       </c>
       <c r="M72" s="1">
         <f t="shared" si="17"/>
-        <v>1.1500000000000001</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="N72" s="1">
         <f t="shared" si="17"/>
@@ -5029,7 +5015,7 @@
       </c>
       <c r="O72" s="1">
         <f t="shared" si="17"/>
-        <v>0.15000000000000013</v>
+        <v>0.15000000000000011</v>
       </c>
       <c r="P72" s="1">
         <f t="shared" si="17"/>
@@ -5045,7 +5031,7 @@
       </c>
       <c r="S72" s="1">
         <f t="shared" si="17"/>
-        <v>1.2500000000000002</v>
+        <v>1.25</v>
       </c>
       <c r="T72" s="1">
         <f t="shared" si="17"/>
@@ -5055,34 +5041,34 @@
         <f t="shared" si="17"/>
         <v>-0.94999999999999984</v>
       </c>
-      <c r="W72" s="9"/>
-      <c r="X72" s="9"/>
-      <c r="Y72" s="9"/>
-      <c r="Z72" s="9"/>
-    </row>
-    <row r="73" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="W72" s="1"/>
+      <c r="X72" s="1"/>
+      <c r="Y72" s="1"/>
+      <c r="Z72" s="1"/>
+    </row>
+    <row r="73" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>16</v>
       </c>
       <c r="B73" s="1">
         <f>CORREL(B55:B65,C55:C65)</f>
-        <v>-0.19999999999999976</v>
+        <v>-0.20000000000000004</v>
       </c>
       <c r="D73" s="1">
         <f>CORREL(D55:D65,E55:E65)</f>
-        <v>-0.19999999999999979</v>
+        <v>-0.19999999999999976</v>
       </c>
       <c r="F73" s="1">
         <f>CORREL(F55:F65,G55:G65)</f>
-        <v>-0.19999999999999973</v>
+        <v>-0.19999999999999982</v>
       </c>
       <c r="H73" s="1">
         <f>CORREL(H55:H65,I55:I65)</f>
-        <v>-0.19999999999999973</v>
+        <v>-0.19999999999999993</v>
       </c>
       <c r="J73" s="1">
         <f>CORREL(J55:J65,K55:K65)</f>
-        <v>-0.19999999999999965</v>
+        <v>-0.19999999999999979</v>
       </c>
       <c r="L73" s="1">
         <f>CORREL(L55:L65,M55:M65)</f>
@@ -5098,109 +5084,103 @@
       </c>
       <c r="R73" s="1">
         <f>CORREL(R55:R65,S55:S65)</f>
-        <v>-0.98019801980198029</v>
+        <v>-0.98019801980198007</v>
       </c>
       <c r="T73" s="1">
         <f>CORREL(T55:T65,U55:U65)</f>
         <v>-0.98019801980197996</v>
       </c>
-      <c r="W73" s="9"/>
-      <c r="X73" s="10"/>
-      <c r="Y73" s="9"/>
-      <c r="Z73" s="10"/>
-    </row>
-    <row r="74" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="W73" s="1"/>
+      <c r="Y73" s="1"/>
+    </row>
+    <row r="74" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A74" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B74" s="3" cm="1">
+      <c r="B74" s="3">
         <f t="array" ref="B74">SUMPRODUCT((B55:B65&gt;C55:C65)*1)</f>
         <v>3</v>
       </c>
-      <c r="C74" s="3" cm="1">
+      <c r="C74" s="3">
         <f t="array" ref="C74">SUMPRODUCT((B55:B65&lt;C55:C65)*1)</f>
         <v>8</v>
       </c>
-      <c r="D74" s="3" cm="1">
+      <c r="D74" s="3">
         <f t="array" ref="D74">SUMPRODUCT((D55:D65&gt;E55:E65)*1)</f>
         <v>3</v>
       </c>
-      <c r="E74" s="3" cm="1">
+      <c r="E74" s="3">
         <f t="array" ref="E74">SUMPRODUCT((D55:D65&lt;E55:E65)*1)</f>
         <v>8</v>
       </c>
-      <c r="F74" s="3" cm="1">
+      <c r="F74" s="3">
         <f t="array" ref="F74">SUMPRODUCT((F55:F65&gt;G55:G65)*1)</f>
         <v>3</v>
       </c>
-      <c r="G74" s="3" cm="1">
+      <c r="G74" s="3">
         <f t="array" ref="G74">SUMPRODUCT((F55:F65&lt;G55:G65)*1)</f>
         <v>8</v>
       </c>
-      <c r="H74" s="3" cm="1">
+      <c r="H74" s="3">
         <f t="array" ref="H74">SUMPRODUCT((H55:H65&gt;I55:I65)*1)</f>
         <v>3</v>
       </c>
-      <c r="I74" s="3" cm="1">
+      <c r="I74" s="3">
         <f t="array" ref="I74">SUMPRODUCT((H55:H65&lt;I55:I65)*1)</f>
         <v>8</v>
       </c>
-      <c r="J74" s="3" cm="1">
+      <c r="J74" s="3">
         <f t="array" ref="J74">SUMPRODUCT((J55:J65&gt;K55:K65)*1)</f>
         <v>3</v>
       </c>
-      <c r="K74" s="3" cm="1">
+      <c r="K74" s="3">
         <f t="array" ref="K74">SUMPRODUCT((J55:J65&lt;K55:K65)*1)</f>
         <v>8</v>
       </c>
-      <c r="L74" s="3" cm="1">
+      <c r="L74" s="3">
         <f t="array" ref="L74">SUMPRODUCT((L55:L65&gt;M55:M65)*1)</f>
         <v>1</v>
       </c>
-      <c r="M74" s="3" cm="1">
+      <c r="M74" s="3">
         <f t="array" ref="M74">SUMPRODUCT((L55:L65&lt;M55:M65)*1)</f>
         <v>10</v>
       </c>
-      <c r="N74" s="3" cm="1">
+      <c r="N74" s="3">
         <f t="array" ref="N74">SUMPRODUCT((N55:N65&gt;O55:O65)*1)</f>
         <v>1</v>
       </c>
-      <c r="O74" s="3" cm="1">
+      <c r="O74" s="3">
         <f t="array" ref="O74">SUMPRODUCT((N55:N65&lt;O55:O65)*1)</f>
         <v>10</v>
       </c>
-      <c r="P74" s="3" cm="1">
+      <c r="P74" s="3">
         <f t="array" ref="P74">SUMPRODUCT((P55:P65&gt;Q55:Q65)*1)</f>
         <v>1</v>
       </c>
-      <c r="Q74" s="3" cm="1">
+      <c r="Q74" s="3">
         <f t="array" ref="Q74">SUMPRODUCT((P55:P65&lt;Q55:Q65)*1)</f>
         <v>10</v>
       </c>
-      <c r="R74" s="3" cm="1">
+      <c r="R74" s="3">
         <f t="array" ref="R74">SUMPRODUCT((R55:R65&gt;S55:S65)*1)</f>
         <v>1</v>
       </c>
-      <c r="S74" s="3" cm="1">
+      <c r="S74" s="3">
         <f t="array" ref="S74">SUMPRODUCT((R55:R65&lt;S55:S65)*1)</f>
         <v>10</v>
       </c>
-      <c r="T74" s="3" cm="1">
+      <c r="T74" s="3">
         <f t="array" ref="T74">SUMPRODUCT((T55:T65&gt;U55:U65)*1)</f>
         <v>1</v>
       </c>
-      <c r="U74" s="3" cm="1">
+      <c r="U74" s="3">
         <f t="array" ref="U74">SUMPRODUCT((T55:T65&lt;U55:U65)*1)</f>
         <v>10</v>
       </c>
-      <c r="W74" s="10"/>
-      <c r="X74" s="10"/>
-      <c r="Y74" s="10"/>
-      <c r="Z74" s="10"/>
-    </row>
-    <row r="75" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="75" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A75" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B75" s="6" t="str">
         <f>IF(B74&gt;C74,"A",IF(C74&gt;B74,"B","Equal"))</f>
@@ -5242,12 +5222,10 @@
         <f>IF(T74&gt;U74,"A",IF(U74&gt;T74,"B","Equal"))</f>
         <v>B</v>
       </c>
-      <c r="W75" s="11"/>
-      <c r="X75" s="10"/>
-      <c r="Y75" s="11"/>
-      <c r="Z75" s="10"/>
-    </row>
-    <row r="76" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="W75" s="6"/>
+      <c r="Y75" s="6"/>
+    </row>
+    <row r="76" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>19</v>
       </c>
@@ -5291,60 +5269,56 @@
         <f>MAX(T74:U74)</f>
         <v>10</v>
       </c>
-      <c r="W76" s="10"/>
-      <c r="X76" s="10"/>
-      <c r="Y76" s="10"/>
-      <c r="Z76" s="10"/>
-    </row>
-    <row r="78" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A78" s="8" t="s">
+    </row>
+    <row r="78" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A78" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="80" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A80" s="2"/>
-      <c r="B80" s="7" t="s">
+      <c r="B80" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C80" s="12"/>
+      <c r="D80" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E80" s="12"/>
+      <c r="F80" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G80" s="12"/>
+      <c r="H80" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="I80" s="12"/>
+      <c r="J80" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="K80" s="12"/>
+      <c r="L80" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="M80" s="12"/>
+      <c r="N80" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="O80" s="12"/>
+      <c r="P80" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q80" s="12"/>
+      <c r="R80" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="S80" s="12"/>
+      <c r="T80" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C80" s="7"/>
-      <c r="D80" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E80" s="7"/>
-      <c r="F80" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G80" s="7"/>
-      <c r="H80" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="I80" s="7"/>
-      <c r="J80" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="K80" s="7"/>
-      <c r="L80" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="M80" s="7"/>
-      <c r="N80" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="O80" s="7"/>
-      <c r="P80" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q80" s="7"/>
-      <c r="R80" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="S80" s="7"/>
-      <c r="T80" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="U80" s="7"/>
-    </row>
-    <row r="81" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="U80" s="12"/>
+    </row>
+    <row r="81" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B81" s="1">
         <v>0.60000000000000009</v>
       </c>
@@ -5382,7 +5356,7 @@
         <v>0</v>
       </c>
       <c r="N81" s="1">
-        <v>-0.15000000000000002</v>
+        <v>-0.15</v>
       </c>
       <c r="O81" s="1">
         <v>-1</v>
@@ -5407,7 +5381,7 @@
       </c>
       <c r="V81" s="1"/>
     </row>
-    <row r="82" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B82" s="1">
         <v>0.8</v>
       </c>
@@ -5415,7 +5389,7 @@
         <v>0.6</v>
       </c>
       <c r="D82" s="1">
-        <v>-0.19999999999999996</v>
+        <v>-0.2</v>
       </c>
       <c r="E82" s="1">
         <v>-0.4</v>
@@ -5448,10 +5422,10 @@
         <v>-0.14000000000000001</v>
       </c>
       <c r="O82" s="1">
-        <v>5.0000000000000044E-2</v>
+        <v>5.0000000000000037E-2</v>
       </c>
       <c r="P82" s="1">
-        <v>-1.1400000000000001</v>
+        <v>-1.1399999999999999</v>
       </c>
       <c r="Q82" s="1">
         <v>-0.95</v>
@@ -5460,17 +5434,17 @@
         <v>0.96</v>
       </c>
       <c r="S82" s="1">
-        <v>1.1500000000000001</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="T82" s="1">
-        <v>-1.2400000000000002</v>
+        <v>-1.24</v>
       </c>
       <c r="U82" s="1">
         <v>-1.05</v>
       </c>
       <c r="V82" s="1"/>
     </row>
-    <row r="83" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B83" s="1">
         <v>1</v>
       </c>
@@ -5481,7 +5455,7 @@
         <v>0</v>
       </c>
       <c r="E83" s="1">
-        <v>-0.30000000000000004</v>
+        <v>-0.3</v>
       </c>
       <c r="F83" s="1">
         <v>-1</v>
@@ -5499,7 +5473,7 @@
         <v>-1.1000000000000001</v>
       </c>
       <c r="K83" s="1">
-        <v>-1.4000000000000001</v>
+        <v>-1.4</v>
       </c>
       <c r="L83" s="1">
         <v>0.87</v>
@@ -5523,7 +5497,7 @@
         <v>0.97</v>
       </c>
       <c r="S83" s="1">
-        <v>1.1600000000000001</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="T83" s="1">
         <v>-1.23</v>
@@ -5533,7 +5507,7 @@
       </c>
       <c r="V83" s="1"/>
     </row>
-    <row r="84" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B84" s="1">
         <v>1.2</v>
       </c>
@@ -5541,16 +5515,16 @@
         <v>0.79999999999999993</v>
       </c>
       <c r="D84" s="1">
-        <v>0.19999999999999996</v>
+        <v>0.2</v>
       </c>
       <c r="E84" s="1">
-        <v>-0.20000000000000007</v>
+        <v>-0.20000000000000009</v>
       </c>
       <c r="F84" s="1">
         <v>-0.8</v>
       </c>
       <c r="G84" s="1">
-        <v>-1.2000000000000002</v>
+        <v>-1.2</v>
       </c>
       <c r="H84" s="1">
         <v>1.3</v>
@@ -5562,7 +5536,7 @@
         <v>-0.9</v>
       </c>
       <c r="K84" s="1">
-        <v>-1.3000000000000003</v>
+        <v>-1.3</v>
       </c>
       <c r="L84" s="1">
         <v>0.88</v>
@@ -5586,17 +5560,17 @@
         <v>0.98</v>
       </c>
       <c r="S84" s="1">
-        <v>1.1700000000000002</v>
+        <v>1.17</v>
       </c>
       <c r="T84" s="1">
-        <v>-1.2200000000000002</v>
+        <v>-1.22</v>
       </c>
       <c r="U84" s="1">
         <v>-1.03</v>
       </c>
       <c r="V84" s="1"/>
     </row>
-    <row r="85" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B85" s="1">
         <v>1.4</v>
       </c>
@@ -5607,7 +5581,7 @@
         <v>0.39999999999999991</v>
       </c>
       <c r="E85" s="1">
-        <v>-0.10000000000000009</v>
+        <v>-0.1000000000000001</v>
       </c>
       <c r="F85" s="1">
         <v>-0.60000000000000009</v>
@@ -5625,7 +5599,7 @@
         <v>-0.70000000000000007</v>
       </c>
       <c r="K85" s="1">
-        <v>-1.2000000000000002</v>
+        <v>-1.2</v>
       </c>
       <c r="L85" s="1">
         <v>0.89</v>
@@ -5634,13 +5608,13 @@
         <v>1.08</v>
       </c>
       <c r="N85" s="1">
-        <v>-0.10999999999999999</v>
+        <v>-0.11</v>
       </c>
       <c r="O85" s="1">
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="P85" s="1">
-        <v>-1.1099999999999999</v>
+        <v>-1.1100000000000001</v>
       </c>
       <c r="Q85" s="1">
         <v>-0.91999999999999993</v>
@@ -5649,7 +5623,7 @@
         <v>0.99</v>
       </c>
       <c r="S85" s="1">
-        <v>1.1800000000000002</v>
+        <v>1.18</v>
       </c>
       <c r="T85" s="1">
         <v>-1.21</v>
@@ -5659,9 +5633,9 @@
       </c>
       <c r="V85" s="1"/>
     </row>
-    <row r="86" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B86" s="1">
-        <v>1.5999999999999999</v>
+        <v>1.6</v>
       </c>
       <c r="C86" s="1">
         <v>0.99999999999999989</v>
@@ -5673,7 +5647,7 @@
         <v>0</v>
       </c>
       <c r="F86" s="1">
-        <v>-0.40000000000000013</v>
+        <v>-0.40000000000000008</v>
       </c>
       <c r="G86" s="1">
         <v>-1</v>
@@ -5682,7 +5656,7 @@
         <v>1.7</v>
       </c>
       <c r="I86" s="1">
-        <v>1.0999999999999999</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="J86" s="1">
         <v>-0.50000000000000011</v>
@@ -5703,7 +5677,7 @@
         <v>9.000000000000008E-2</v>
       </c>
       <c r="P86" s="1">
-        <v>-1.0899999999999999</v>
+        <v>-1.0900000000000001</v>
       </c>
       <c r="Q86" s="1">
         <v>-0.90999999999999992</v>
@@ -5712,7 +5686,7 @@
         <v>1.01</v>
       </c>
       <c r="S86" s="1">
-        <v>1.1900000000000002</v>
+        <v>1.19</v>
       </c>
       <c r="T86" s="1">
         <v>-1.19</v>
@@ -5722,12 +5696,12 @@
       </c>
       <c r="V86" s="1"/>
     </row>
-    <row r="87" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B87" s="1">
-        <v>1.7999999999999998</v>
+        <v>1.8</v>
       </c>
       <c r="C87" s="1">
-        <v>1.0999999999999999</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="D87" s="1">
         <v>0.79999999999999982</v>
@@ -5736,7 +5710,7 @@
         <v>9.9999999999999867E-2</v>
       </c>
       <c r="F87" s="1">
-        <v>-0.20000000000000018</v>
+        <v>-0.20000000000000021</v>
       </c>
       <c r="G87" s="1">
         <v>-0.90000000000000013</v>
@@ -5748,10 +5722,10 @@
         <v>1.2</v>
       </c>
       <c r="J87" s="1">
-        <v>-0.30000000000000016</v>
+        <v>-0.30000000000000021</v>
       </c>
       <c r="K87" s="1">
-        <v>-1.0000000000000002</v>
+        <v>-1</v>
       </c>
       <c r="L87" s="1">
         <v>0.92</v>
@@ -5775,19 +5749,19 @@
         <v>1.02</v>
       </c>
       <c r="S87" s="1">
-        <v>1.2100000000000002</v>
+        <v>1.21</v>
       </c>
       <c r="T87" s="1">
-        <v>-1.1800000000000002</v>
+        <v>-1.18</v>
       </c>
       <c r="U87" s="1">
         <v>-0.98999999999999988</v>
       </c>
       <c r="V87" s="1"/>
     </row>
-    <row r="88" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B88" s="1">
-        <v>1.9999999999999998</v>
+        <v>2</v>
       </c>
       <c r="C88" s="1">
         <v>1.2</v>
@@ -5796,7 +5770,7 @@
         <v>0.99999999999999978</v>
       </c>
       <c r="E88" s="1">
-        <v>0.19999999999999996</v>
+        <v>0.2</v>
       </c>
       <c r="F88" s="1">
         <v>0</v>
@@ -5805,7 +5779,7 @@
         <v>-0.8</v>
       </c>
       <c r="H88" s="1">
-        <v>2.0999999999999996</v>
+        <v>2.1</v>
       </c>
       <c r="I88" s="1">
         <v>1.3</v>
@@ -5829,7 +5803,7 @@
         <v>0.12000000000000011</v>
       </c>
       <c r="P88" s="1">
-        <v>-1.0699999999999998</v>
+        <v>-1.07</v>
       </c>
       <c r="Q88" s="1">
         <v>-0.87999999999999989</v>
@@ -5838,7 +5812,7 @@
         <v>1.03</v>
       </c>
       <c r="S88" s="1">
-        <v>1.2200000000000002</v>
+        <v>1.22</v>
       </c>
       <c r="T88" s="1">
         <v>-1.17</v>
@@ -5848,7 +5822,7 @@
       </c>
       <c r="V88" s="1"/>
     </row>
-    <row r="89" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B89" s="1">
         <v>0</v>
       </c>
@@ -5859,7 +5833,7 @@
         <v>-1</v>
       </c>
       <c r="E89" s="1">
-        <v>0.30000000000000004</v>
+        <v>0.3</v>
       </c>
       <c r="F89" s="1">
         <v>-2</v>
@@ -5871,7 +5845,7 @@
         <v>0.1</v>
       </c>
       <c r="I89" s="1">
-        <v>1.4000000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="J89" s="1">
         <v>-2.1</v>
@@ -5883,13 +5857,13 @@
         <v>0.94000000000000006</v>
       </c>
       <c r="M89" s="1">
-        <v>1.1300000000000001</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="N89" s="1">
         <v>-5.9999999999999942E-2</v>
       </c>
       <c r="O89" s="1">
-        <v>0.13000000000000012</v>
+        <v>0.13000000000000009</v>
       </c>
       <c r="P89" s="1">
         <v>-1.06</v>
@@ -5901,28 +5875,28 @@
         <v>1.04</v>
       </c>
       <c r="S89" s="1">
-        <v>1.2300000000000002</v>
+        <v>1.23</v>
       </c>
       <c r="T89" s="1">
-        <v>-1.1600000000000001</v>
+        <v>-1.1599999999999999</v>
       </c>
       <c r="U89" s="1">
         <v>-0.96999999999999986</v>
       </c>
       <c r="V89" s="1"/>
     </row>
-    <row r="90" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B90" s="1">
         <v>0.2</v>
       </c>
       <c r="C90" s="1">
-        <v>1.4000000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="D90" s="1">
         <v>-0.8</v>
       </c>
       <c r="E90" s="1">
-        <v>0.40000000000000013</v>
+        <v>0.40000000000000008</v>
       </c>
       <c r="F90" s="1">
         <v>-1.8</v>
@@ -5931,13 +5905,13 @@
         <v>-0.59999999999999987</v>
       </c>
       <c r="H90" s="1">
-        <v>0.30000000000000004</v>
+        <v>0.3</v>
       </c>
       <c r="I90" s="1">
-        <v>1.5000000000000002</v>
+        <v>1.5</v>
       </c>
       <c r="J90" s="1">
-        <v>-1.9000000000000001</v>
+        <v>-1.9</v>
       </c>
       <c r="K90" s="1">
         <v>-0.69999999999999984</v>
@@ -5946,16 +5920,16 @@
         <v>0.95000000000000007</v>
       </c>
       <c r="M90" s="1">
-        <v>1.1400000000000001</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="N90" s="1">
         <v>-4.9999999999999933E-2</v>
       </c>
       <c r="O90" s="1">
-        <v>0.14000000000000012</v>
+        <v>0.1400000000000001</v>
       </c>
       <c r="P90" s="1">
-        <v>-1.0499999999999998</v>
+        <v>-1.05</v>
       </c>
       <c r="Q90" s="1">
         <v>-0.85999999999999988</v>
@@ -5964,7 +5938,7 @@
         <v>1.05</v>
       </c>
       <c r="S90" s="1">
-        <v>1.2400000000000002</v>
+        <v>1.24</v>
       </c>
       <c r="T90" s="1">
         <v>-1.1499999999999999</v>
@@ -5974,12 +5948,12 @@
       </c>
       <c r="V90" s="1"/>
     </row>
-    <row r="91" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B91" s="1">
         <v>0.4</v>
       </c>
       <c r="C91" s="1">
-        <v>1.5000000000000002</v>
+        <v>1.5</v>
       </c>
       <c r="D91" s="1">
         <v>-0.6</v>
@@ -5997,10 +5971,10 @@
         <v>0.5</v>
       </c>
       <c r="I91" s="1">
-        <v>1.6000000000000003</v>
+        <v>1.6</v>
       </c>
       <c r="J91" s="1">
-        <v>-1.7000000000000002</v>
+        <v>-1.7</v>
       </c>
       <c r="K91" s="1">
         <v>-0.59999999999999976</v>
@@ -6009,13 +5983,13 @@
         <v>2</v>
       </c>
       <c r="M91" s="1">
-        <v>1.1500000000000001</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="N91" s="1">
         <v>1</v>
       </c>
       <c r="O91" s="1">
-        <v>0.15000000000000013</v>
+        <v>0.15000000000000011</v>
       </c>
       <c r="P91" s="1">
         <v>0</v>
@@ -6027,7 +6001,7 @@
         <v>2.1</v>
       </c>
       <c r="S91" s="1">
-        <v>1.2500000000000002</v>
+        <v>1.25</v>
       </c>
       <c r="T91" s="1">
         <v>-0.1</v>
@@ -6037,13 +6011,13 @@
       </c>
       <c r="V91" s="1"/>
     </row>
-    <row r="93" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B93" s="1">
         <f t="shared" ref="B93:U93" si="18">AVERAGE(B81:B91)</f>
-        <v>0.99999999999999989</v>
+        <v>1</v>
       </c>
       <c r="C93" s="1">
         <f t="shared" si="18"/>
@@ -6075,11 +6049,11 @@
       </c>
       <c r="J93" s="1">
         <f t="shared" si="18"/>
-        <v>-1.1000000000000001</v>
+        <v>-1.0999999999999999</v>
       </c>
       <c r="K93" s="1">
         <f t="shared" si="18"/>
-        <v>-1.1000000000000001</v>
+        <v>-1.0999999999999999</v>
       </c>
       <c r="L93" s="1">
         <f t="shared" si="18"/>
@@ -6095,11 +6069,11 @@
       </c>
       <c r="O93" s="1">
         <f t="shared" si="18"/>
-        <v>8.0743492700011387E-17</v>
+        <v>7.5697024406260668E-17</v>
       </c>
       <c r="P93" s="1">
         <f t="shared" si="18"/>
-        <v>-1</v>
+        <v>-1.0000000000000002</v>
       </c>
       <c r="Q93" s="1">
         <f t="shared" si="18"/>
@@ -6111,7 +6085,7 @@
       </c>
       <c r="S93" s="1">
         <f t="shared" si="18"/>
-        <v>1.1000000000000001</v>
+        <v>1.0999999999999999</v>
       </c>
       <c r="T93" s="1">
         <f t="shared" si="18"/>
@@ -6122,17 +6096,17 @@
         <v>-1.0999999999999999</v>
       </c>
     </row>
-    <row r="94" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A94" s="3" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B94" s="4">
         <f t="shared" ref="B94:U94" si="19">_xlfn.STDEV.P(B81:B91)</f>
-        <v>0.63245553203367599</v>
+        <v>0.63245553203367566</v>
       </c>
       <c r="C94" s="4">
         <f t="shared" si="19"/>
-        <v>0.31622776601683822</v>
+        <v>0.31622776601683783</v>
       </c>
       <c r="D94" s="4">
         <f t="shared" si="19"/>
@@ -6156,11 +6130,11 @@
       </c>
       <c r="I94" s="4">
         <f t="shared" si="19"/>
-        <v>0.31622776601683822</v>
+        <v>0.31622776601683783</v>
       </c>
       <c r="J94" s="4">
         <f t="shared" si="19"/>
-        <v>0.63245553203367566</v>
+        <v>0.63245553203367588</v>
       </c>
       <c r="K94" s="4">
         <f t="shared" si="19"/>
@@ -6180,11 +6154,11 @@
       </c>
       <c r="O94" s="1">
         <f t="shared" si="19"/>
-        <v>0.31780497164141408</v>
+        <v>0.31780497164141402</v>
       </c>
       <c r="P94" s="1">
         <f t="shared" si="19"/>
-        <v>0.31780497164141375</v>
+        <v>0.31780497164141358</v>
       </c>
       <c r="Q94" s="1">
         <f t="shared" si="19"/>
@@ -6207,17 +6181,17 @@
         <v>0.31780497164141375</v>
       </c>
     </row>
-    <row r="95" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B95" s="1">
         <f t="shared" ref="B95:U95" si="20">_xlfn.SKEW.P(B81:B91)</f>
-        <v>2.0185873175002846E-16</v>
+        <v>0</v>
       </c>
       <c r="C95" s="1">
         <f t="shared" si="20"/>
-        <v>6.0557619525008534E-16</v>
+        <v>-2.0185873175002846E-16</v>
       </c>
       <c r="D95" s="1">
         <f t="shared" si="20"/>
@@ -6225,7 +6199,7 @@
       </c>
       <c r="E95" s="1">
         <f t="shared" si="20"/>
-        <v>6.0557619525008534E-16</v>
+        <v>5.2483270255007403E-16</v>
       </c>
       <c r="F95" s="1">
         <f t="shared" si="20"/>
@@ -6233,23 +6207,23 @@
       </c>
       <c r="G95" s="1">
         <f t="shared" si="20"/>
-        <v>7.6706318065010816E-16</v>
+        <v>8.4780667335011958E-16</v>
       </c>
       <c r="H95" s="1">
         <f t="shared" si="20"/>
-        <v>2.0185873175002846E-16</v>
+        <v>6.6613381477509392E-16</v>
       </c>
       <c r="I95" s="1">
         <f t="shared" si="20"/>
-        <v>2.2204460492503131E-15</v>
+        <v>1.170780644150165E-15</v>
       </c>
       <c r="J95" s="1">
         <f t="shared" si="20"/>
-        <v>-1.1102230246251565E-16</v>
+        <v>-7.9734199041261241E-16</v>
       </c>
       <c r="K95" s="1">
         <f t="shared" si="20"/>
-        <v>1.2111523905001707E-15</v>
+        <v>-5.2483270255007403E-16</v>
       </c>
       <c r="L95" s="4">
         <f t="shared" si="20"/>
@@ -6265,11 +6239,11 @@
       </c>
       <c r="O95" s="4">
         <f t="shared" si="20"/>
-        <v>-2.7945403348921531</v>
+        <v>-2.7945403348921536</v>
       </c>
       <c r="P95" s="4">
         <f t="shared" si="20"/>
-        <v>2.7945403348921518</v>
+        <v>2.7945403348921536</v>
       </c>
       <c r="Q95" s="4">
         <f t="shared" si="20"/>
@@ -6292,13 +6266,13 @@
         <v>-2.794540334892154</v>
       </c>
     </row>
-    <row r="96" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B96" s="1">
         <f t="shared" ref="B96:U96" si="21">KURT(B81:B91)</f>
-        <v>-1.1999999999999988</v>
+        <v>-1.2000000000000011</v>
       </c>
       <c r="C96" s="1">
         <f t="shared" si="21"/>
@@ -6310,7 +6284,7 @@
       </c>
       <c r="E96" s="1">
         <f t="shared" si="21"/>
-        <v>-1.200000000000002</v>
+        <v>-1.1999999999999997</v>
       </c>
       <c r="F96" s="1">
         <f t="shared" si="21"/>
@@ -6318,11 +6292,11 @@
       </c>
       <c r="G96" s="1">
         <f t="shared" si="21"/>
-        <v>-1.200000000000002</v>
+        <v>-1.1999999999999997</v>
       </c>
       <c r="H96" s="1">
         <f t="shared" si="21"/>
-        <v>-1.1999999999999997</v>
+        <v>-1.2000000000000002</v>
       </c>
       <c r="I96" s="1">
         <f t="shared" si="21"/>
@@ -6330,11 +6304,11 @@
       </c>
       <c r="J96" s="1">
         <f t="shared" si="21"/>
-        <v>-1.2000000000000015</v>
+        <v>-1.2000000000000011</v>
       </c>
       <c r="K96" s="1">
         <f t="shared" si="21"/>
-        <v>-1.2000000000000002</v>
+        <v>-1.2000000000000011</v>
       </c>
       <c r="L96" s="1">
         <f t="shared" si="21"/>
@@ -6354,7 +6328,7 @@
       </c>
       <c r="P96" s="1">
         <f t="shared" si="21"/>
-        <v>10.711250530993684</v>
+        <v>10.711250530993702</v>
       </c>
       <c r="Q96" s="1">
         <f t="shared" si="21"/>
@@ -6366,7 +6340,7 @@
       </c>
       <c r="S96" s="1">
         <f t="shared" si="21"/>
-        <v>10.711250530993688</v>
+        <v>10.711250530993695</v>
       </c>
       <c r="T96" s="1">
         <f t="shared" si="21"/>
@@ -6377,7 +6351,7 @@
         <v>10.711250530993706</v>
       </c>
     </row>
-    <row r="97" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>14</v>
       </c>
@@ -6431,7 +6405,7 @@
       </c>
       <c r="N97" s="1">
         <f t="shared" si="22"/>
-        <v>-0.15000000000000002</v>
+        <v>-0.15</v>
       </c>
       <c r="O97" s="1">
         <f t="shared" si="22"/>
@@ -6462,17 +6436,17 @@
         <v>-2.1</v>
       </c>
     </row>
-    <row r="98" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>15</v>
       </c>
       <c r="B98" s="1">
         <f t="shared" ref="B98:U98" si="23">MAX(B81:B91)</f>
-        <v>1.9999999999999998</v>
+        <v>2</v>
       </c>
       <c r="C98" s="1">
         <f t="shared" si="23"/>
-        <v>1.5000000000000002</v>
+        <v>1.5</v>
       </c>
       <c r="D98" s="1">
         <f t="shared" si="23"/>
@@ -6492,11 +6466,11 @@
       </c>
       <c r="H98" s="1">
         <f t="shared" si="23"/>
-        <v>2.0999999999999996</v>
+        <v>2.1</v>
       </c>
       <c r="I98" s="1">
         <f t="shared" si="23"/>
-        <v>1.6000000000000003</v>
+        <v>1.6</v>
       </c>
       <c r="J98" s="1">
         <f t="shared" si="23"/>
@@ -6512,7 +6486,7 @@
       </c>
       <c r="M98" s="1">
         <f t="shared" si="23"/>
-        <v>1.1500000000000001</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="N98" s="1">
         <f t="shared" si="23"/>
@@ -6520,7 +6494,7 @@
       </c>
       <c r="O98" s="1">
         <f t="shared" si="23"/>
-        <v>0.15000000000000013</v>
+        <v>0.15000000000000011</v>
       </c>
       <c r="P98" s="1">
         <f t="shared" si="23"/>
@@ -6536,7 +6510,7 @@
       </c>
       <c r="S98" s="1">
         <f t="shared" si="23"/>
-        <v>1.2500000000000002</v>
+        <v>1.25</v>
       </c>
       <c r="T98" s="1">
         <f t="shared" si="23"/>
@@ -6547,41 +6521,41 @@
         <v>-0.94999999999999984</v>
       </c>
     </row>
-    <row r="99" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>16</v>
       </c>
       <c r="B99" s="1">
         <f>CORREL(B81:B91,C81:C91)</f>
-        <v>-0.20000000000000023</v>
+        <v>-0.20000000000000004</v>
       </c>
       <c r="D99" s="1">
         <f>CORREL(D81:D91,E81:E91)</f>
-        <v>-0.20000000000000023</v>
+        <v>-0.20000000000000018</v>
       </c>
       <c r="F99" s="1">
         <f>CORREL(F81:F91,G81:G91)</f>
-        <v>-0.20000000000000029</v>
+        <v>-0.20000000000000021</v>
       </c>
       <c r="H99" s="1">
         <f>CORREL(H81:H91,I81:I91)</f>
-        <v>-0.20000000000000034</v>
+        <v>-0.19999999999999996</v>
       </c>
       <c r="J99" s="1">
         <f>CORREL(J81:J91,K81:K91)</f>
-        <v>-0.20000000000000034</v>
+        <v>-0.20000000000000009</v>
       </c>
       <c r="L99" s="1">
         <f>CORREL(L81:L91,M81:M91)</f>
-        <v>0.20513051305130522</v>
+        <v>0.20513051305130503</v>
       </c>
       <c r="N99" s="1">
         <f>CORREL(N81:N91,O81:O91)</f>
-        <v>0.20513051305130522</v>
+        <v>0.2051305130513052</v>
       </c>
       <c r="P99" s="1">
         <f>CORREL(P81:P91,Q81:Q91)</f>
-        <v>0.2051305130513052</v>
+        <v>0.20513051305130506</v>
       </c>
       <c r="R99" s="1">
         <f>CORREL(R81:R91,S81:S91)</f>
@@ -6589,97 +6563,97 @@
       </c>
       <c r="T99" s="1">
         <f>CORREL(T81:T91,U81:U91)</f>
-        <v>0.20513051305130522</v>
-      </c>
-    </row>
-    <row r="100" spans="1:21" x14ac:dyDescent="0.25">
+        <v>0.20513051305130531</v>
+      </c>
+    </row>
+    <row r="100" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A100" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B100" s="3" cm="1">
+      <c r="B100" s="3">
         <f t="array" ref="B100">SUMPRODUCT((B81:B91&gt;C81:C91)*1)</f>
         <v>8</v>
       </c>
-      <c r="C100" s="3" cm="1">
+      <c r="C100" s="3">
         <f t="array" ref="C100">SUMPRODUCT((B81:B91&lt;C81:C91)*1)</f>
         <v>3</v>
       </c>
-      <c r="D100" s="3" cm="1">
+      <c r="D100" s="3">
         <f t="array" ref="D100">SUMPRODUCT((D81:D91&gt;E81:E91)*1)</f>
         <v>8</v>
       </c>
-      <c r="E100" s="3" cm="1">
+      <c r="E100" s="3">
         <f t="array" ref="E100">SUMPRODUCT((D81:D91&lt;E81:E91)*1)</f>
         <v>3</v>
       </c>
-      <c r="F100" s="3" cm="1">
+      <c r="F100" s="3">
         <f t="array" ref="F100">SUMPRODUCT((F81:F91&gt;G81:G91)*1)</f>
         <v>8</v>
       </c>
-      <c r="G100" s="3" cm="1">
+      <c r="G100" s="3">
         <f t="array" ref="G100">SUMPRODUCT((F81:F91&lt;G81:G91)*1)</f>
         <v>3</v>
       </c>
-      <c r="H100" s="3" cm="1">
+      <c r="H100" s="3">
         <f t="array" ref="H100">SUMPRODUCT((H81:H91&gt;I81:I91)*1)</f>
         <v>8</v>
       </c>
-      <c r="I100" s="3" cm="1">
+      <c r="I100" s="3">
         <f t="array" ref="I100">SUMPRODUCT((H81:H91&lt;I81:I91)*1)</f>
         <v>3</v>
       </c>
-      <c r="J100" s="3" cm="1">
+      <c r="J100" s="3">
         <f t="array" ref="J100">SUMPRODUCT((J81:J91&gt;K81:K91)*1)</f>
         <v>8</v>
       </c>
-      <c r="K100" s="3" cm="1">
+      <c r="K100" s="3">
         <f t="array" ref="K100">SUMPRODUCT((J81:J91&lt;K81:K91)*1)</f>
         <v>3</v>
       </c>
-      <c r="L100" s="3" cm="1">
+      <c r="L100" s="3">
         <f t="array" ref="L100">SUMPRODUCT((L81:L91&gt;M81:M91)*1)</f>
         <v>2</v>
       </c>
-      <c r="M100" s="3" cm="1">
+      <c r="M100" s="3">
         <f t="array" ref="M100">SUMPRODUCT((L81:L91&lt;M81:M91)*1)</f>
         <v>9</v>
       </c>
-      <c r="N100" s="3" cm="1">
+      <c r="N100" s="3">
         <f t="array" ref="N100">SUMPRODUCT((N81:N91&gt;O81:O91)*1)</f>
         <v>2</v>
       </c>
-      <c r="O100" s="3" cm="1">
+      <c r="O100" s="3">
         <f t="array" ref="O100">SUMPRODUCT((N81:N91&lt;O81:O91)*1)</f>
         <v>9</v>
       </c>
-      <c r="P100" s="3" cm="1">
+      <c r="P100" s="3">
         <f t="array" ref="P100">SUMPRODUCT((P81:P91&gt;Q81:Q91)*1)</f>
         <v>2</v>
       </c>
-      <c r="Q100" s="3" cm="1">
+      <c r="Q100" s="3">
         <f t="array" ref="Q100">SUMPRODUCT((P81:P91&lt;Q81:Q91)*1)</f>
         <v>9</v>
       </c>
-      <c r="R100" s="3" cm="1">
+      <c r="R100" s="3">
         <f t="array" ref="R100">SUMPRODUCT((R81:R91&gt;S81:S91)*1)</f>
         <v>2</v>
       </c>
-      <c r="S100" s="3" cm="1">
+      <c r="S100" s="3">
         <f t="array" ref="S100">SUMPRODUCT((R81:R91&lt;S81:S91)*1)</f>
         <v>9</v>
       </c>
-      <c r="T100" s="3" cm="1">
+      <c r="T100" s="3">
         <f t="array" ref="T100">SUMPRODUCT((T81:T91&gt;U81:U91)*1)</f>
         <v>2</v>
       </c>
-      <c r="U100" s="3" cm="1">
+      <c r="U100" s="3">
         <f t="array" ref="U100">SUMPRODUCT((T81:T91&lt;U81:U91)*1)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A101" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B101" s="6" t="str">
         <f>IF(B100&gt;C100,"A",IF(C100&gt;B100,"B","Equal"))</f>
@@ -6722,7 +6696,7 @@
         <v>B</v>
       </c>
     </row>
-    <row r="102" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>19</v>
       </c>
@@ -6767,81 +6741,223 @@
         <v>9</v>
       </c>
     </row>
+    <row r="104" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A104" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="106" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="B106" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D106" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F106" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="H106" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J106" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="L106" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="N106" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="P106" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="R106" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="T106" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="107" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A107" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B107" s="10">
+        <v>0.8</v>
+      </c>
+      <c r="D107" s="10">
+        <v>0.8</v>
+      </c>
+      <c r="F107" s="10">
+        <v>0.8</v>
+      </c>
+      <c r="H107" s="10">
+        <v>0.8</v>
+      </c>
+      <c r="J107" s="10">
+        <v>0.8</v>
+      </c>
+      <c r="L107" s="10">
+        <v>0.8</v>
+      </c>
+      <c r="N107" s="10">
+        <v>0.8</v>
+      </c>
+      <c r="P107" s="10">
+        <v>0.8</v>
+      </c>
+      <c r="R107" s="10">
+        <v>0.8</v>
+      </c>
+      <c r="T107" s="10">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="108" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A108" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B108" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="D108" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="F108" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="H108" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="J108" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="L108" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="N108" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="P108" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="R108" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="T108" s="10">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="109" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A109" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B109" s="10">
+        <v>1.4</v>
+      </c>
+      <c r="D109" s="10">
+        <v>1.4</v>
+      </c>
+      <c r="F109" s="10">
+        <v>1.4</v>
+      </c>
+      <c r="H109" s="10">
+        <v>1.4</v>
+      </c>
+      <c r="J109" s="10">
+        <v>1.4</v>
+      </c>
+      <c r="L109" s="10">
+        <v>1.4</v>
+      </c>
+      <c r="N109" s="10">
+        <v>1.4</v>
+      </c>
+      <c r="P109" s="10">
+        <v>1.4</v>
+      </c>
+      <c r="R109" s="10">
+        <v>1.4</v>
+      </c>
+      <c r="T109" s="10">
+        <v>1.4</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="L80:M80"/>
+    <mergeCell ref="T28:U28"/>
     <mergeCell ref="N80:O80"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="P54:Q54"/>
+    <mergeCell ref="T54:U54"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="J80:K80"/>
     <mergeCell ref="P80:Q80"/>
     <mergeCell ref="R80:S80"/>
     <mergeCell ref="T80:U80"/>
-    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="J54:K54"/>
+    <mergeCell ref="L54:M54"/>
+    <mergeCell ref="R54:S54"/>
+    <mergeCell ref="N28:O28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="J28:K28"/>
     <mergeCell ref="D80:E80"/>
-    <mergeCell ref="F80:G80"/>
-    <mergeCell ref="H80:I80"/>
-    <mergeCell ref="J80:K80"/>
-    <mergeCell ref="L54:M54"/>
-    <mergeCell ref="N54:O54"/>
-    <mergeCell ref="P54:Q54"/>
-    <mergeCell ref="R54:S54"/>
-    <mergeCell ref="T54:U54"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="F54:G54"/>
-    <mergeCell ref="H54:I54"/>
-    <mergeCell ref="J54:K54"/>
     <mergeCell ref="L28:M28"/>
     <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="D28:E28"/>
     <mergeCell ref="F28:G28"/>
+    <mergeCell ref="P28:Q28"/>
     <mergeCell ref="H28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="N28:O28"/>
-    <mergeCell ref="P28:Q28"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="T28:U28"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="H80:I80"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="J2:K2"/>
     <mergeCell ref="R2:S2"/>
-    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="L80:M80"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="H54:I54"/>
+    <mergeCell ref="N54:O54"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F8AFBDA-D1FE-4446-949A-80630D238D1D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A2:K21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="2" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="7"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="12"/>
+      <c r="D2" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="12"/>
+      <c r="F2" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="12"/>
+      <c r="H2" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" s="12"/>
+      <c r="J2" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="K2" s="12"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B3" s="1">
         <v>0</v>
       </c>
@@ -6849,39 +6965,39 @@
         <v>0.5</v>
       </c>
       <c r="D3" s="1">
-        <f>B3-1</f>
+        <f t="shared" ref="D3:D13" si="0">B3-1</f>
         <v>-1</v>
       </c>
       <c r="E3" s="1">
-        <f>C3-1</f>
+        <f t="shared" ref="E3:E13" si="1">C3-1</f>
         <v>-0.5</v>
       </c>
       <c r="F3" s="1">
-        <f>B3-2</f>
+        <f t="shared" ref="F3:F13" si="2">B3-2</f>
         <v>-2</v>
       </c>
       <c r="G3" s="1">
-        <f>C3-2</f>
+        <f t="shared" ref="G3:G13" si="3">C3-2</f>
         <v>-1.5</v>
       </c>
       <c r="H3" s="1">
-        <f>B3+0.1</f>
+        <f t="shared" ref="H3:H13" si="4">B3+0.1</f>
         <v>0.1</v>
       </c>
       <c r="I3" s="1">
-        <f>C3+0.1</f>
+        <f t="shared" ref="I3:I13" si="5">C3+0.1</f>
         <v>0.6</v>
       </c>
       <c r="J3" s="1">
-        <f>F3-0.1</f>
+        <f t="shared" ref="J3:J13" si="6">F3-0.1</f>
         <v>-2.1</v>
       </c>
       <c r="K3" s="1">
-        <f>G3-0.1</f>
+        <f t="shared" ref="K3:K13" si="7">G3-0.1</f>
         <v>-1.6</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B4" s="1">
         <v>0.2</v>
       </c>
@@ -6889,39 +7005,39 @@
         <v>0.6</v>
       </c>
       <c r="D4" s="1">
-        <f t="shared" ref="D4:E13" si="0">B4-1</f>
+        <f t="shared" si="0"/>
         <v>-0.8</v>
       </c>
       <c r="E4" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-0.4</v>
       </c>
       <c r="F4" s="1">
-        <f t="shared" ref="F4:G13" si="1">B4-2</f>
+        <f t="shared" si="2"/>
         <v>-1.8</v>
       </c>
       <c r="G4" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-1.4</v>
       </c>
       <c r="H4" s="1">
-        <f t="shared" ref="H4:I13" si="2">B4+0.1</f>
+        <f t="shared" si="4"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="I4" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0.7</v>
       </c>
       <c r="J4" s="1">
-        <f t="shared" ref="J4:J13" si="3">F4-0.1</f>
+        <f t="shared" si="6"/>
         <v>-1.9000000000000001</v>
       </c>
       <c r="K4" s="1">
-        <f t="shared" ref="K4:K13" si="4">G4-0.1</f>
+        <f t="shared" si="7"/>
         <v>-1.5</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B5" s="1">
         <v>0.4</v>
       </c>
@@ -6933,35 +7049,35 @@
         <v>-0.6</v>
       </c>
       <c r="E5" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-0.30000000000000004</v>
       </c>
       <c r="F5" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-1.6</v>
       </c>
       <c r="G5" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-1.3</v>
       </c>
       <c r="H5" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
       <c r="I5" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0.79999999999999993</v>
       </c>
       <c r="J5" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>-1.7000000000000002</v>
       </c>
       <c r="K5" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>-1.4000000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B6" s="1">
         <v>0.60000000000000009</v>
       </c>
@@ -6973,35 +7089,35 @@
         <v>-0.39999999999999991</v>
       </c>
       <c r="E6" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-0.20000000000000007</v>
       </c>
       <c r="F6" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-1.4</v>
       </c>
       <c r="G6" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-1.2000000000000002</v>
       </c>
       <c r="H6" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.70000000000000007</v>
       </c>
       <c r="I6" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0.89999999999999991</v>
       </c>
       <c r="J6" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>-1.5</v>
       </c>
       <c r="K6" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>-1.3000000000000003</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B7" s="1">
         <v>0.8</v>
       </c>
@@ -7013,35 +7129,35 @@
         <v>-0.19999999999999996</v>
       </c>
       <c r="E7" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-0.10000000000000009</v>
       </c>
       <c r="F7" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-1.2</v>
       </c>
       <c r="G7" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-1.1000000000000001</v>
       </c>
       <c r="H7" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.9</v>
       </c>
       <c r="I7" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0.99999999999999989</v>
       </c>
       <c r="J7" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>-1.3</v>
       </c>
       <c r="K7" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>-1.2000000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B8" s="1">
         <v>1</v>
       </c>
@@ -7053,75 +7169,75 @@
         <v>0</v>
       </c>
       <c r="E8" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F8" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-1</v>
       </c>
       <c r="G8" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-1</v>
       </c>
       <c r="H8" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="I8" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1.0999999999999999</v>
       </c>
       <c r="J8" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>-1.1000000000000001</v>
       </c>
       <c r="K8" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>-1.1000000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B9" s="1">
         <v>1.2</v>
       </c>
       <c r="C9" s="1">
-        <v>1.0999999999999999</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="D9" s="1">
         <f t="shared" si="0"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="E9" s="1">
-        <f t="shared" si="0"/>
-        <v>9.9999999999999867E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.10000000000000009</v>
       </c>
       <c r="F9" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-0.8</v>
       </c>
       <c r="G9" s="1">
-        <f t="shared" si="1"/>
-        <v>-0.90000000000000013</v>
+        <f t="shared" si="3"/>
+        <v>-0.89999999999999991</v>
       </c>
       <c r="H9" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3</v>
       </c>
       <c r="I9" s="1">
-        <f t="shared" si="2"/>
-        <v>1.2</v>
+        <f t="shared" si="5"/>
+        <v>1.2000000000000002</v>
       </c>
       <c r="J9" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>-0.9</v>
       </c>
       <c r="K9" s="1">
-        <f t="shared" si="4"/>
-        <v>-1.0000000000000002</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="7"/>
+        <v>-0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B10" s="1">
         <v>1.4</v>
       </c>
@@ -7133,431 +7249,431 @@
         <v>0.39999999999999991</v>
       </c>
       <c r="E10" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="F10" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-0.60000000000000009</v>
       </c>
       <c r="G10" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-0.8</v>
       </c>
       <c r="H10" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.5</v>
       </c>
       <c r="I10" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1.3</v>
       </c>
       <c r="J10" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>-0.70000000000000007</v>
       </c>
       <c r="K10" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>-0.9</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B11" s="1">
-        <v>1.5999999999999999</v>
+        <v>1.6</v>
       </c>
       <c r="C11" s="1">
         <v>1.3</v>
       </c>
       <c r="D11" s="1">
         <f t="shared" si="0"/>
-        <v>0.59999999999999987</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="E11" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="F11" s="1">
-        <f t="shared" si="1"/>
-        <v>-0.40000000000000013</v>
+        <f t="shared" si="2"/>
+        <v>-0.39999999999999991</v>
       </c>
       <c r="G11" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-0.7</v>
       </c>
       <c r="H11" s="1">
-        <f t="shared" si="2"/>
-        <v>1.7</v>
+        <f t="shared" si="4"/>
+        <v>1.7000000000000002</v>
       </c>
       <c r="I11" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="J11" s="1">
-        <f t="shared" si="3"/>
-        <v>-0.50000000000000011</v>
+        <f t="shared" si="6"/>
+        <v>-0.49999999999999989</v>
       </c>
       <c r="K11" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>-0.79999999999999993</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B12" s="1">
-        <v>1.7999999999999998</v>
+        <v>1.8</v>
       </c>
       <c r="C12" s="1">
-        <v>1.4000000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="D12" s="1">
         <f t="shared" si="0"/>
-        <v>0.79999999999999982</v>
+        <v>0.8</v>
       </c>
       <c r="E12" s="1">
-        <f t="shared" si="0"/>
-        <v>0.40000000000000013</v>
+        <f t="shared" si="1"/>
+        <v>0.39999999999999991</v>
       </c>
       <c r="F12" s="1">
-        <f t="shared" si="1"/>
-        <v>-0.20000000000000018</v>
+        <f t="shared" si="2"/>
+        <v>-0.19999999999999996</v>
       </c>
       <c r="G12" s="1">
-        <f t="shared" si="1"/>
-        <v>-0.59999999999999987</v>
+        <f t="shared" si="3"/>
+        <v>-0.60000000000000009</v>
       </c>
       <c r="H12" s="1">
-        <f t="shared" si="2"/>
-        <v>1.9</v>
+        <f t="shared" si="4"/>
+        <v>1.9000000000000001</v>
       </c>
       <c r="I12" s="1">
-        <f t="shared" si="2"/>
-        <v>1.5000000000000002</v>
+        <f t="shared" si="5"/>
+        <v>1.5</v>
       </c>
       <c r="J12" s="1">
-        <f t="shared" si="3"/>
-        <v>-0.30000000000000016</v>
+        <f t="shared" si="6"/>
+        <v>-0.29999999999999993</v>
       </c>
       <c r="K12" s="1">
-        <f t="shared" si="4"/>
-        <v>-0.69999999999999984</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="7"/>
+        <v>-0.70000000000000007</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B13" s="1">
-        <v>1.9999999999999998</v>
+        <v>2</v>
       </c>
       <c r="C13" s="1">
-        <v>1.5000000000000002</v>
+        <v>1.5</v>
       </c>
       <c r="D13" s="1">
         <f t="shared" si="0"/>
-        <v>0.99999999999999978</v>
+        <v>1</v>
       </c>
       <c r="E13" s="1">
-        <f t="shared" si="0"/>
-        <v>0.50000000000000022</v>
+        <f t="shared" si="1"/>
+        <v>0.5</v>
       </c>
       <c r="F13" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G13" s="1">
-        <f t="shared" si="1"/>
-        <v>-0.49999999999999978</v>
+        <f t="shared" si="3"/>
+        <v>-0.5</v>
       </c>
       <c r="H13" s="1">
-        <f t="shared" si="2"/>
-        <v>2.0999999999999996</v>
+        <f t="shared" si="4"/>
+        <v>2.1</v>
       </c>
       <c r="I13" s="1">
-        <f t="shared" si="2"/>
-        <v>1.6000000000000003</v>
+        <f t="shared" si="5"/>
+        <v>1.6</v>
       </c>
       <c r="J13" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>-0.1</v>
       </c>
       <c r="K13" s="1">
-        <f t="shared" si="4"/>
-        <v>-0.59999999999999976</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="7"/>
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B15" s="1">
-        <f t="shared" ref="B15:K15" si="5">AVERAGE(B3:B13)</f>
+        <f t="shared" ref="B15:K15" si="8">AVERAGE(B3:B13)</f>
         <v>1</v>
       </c>
       <c r="C15" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="D15" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E15" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F15" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>-1</v>
       </c>
       <c r="G15" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>-1</v>
       </c>
       <c r="H15" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="I15" s="1">
+        <f t="shared" si="8"/>
         <v>1.0999999999999999</v>
       </c>
-      <c r="I15" s="1">
-        <f t="shared" si="5"/>
-        <v>1.0999999999999999</v>
-      </c>
       <c r="J15" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>-1.0999999999999999</v>
       </c>
       <c r="K15" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>-1.1000000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B16" s="4">
-        <f t="shared" ref="B16:K16" si="6">_xlfn.STDEV.P(B3:B13)</f>
+        <f t="shared" ref="B16:K16" si="9">_xlfn.STDEV.P(B3:B13)</f>
+        <v>0.63245553203367588</v>
+      </c>
+      <c r="C16" s="4">
+        <f t="shared" si="9"/>
+        <v>0.31622776601683783</v>
+      </c>
+      <c r="D16" s="4">
+        <f t="shared" si="9"/>
+        <v>0.63245553203367588</v>
+      </c>
+      <c r="E16" s="4">
+        <f t="shared" si="9"/>
+        <v>0.31622776601683794</v>
+      </c>
+      <c r="F16" s="4">
+        <f t="shared" si="9"/>
         <v>0.63245553203367566</v>
       </c>
-      <c r="C16" s="4">
-        <f t="shared" si="6"/>
+      <c r="G16" s="4">
+        <f t="shared" si="9"/>
         <v>0.31622776601683822</v>
       </c>
-      <c r="D16" s="4">
-        <f t="shared" si="6"/>
-        <v>0.63245553203367577</v>
-      </c>
-      <c r="E16" s="4">
-        <f t="shared" si="6"/>
-        <v>0.316227766016838</v>
-      </c>
-      <c r="F16" s="4">
-        <f t="shared" si="6"/>
-        <v>0.63245553203367588</v>
-      </c>
-      <c r="G16" s="4">
-        <f t="shared" si="6"/>
+      <c r="H16" s="4">
+        <f t="shared" si="9"/>
+        <v>0.63245553203367566</v>
+      </c>
+      <c r="I16" s="4">
+        <f t="shared" si="9"/>
         <v>0.31622776601683822</v>
       </c>
-      <c r="H16" s="4">
-        <f t="shared" si="6"/>
-        <v>0.63245553203367588</v>
-      </c>
-      <c r="I16" s="4">
-        <f t="shared" si="6"/>
+      <c r="J16" s="4">
+        <f t="shared" si="9"/>
+        <v>0.63245553203367566</v>
+      </c>
+      <c r="K16" s="4">
+        <f t="shared" si="9"/>
         <v>0.31622776601683822</v>
       </c>
-      <c r="J16" s="4">
-        <f t="shared" si="6"/>
-        <v>0.63245553203367566</v>
-      </c>
-      <c r="K16" s="4">
-        <f t="shared" si="6"/>
-        <v>0.31622776601683822</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B17" s="1">
-        <f t="shared" ref="B17:K17" si="7">_xlfn.SKEW.P(B3:B13)</f>
-        <v>-4.0371746350005691E-16</v>
+        <f t="shared" ref="B17:K17" si="10">_xlfn.SKEW.P(B3:B13)</f>
+        <v>0</v>
       </c>
       <c r="C17" s="1">
-        <f t="shared" si="7"/>
-        <v>6.0557619525008534E-16</v>
+        <f t="shared" si="10"/>
+        <v>-2.0185873175002846E-16</v>
       </c>
       <c r="D17" s="1">
-        <f t="shared" si="7"/>
-        <v>-4.4408920985006262E-16</v>
+        <f t="shared" si="10"/>
+        <v>0</v>
       </c>
       <c r="E17" s="1">
-        <f t="shared" si="7"/>
-        <v>6.0557619525008534E-16</v>
+        <f t="shared" si="10"/>
+        <v>1.2111523905001707E-16</v>
       </c>
       <c r="F17" s="1">
-        <f t="shared" si="7"/>
-        <v>-2.8260222445003984E-16</v>
+        <f t="shared" si="10"/>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
-        <f t="shared" si="7"/>
-        <v>7.6706318065010816E-16</v>
+        <f t="shared" si="10"/>
+        <v>-1.2111523905001707E-16</v>
       </c>
       <c r="H17" s="1">
-        <f t="shared" si="7"/>
-        <v>1.2111523905001707E-16</v>
+        <f t="shared" si="10"/>
+        <v>0</v>
       </c>
       <c r="I17" s="1">
-        <f t="shared" si="7"/>
-        <v>2.2204460492503131E-15</v>
+        <f t="shared" si="10"/>
+        <v>1.3322676295501878E-15</v>
       </c>
       <c r="J17" s="1">
-        <f t="shared" si="7"/>
-        <v>-8.4780667335011958E-16</v>
+        <f t="shared" si="10"/>
+        <v>-8.8817841970012523E-16</v>
       </c>
       <c r="K17" s="1">
-        <f t="shared" si="7"/>
-        <v>1.2111523905001707E-15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>5.2483270255007403E-16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B18" s="1">
-        <f t="shared" ref="B18:K18" si="8">KURT(B3:B13)</f>
+        <f t="shared" ref="B18:K18" si="11">KURT(B3:B13)</f>
+        <v>-1.2000000000000015</v>
+      </c>
+      <c r="C18" s="1">
+        <f t="shared" si="11"/>
+        <v>-1.200000000000002</v>
+      </c>
+      <c r="D18" s="1">
+        <f t="shared" si="11"/>
+        <v>-1.2000000000000015</v>
+      </c>
+      <c r="E18" s="1">
+        <f t="shared" si="11"/>
+        <v>-1.200000000000002</v>
+      </c>
+      <c r="F18" s="1">
+        <f t="shared" si="11"/>
         <v>-1.2000000000000011</v>
       </c>
-      <c r="C18" s="1">
-        <f t="shared" si="8"/>
+      <c r="G18" s="1">
+        <f t="shared" si="11"/>
         <v>-1.200000000000002</v>
       </c>
-      <c r="D18" s="1">
-        <f t="shared" si="8"/>
-        <v>-1.1999999999999997</v>
-      </c>
-      <c r="E18" s="1">
-        <f t="shared" si="8"/>
-        <v>-1.200000000000002</v>
-      </c>
-      <c r="F18" s="1">
-        <f t="shared" si="8"/>
-        <v>-1.200000000000002</v>
-      </c>
-      <c r="G18" s="1">
-        <f t="shared" si="8"/>
-        <v>-1.200000000000002</v>
-      </c>
       <c r="H18" s="1">
-        <f t="shared" si="8"/>
-        <v>-1.200000000000002</v>
+        <f t="shared" si="11"/>
+        <v>-1.2000000000000011</v>
       </c>
       <c r="I18" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
+        <v>-1.2000000000000028</v>
+      </c>
+      <c r="J18" s="1">
+        <f t="shared" si="11"/>
         <v>-1.2000000000000011</v>
       </c>
-      <c r="J18" s="1">
-        <f t="shared" si="8"/>
+      <c r="K18" s="1">
+        <f t="shared" si="11"/>
         <v>-1.2000000000000011</v>
       </c>
-      <c r="K18" s="1">
-        <f t="shared" si="8"/>
-        <v>-1.2000000000000002</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>14</v>
       </c>
       <c r="B19" s="1">
-        <f t="shared" ref="B19:K19" si="9">MIN(B3:B13)</f>
+        <f t="shared" ref="B19:K19" si="12">MIN(B3:B13)</f>
         <v>0</v>
       </c>
       <c r="C19" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
       <c r="D19" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>-1</v>
       </c>
       <c r="E19" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>-0.5</v>
       </c>
       <c r="F19" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>-2</v>
       </c>
       <c r="G19" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>-1.5</v>
       </c>
       <c r="H19" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0.1</v>
       </c>
       <c r="I19" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0.6</v>
       </c>
       <c r="J19" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>-2.1</v>
       </c>
       <c r="K19" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>-1.6</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>15</v>
       </c>
       <c r="B20" s="1">
-        <f t="shared" ref="B20:K20" si="10">MAX(B3:B13)</f>
-        <v>1.9999999999999998</v>
+        <f t="shared" ref="B20:K20" si="13">MAX(B3:B13)</f>
+        <v>2</v>
       </c>
       <c r="C20" s="1">
-        <f t="shared" si="10"/>
-        <v>1.5000000000000002</v>
+        <f t="shared" si="13"/>
+        <v>1.5</v>
       </c>
       <c r="D20" s="1">
-        <f t="shared" si="10"/>
-        <v>0.99999999999999978</v>
+        <f t="shared" si="13"/>
+        <v>1</v>
       </c>
       <c r="E20" s="1">
-        <f t="shared" si="10"/>
-        <v>0.50000000000000022</v>
+        <f t="shared" si="13"/>
+        <v>0.5</v>
       </c>
       <c r="F20" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="G20" s="1">
-        <f t="shared" si="10"/>
-        <v>-0.49999999999999978</v>
+        <f t="shared" si="13"/>
+        <v>-0.5</v>
       </c>
       <c r="H20" s="1">
-        <f t="shared" si="10"/>
-        <v>2.0999999999999996</v>
+        <f t="shared" si="13"/>
+        <v>2.1</v>
       </c>
       <c r="I20" s="1">
-        <f t="shared" si="10"/>
-        <v>1.6000000000000003</v>
+        <f t="shared" si="13"/>
+        <v>1.6</v>
       </c>
       <c r="J20" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>-0.1</v>
       </c>
       <c r="K20" s="1">
-        <f t="shared" si="10"/>
-        <v>-0.59999999999999976</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="13"/>
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>16</v>
       </c>
       <c r="B21" s="1">
         <f>CORREL(B3:B13,C3:C13)</f>
-        <v>0.99999999999999989</v>
+        <v>1</v>
       </c>
       <c r="D21" s="1">
         <f>CORREL(D3:D13,E3:E13)</f>
@@ -7565,23 +7681,23 @@
       </c>
       <c r="F21" s="1">
         <f>CORREL(F3:F13,G3:G13)</f>
-        <v>0.99999999999999989</v>
+        <v>1</v>
       </c>
       <c r="H21" s="1">
         <f>CORREL(H3:H13,I3:I13)</f>
-        <v>0.99999999999999978</v>
+        <v>0.99999999999999989</v>
       </c>
       <c r="J21" s="1">
         <f>CORREL(J3:J13,K3:K13)</f>
-        <v>1.0000000000000002</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="F2:G2"/>
     <mergeCell ref="B2:C2"/>
+    <mergeCell ref="H2:I2"/>
     <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
     <mergeCell ref="J2:K2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7589,33 +7705,33 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF773734-4B47-4C9C-9EE0-FCAAC16253AB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A2:K21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="2" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7" t="s">
+    <row r="2" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="12"/>
+      <c r="D2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7" t="s">
+      <c r="E2" s="12"/>
+      <c r="F2" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7" t="s">
+      <c r="G2" s="12"/>
+      <c r="H2" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="7"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I2" s="12"/>
+      <c r="J2" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="12"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B3" s="1">
         <v>0.85</v>
       </c>
@@ -7623,39 +7739,39 @@
         <v>1.05</v>
       </c>
       <c r="D3" s="1">
-        <f>B3-1</f>
+        <f t="shared" ref="D3:D13" si="0">B3-1</f>
         <v>-0.15000000000000002</v>
       </c>
       <c r="E3" s="1">
-        <f>C3-1</f>
+        <f t="shared" ref="E3:E13" si="1">C3-1</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="F3" s="1">
-        <f>B3-2</f>
+        <f t="shared" ref="F3:F13" si="2">B3-2</f>
         <v>-1.1499999999999999</v>
       </c>
       <c r="G3" s="1">
-        <f>C3-2</f>
+        <f t="shared" ref="G3:G13" si="3">C3-2</f>
         <v>-0.95</v>
       </c>
       <c r="H3" s="1">
-        <f>B3+0.1</f>
+        <f t="shared" ref="H3:H13" si="4">B3+0.1</f>
         <v>0.95</v>
       </c>
       <c r="I3" s="1">
-        <f>C3+0.1</f>
+        <f t="shared" ref="I3:I13" si="5">C3+0.1</f>
         <v>1.1500000000000001</v>
       </c>
       <c r="J3" s="1">
-        <f>F3-0.1</f>
+        <f t="shared" ref="J3:J13" si="6">F3-0.1</f>
         <v>-1.25</v>
       </c>
       <c r="K3" s="1">
-        <f>G3-0.1</f>
+        <f t="shared" ref="K3:K13" si="7">G3-0.1</f>
         <v>-1.05</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B4" s="1">
         <v>0.86</v>
       </c>
@@ -7663,39 +7779,39 @@
         <v>1.06</v>
       </c>
       <c r="D4" s="1">
-        <f t="shared" ref="D4:E13" si="0">B4-1</f>
+        <f t="shared" si="0"/>
         <v>-0.14000000000000001</v>
       </c>
       <c r="E4" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="F4" s="1">
-        <f t="shared" ref="F4:G13" si="1">B4-2</f>
+        <f t="shared" si="2"/>
         <v>-1.1400000000000001</v>
       </c>
       <c r="G4" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-0.94</v>
       </c>
       <c r="H4" s="1">
-        <f t="shared" ref="H4:I13" si="2">B4+0.1</f>
+        <f t="shared" si="4"/>
         <v>0.96</v>
       </c>
       <c r="I4" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1.1600000000000001</v>
       </c>
       <c r="J4" s="1">
-        <f t="shared" ref="J4:K13" si="3">F4-0.1</f>
+        <f t="shared" si="6"/>
         <v>-1.2400000000000002</v>
       </c>
       <c r="K4" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-1.04</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B5" s="1">
         <v>0.87</v>
       </c>
@@ -7707,35 +7823,35 @@
         <v>-0.13</v>
       </c>
       <c r="E5" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7.0000000000000062E-2</v>
       </c>
       <c r="F5" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-1.1299999999999999</v>
       </c>
       <c r="G5" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-0.92999999999999994</v>
       </c>
       <c r="H5" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.97</v>
       </c>
       <c r="I5" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1.1700000000000002</v>
       </c>
       <c r="J5" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>-1.23</v>
       </c>
       <c r="K5" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-1.03</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B6" s="1">
         <v>0.88</v>
       </c>
@@ -7747,35 +7863,35 @@
         <v>-0.12</v>
       </c>
       <c r="E6" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="F6" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-1.1200000000000001</v>
       </c>
       <c r="G6" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-0.91999999999999993</v>
       </c>
       <c r="H6" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.98</v>
       </c>
       <c r="I6" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1.1800000000000002</v>
       </c>
       <c r="J6" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>-1.2200000000000002</v>
       </c>
       <c r="K6" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-1.02</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B7" s="1">
         <v>0.89</v>
       </c>
@@ -7787,35 +7903,35 @@
         <v>-0.10999999999999999</v>
       </c>
       <c r="E7" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9.000000000000008E-2</v>
       </c>
       <c r="F7" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-1.1099999999999999</v>
       </c>
       <c r="G7" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-0.90999999999999992</v>
       </c>
       <c r="H7" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.99</v>
       </c>
       <c r="I7" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1.1900000000000002</v>
       </c>
       <c r="J7" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>-1.21</v>
       </c>
       <c r="K7" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-1.01</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B8" s="1">
         <v>0.91</v>
       </c>
@@ -7827,35 +7943,35 @@
         <v>-8.9999999999999969E-2</v>
       </c>
       <c r="E8" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.1100000000000001</v>
       </c>
       <c r="F8" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-1.0899999999999999</v>
       </c>
       <c r="G8" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-0.8899999999999999</v>
       </c>
       <c r="H8" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.01</v>
       </c>
       <c r="I8" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1.2100000000000002</v>
       </c>
       <c r="J8" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>-1.19</v>
       </c>
       <c r="K8" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-0.98999999999999988</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B9" s="1">
         <v>0.92</v>
       </c>
@@ -7867,155 +7983,155 @@
         <v>-7.999999999999996E-2</v>
       </c>
       <c r="E9" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.12000000000000011</v>
       </c>
       <c r="F9" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-1.08</v>
       </c>
       <c r="G9" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-0.87999999999999989</v>
       </c>
       <c r="H9" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.02</v>
       </c>
       <c r="I9" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1.2200000000000002</v>
       </c>
       <c r="J9" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>-1.1800000000000002</v>
       </c>
       <c r="K9" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-0.97999999999999987</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B10" s="1">
         <v>0.93</v>
       </c>
       <c r="C10" s="1">
-        <v>1.1300000000000001</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="D10" s="1">
         <f t="shared" si="0"/>
         <v>-6.9999999999999951E-2</v>
       </c>
       <c r="E10" s="1">
-        <f t="shared" si="0"/>
-        <v>0.13000000000000012</v>
+        <f t="shared" si="1"/>
+        <v>0.12999999999999989</v>
       </c>
       <c r="F10" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-1.0699999999999998</v>
       </c>
       <c r="G10" s="1">
-        <f t="shared" si="1"/>
-        <v>-0.86999999999999988</v>
+        <f t="shared" si="3"/>
+        <v>-0.87000000000000011</v>
       </c>
       <c r="H10" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.03</v>
       </c>
       <c r="I10" s="1">
-        <f t="shared" si="2"/>
-        <v>1.2300000000000002</v>
+        <f t="shared" si="5"/>
+        <v>1.23</v>
       </c>
       <c r="J10" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>-1.17</v>
       </c>
       <c r="K10" s="1">
-        <f t="shared" si="3"/>
-        <v>-0.96999999999999986</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="7"/>
+        <v>-0.97000000000000008</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B11" s="1">
         <v>0.94000000000000006</v>
       </c>
       <c r="C11" s="1">
-        <v>1.1400000000000001</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="D11" s="1">
         <f t="shared" si="0"/>
         <v>-5.9999999999999942E-2</v>
       </c>
       <c r="E11" s="1">
-        <f t="shared" si="0"/>
-        <v>0.14000000000000012</v>
+        <f t="shared" si="1"/>
+        <v>0.1399999999999999</v>
       </c>
       <c r="F11" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-1.06</v>
       </c>
       <c r="G11" s="1">
-        <f t="shared" si="1"/>
-        <v>-0.85999999999999988</v>
+        <f t="shared" si="3"/>
+        <v>-0.8600000000000001</v>
       </c>
       <c r="H11" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.04</v>
       </c>
       <c r="I11" s="1">
-        <f t="shared" si="2"/>
-        <v>1.2400000000000002</v>
+        <f t="shared" si="5"/>
+        <v>1.24</v>
       </c>
       <c r="J11" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>-1.1600000000000001</v>
       </c>
       <c r="K11" s="1">
-        <f t="shared" si="3"/>
-        <v>-0.95999999999999985</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="7"/>
+        <v>-0.96000000000000008</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B12" s="1">
         <v>0.95000000000000007</v>
       </c>
       <c r="C12" s="1">
-        <v>1.1500000000000001</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="D12" s="1">
         <f t="shared" si="0"/>
         <v>-4.9999999999999933E-2</v>
       </c>
       <c r="E12" s="1">
-        <f t="shared" si="0"/>
-        <v>0.15000000000000013</v>
+        <f t="shared" si="1"/>
+        <v>0.14999999999999991</v>
       </c>
       <c r="F12" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-1.0499999999999998</v>
       </c>
       <c r="G12" s="1">
-        <f t="shared" si="1"/>
-        <v>-0.84999999999999987</v>
+        <f t="shared" si="3"/>
+        <v>-0.85000000000000009</v>
       </c>
       <c r="H12" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.05</v>
       </c>
       <c r="I12" s="1">
-        <f t="shared" si="2"/>
-        <v>1.2500000000000002</v>
+        <f t="shared" si="5"/>
+        <v>1.25</v>
       </c>
       <c r="J12" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>-1.1499999999999999</v>
       </c>
       <c r="K12" s="1">
-        <f t="shared" si="3"/>
-        <v>-0.94999999999999984</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="7"/>
+        <v>-0.95000000000000007</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B13" s="1">
         <v>2</v>
       </c>
@@ -8027,305 +8143,305 @@
         <v>1</v>
       </c>
       <c r="E13" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-1</v>
       </c>
       <c r="F13" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G13" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-2</v>
       </c>
       <c r="H13" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.1</v>
       </c>
       <c r="I13" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0.1</v>
       </c>
       <c r="J13" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>-0.1</v>
       </c>
       <c r="K13" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-2.1</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B15" s="1">
-        <f t="shared" ref="B15:K15" si="4">AVERAGE(B3:B13)</f>
+        <f t="shared" ref="B15:K15" si="8">AVERAGE(B3:B13)</f>
         <v>0.99999999999999989</v>
       </c>
       <c r="C15" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>1.0000000000000002</v>
       </c>
       <c r="D15" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E15" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F15" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>-1</v>
       </c>
       <c r="G15" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>-0.99999999999999989</v>
       </c>
       <c r="H15" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>1.0999999999999999</v>
       </c>
       <c r="I15" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="J15" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>-1.0999999999999999</v>
       </c>
       <c r="K15" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>-1.0999999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B16" s="1">
-        <f t="shared" ref="B16:K16" si="5">_xlfn.STDEV.P(B3:B13)</f>
+        <f t="shared" ref="B16:K16" si="9">_xlfn.STDEV.P(B3:B13)</f>
         <v>0.31780497164141469</v>
       </c>
       <c r="C16" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.31780497164141358</v>
       </c>
       <c r="D16" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.31780497164141408</v>
       </c>
       <c r="E16" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.31780497164141408</v>
       </c>
       <c r="F16" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.31780497164141375</v>
       </c>
       <c r="G16" s="1">
-        <f t="shared" si="5"/>
-        <v>0.3178049716414143</v>
+        <f t="shared" si="9"/>
+        <v>0.31780497164141469</v>
       </c>
       <c r="H16" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.31780497164141414</v>
       </c>
       <c r="I16" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
+        <v>0.31780497164141375</v>
+      </c>
+      <c r="J16" s="1">
+        <f t="shared" si="9"/>
         <v>0.31780497164141414</v>
       </c>
-      <c r="J16" s="1">
-        <f t="shared" si="5"/>
+      <c r="K16" s="1">
+        <f t="shared" si="9"/>
         <v>0.31780497164141414</v>
       </c>
-      <c r="K16" s="1">
-        <f t="shared" si="5"/>
-        <v>0.31780497164141486</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B17" s="4">
-        <f t="shared" ref="B17:K17" si="6">_xlfn.SKEW.P(B3:B13)</f>
+        <f t="shared" ref="B17:K17" si="10">_xlfn.SKEW.P(B3:B13)</f>
         <v>2.7945403348921536</v>
       </c>
       <c r="C17" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>-2.7945403348921536</v>
       </c>
       <c r="D17" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>2.7945403348921518</v>
       </c>
       <c r="E17" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>-2.7945403348921518</v>
       </c>
       <c r="F17" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>2.7945403348921518</v>
       </c>
       <c r="G17" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
+        <v>-2.7945403348921536</v>
+      </c>
+      <c r="H17" s="4">
+        <f t="shared" si="10"/>
+        <v>2.7945403348921536</v>
+      </c>
+      <c r="I17" s="4">
+        <f t="shared" si="10"/>
         <v>-2.7945403348921518</v>
       </c>
-      <c r="H17" s="4">
-        <f t="shared" si="6"/>
-        <v>2.7945403348921536</v>
-      </c>
-      <c r="I17" s="4">
-        <f t="shared" si="6"/>
-        <v>-2.7945403348921518</v>
-      </c>
       <c r="J17" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>2.7945403348921505</v>
       </c>
       <c r="K17" s="4">
-        <f t="shared" si="6"/>
-        <v>-2.7945403348921518</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>-2.7945403348921536</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B18" s="1">
-        <f t="shared" ref="B18:K18" si="7">KURT(B3:B13)</f>
+        <f t="shared" ref="B18:K18" si="11">KURT(B3:B13)</f>
         <v>10.711250530993702</v>
       </c>
       <c r="C18" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>10.711250530993702</v>
       </c>
       <c r="D18" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>10.711250530993684</v>
       </c>
       <c r="E18" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>10.711250530993684</v>
       </c>
       <c r="F18" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>10.711250530993684</v>
       </c>
       <c r="G18" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
+        <v>10.711250530993702</v>
+      </c>
+      <c r="H18" s="1">
+        <f t="shared" si="11"/>
+        <v>10.711250530993702</v>
+      </c>
+      <c r="I18" s="1">
+        <f t="shared" si="11"/>
         <v>10.711250530993684</v>
       </c>
-      <c r="H18" s="1">
-        <f t="shared" si="7"/>
+      <c r="J18" s="1">
+        <f t="shared" si="11"/>
+        <v>10.711250530993684</v>
+      </c>
+      <c r="K18" s="1">
+        <f t="shared" si="11"/>
         <v>10.711250530993702</v>
       </c>
-      <c r="I18" s="1">
-        <f t="shared" si="7"/>
-        <v>10.711250530993684</v>
-      </c>
-      <c r="J18" s="1">
-        <f t="shared" si="7"/>
-        <v>10.711250530993684</v>
-      </c>
-      <c r="K18" s="1">
-        <f t="shared" si="7"/>
-        <v>10.711250530993691</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>14</v>
       </c>
       <c r="B19" s="1">
-        <f t="shared" ref="B19:K19" si="8">MIN(B3:B13)</f>
+        <f t="shared" ref="B19:K19" si="12">MIN(B3:B13)</f>
         <v>0.85</v>
       </c>
       <c r="C19" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="D19" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>-0.15000000000000002</v>
       </c>
       <c r="E19" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>-1</v>
       </c>
       <c r="F19" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>-1.1499999999999999</v>
       </c>
       <c r="G19" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>-2</v>
       </c>
       <c r="H19" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.95</v>
       </c>
       <c r="I19" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.1</v>
       </c>
       <c r="J19" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>-1.25</v>
       </c>
       <c r="K19" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>-2.1</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>15</v>
       </c>
       <c r="B20" s="1">
-        <f t="shared" ref="B20:K20" si="9">MAX(B3:B13)</f>
+        <f t="shared" ref="B20:K20" si="13">MAX(B3:B13)</f>
         <v>2</v>
       </c>
       <c r="C20" s="1">
-        <f t="shared" si="9"/>
-        <v>1.1500000000000001</v>
+        <f t="shared" si="13"/>
+        <v>1.1499999999999999</v>
       </c>
       <c r="D20" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E20" s="1">
-        <f t="shared" si="9"/>
-        <v>0.15000000000000013</v>
+        <f t="shared" si="13"/>
+        <v>0.14999999999999991</v>
       </c>
       <c r="F20" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="G20" s="1">
-        <f t="shared" si="9"/>
-        <v>-0.84999999999999987</v>
+        <f t="shared" si="13"/>
+        <v>-0.85000000000000009</v>
       </c>
       <c r="H20" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>2.1</v>
       </c>
       <c r="I20" s="1">
-        <f t="shared" si="9"/>
-        <v>1.2500000000000002</v>
+        <f t="shared" si="13"/>
+        <v>1.25</v>
       </c>
       <c r="J20" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>-0.1</v>
       </c>
       <c r="K20" s="1">
-        <f t="shared" si="9"/>
-        <v>-0.94999999999999984</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="13"/>
+        <v>-0.95000000000000007</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>16</v>
       </c>
@@ -8339,7 +8455,7 @@
       </c>
       <c r="F21" s="1">
         <f>CORREL(F3:F13,G3:G13)</f>
-        <v>-0.98019801980198007</v>
+        <v>-0.98019801980198018</v>
       </c>
       <c r="H21" s="1">
         <f>CORREL(H3:H13,I3:I13)</f>
@@ -8347,15 +8463,15 @@
       </c>
       <c r="J21" s="1">
         <f>CORREL(J3:J13,K3:K13)</f>
-        <v>-0.98019801980197996</v>
+        <v>-0.98019801980198007</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="F2:G2"/>
     <mergeCell ref="B2:C2"/>
+    <mergeCell ref="H2:I2"/>
     <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
     <mergeCell ref="J2:K2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Distributions.xlsx
+++ b/Distributions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aaltofi-my.sharepoint.com/personal/samuel_salin_aalto_fi/Documents/Desktop/Risk Elicitation/RE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BBF9AF74AC20D3FF2286BA73C3D10CC99D880FBC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B475AB59-9C80-4B51-ABA7-F0F6F2694E65}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_BA4D2FB74CA8045DC74C1AC6005315D59D888FE4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E53CF80-D76A-45FC-B8D4-F6B92E7F8969}"/>
   <bookViews>
     <workbookView xWindow="-5160" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="29">
   <si>
     <t>D1</t>
   </si>
@@ -109,9 +109,6 @@
     <t>Variation 2.2: Random allocation of outcomes to situations by state (e.g., same-row observations in column B and column C form an outcome pair that cannot be broken up, so that the structure of dependence is fixed)</t>
   </si>
   <si>
-    <t>Round Thresholds: FREQ_THRES_L / TAIL_THRES_L / TAIL_THRES_H per distribution (same threshold used for both alternatives in a round that draws this distribution; edit the numbers below directly - no code changes needed)</t>
-  </si>
-  <si>
     <t>FREQ_THRES_L</t>
   </si>
   <si>
@@ -119,6 +116,12 @@
   </si>
   <si>
     <t>TAIL_THRES_H</t>
+  </si>
+  <si>
+    <t>FREQ_THRES_H</t>
+  </si>
+  <si>
+    <t>Round Thresholds: FREQ_THRES_L /H and  TAIL_THRES_L / H per distribution (same threshold used for both alternatives in a round that draws this distribution; edit the numbers below directly - no code changes needed)</t>
   </si>
 </sst>
 </file>
@@ -540,7 +543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:AB109"/>
+  <dimension ref="A2:AB110"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="198.81640625" bestFit="1" customWidth="1"/>
@@ -2061,27 +2064,27 @@
       </c>
       <c r="C29" s="1">
         <f t="array" aca="1" ref="C29:C39" ca="1">_xlfn.SORTBY(C3:C13,_xlfn.RANDARRAY(ROWS(C3:C13)))</f>
-        <v>0.6</v>
+        <v>0.79999999999999993</v>
       </c>
       <c r="D29" s="1">
         <f t="array" aca="1" ref="D29:D39" ca="1">_xlfn.SORTBY(D3:D13,_xlfn.RANDARRAY(ROWS(D3:D13)))</f>
-        <v>0</v>
+        <v>0.79999999999999982</v>
       </c>
       <c r="E29" s="1">
         <f t="array" aca="1" ref="E29:E39" ca="1">_xlfn.SORTBY(E3:E13,_xlfn.RANDARRAY(ROWS(E3:E13)))</f>
-        <v>-0.20000000000000009</v>
+        <v>9.9999999999999867E-2</v>
       </c>
       <c r="F29" s="1">
         <f t="array" aca="1" ref="F29:F39" ca="1">_xlfn.SORTBY(F3:F13,_xlfn.RANDARRAY(ROWS(F3:F13)))</f>
-        <v>-0.20000000000000021</v>
+        <v>-2</v>
       </c>
       <c r="G29" s="1">
         <f t="array" aca="1" ref="G29:G39" ca="1">_xlfn.SORTBY(G3:G13,_xlfn.RANDARRAY(ROWS(G3:G13)))</f>
-        <v>-1.1000000000000001</v>
+        <v>-0.59999999999999987</v>
       </c>
       <c r="H29" s="1">
         <f t="array" aca="1" ref="H29:H39" ca="1">_xlfn.SORTBY(H3:H13,_xlfn.RANDARRAY(ROWS(H3:H13)))</f>
-        <v>1.9</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="I29" s="1">
         <f t="array" aca="1" ref="I29:I39" ca="1">_xlfn.SORTBY(I3:I13,_xlfn.RANDARRAY(ROWS(I3:I13)))</f>
@@ -2089,51 +2092,51 @@
       </c>
       <c r="J29" s="1">
         <f t="array" aca="1" ref="J29:J39" ca="1">_xlfn.SORTBY(J3:J13,_xlfn.RANDARRAY(ROWS(J3:J13)))</f>
-        <v>-0.70000000000000007</v>
+        <v>-1.9</v>
       </c>
       <c r="K29" s="1">
         <f t="array" aca="1" ref="K29:K39" ca="1">_xlfn.SORTBY(K3:K13,_xlfn.RANDARRAY(ROWS(K3:K13)))</f>
-        <v>-1</v>
+        <v>-0.59999999999999976</v>
       </c>
       <c r="L29" s="1">
         <f t="array" aca="1" ref="L29:L39" ca="1">_xlfn.SORTBY(L3:L13,_xlfn.RANDARRAY(ROWS(L3:L13)))</f>
-        <v>2</v>
+        <v>0.89</v>
       </c>
       <c r="M29" s="1">
         <f t="array" aca="1" ref="M29:M39" ca="1">_xlfn.SORTBY(M3:M13,_xlfn.RANDARRAY(ROWS(M3:M13)))</f>
-        <v>1.1499999999999999</v>
+        <v>1.07</v>
       </c>
       <c r="N29" s="1">
         <f t="array" aca="1" ref="N29:N39" ca="1">_xlfn.SORTBY(N3:N13,_xlfn.RANDARRAY(ROWS(N3:N13)))</f>
-        <v>-0.12</v>
+        <v>1</v>
       </c>
       <c r="O29" s="1">
         <f t="array" aca="1" ref="O29:O39" ca="1">_xlfn.SORTBY(O3:O13,_xlfn.RANDARRAY(ROWS(O3:O13)))</f>
-        <v>0.15000000000000011</v>
+        <v>0.12000000000000011</v>
       </c>
       <c r="P29" s="1">
         <f t="array" aca="1" ref="P29:P39" ca="1">_xlfn.SORTBY(P3:P13,_xlfn.RANDARRAY(ROWS(P3:P13)))</f>
-        <v>-1.08</v>
+        <v>-1.05</v>
       </c>
       <c r="Q29" s="1">
         <f t="array" aca="1" ref="Q29:Q39" ca="1">_xlfn.SORTBY(Q3:Q13,_xlfn.RANDARRAY(ROWS(Q3:Q13)))</f>
-        <v>-2</v>
+        <v>-0.94</v>
       </c>
       <c r="R29" s="1">
         <f t="array" aca="1" ref="R29:R39" ca="1">_xlfn.SORTBY(R3:R13,_xlfn.RANDARRAY(ROWS(R3:R13)))</f>
-        <v>2.1</v>
+        <v>0.95</v>
       </c>
       <c r="S29" s="1">
         <f t="array" aca="1" ref="S29:S39" ca="1">_xlfn.SORTBY(S3:S13,_xlfn.RANDARRAY(ROWS(S3:S13)))</f>
-        <v>1.1599999999999999</v>
+        <v>1.23</v>
       </c>
       <c r="T29" s="1">
         <f t="array" aca="1" ref="T29:T39" ca="1">_xlfn.SORTBY(T3:T13,_xlfn.RANDARRAY(ROWS(T3:T13)))</f>
-        <v>-0.1</v>
+        <v>-1.1599999999999999</v>
       </c>
       <c r="U29" s="1">
         <f t="array" aca="1" ref="U29:U39" ca="1">_xlfn.SORTBY(U3:U13,_xlfn.RANDARRAY(ROWS(U3:U13)))</f>
-        <v>-0.95999999999999985</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.35">
@@ -2142,83 +2145,83 @@
       </c>
       <c r="B30" s="1">
         <f ca="1"/>
+        <v>2</v>
+      </c>
+      <c r="C30" s="1">
+        <f ca="1"/>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D30" s="1">
+        <f ca="1"/>
+        <v>-0.2</v>
+      </c>
+      <c r="E30" s="1">
+        <f ca="1"/>
+        <v>0.40000000000000008</v>
+      </c>
+      <c r="F30" s="1">
+        <f ca="1"/>
+        <v>-1</v>
+      </c>
+      <c r="G30" s="1">
+        <f ca="1"/>
+        <v>-0.8</v>
+      </c>
+      <c r="H30" s="1">
+        <f ca="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="I30" s="1">
+        <f ca="1"/>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="J30" s="1">
+        <f ca="1"/>
+        <v>-0.70000000000000007</v>
+      </c>
+      <c r="K30" s="1">
+        <f ca="1"/>
+        <v>-1.5</v>
+      </c>
+      <c r="L30" s="1">
+        <f ca="1"/>
+        <v>0.85</v>
+      </c>
+      <c r="M30" s="1">
+        <f ca="1"/>
+        <v>1.08</v>
+      </c>
+      <c r="N30" s="1">
+        <f ca="1"/>
+        <v>-0.12</v>
+      </c>
+      <c r="O30" s="1">
+        <f ca="1"/>
+        <v>5.0000000000000037E-2</v>
+      </c>
+      <c r="P30" s="1">
+        <f ca="1"/>
         <v>0</v>
       </c>
-      <c r="C30" s="1">
-        <f ca="1"/>
-        <v>1.2</v>
-      </c>
-      <c r="D30" s="1">
-        <f ca="1"/>
-        <v>0.2</v>
-      </c>
-      <c r="E30" s="1">
-        <f ca="1"/>
-        <v>-0.4</v>
-      </c>
-      <c r="F30" s="1">
-        <f ca="1"/>
-        <v>-1.4</v>
-      </c>
-      <c r="G30" s="1">
-        <f ca="1"/>
-        <v>-0.8</v>
-      </c>
-      <c r="H30" s="1">
-        <f ca="1"/>
-        <v>0.5</v>
-      </c>
-      <c r="I30" s="1">
-        <f ca="1"/>
-        <v>1.4</v>
-      </c>
-      <c r="J30" s="1">
-        <f ca="1"/>
-        <v>-1.1000000000000001</v>
-      </c>
-      <c r="K30" s="1">
-        <f ca="1"/>
-        <v>-0.9</v>
-      </c>
-      <c r="L30" s="1">
-        <f ca="1"/>
-        <v>0.86</v>
-      </c>
-      <c r="M30" s="1">
-        <f ca="1"/>
-        <v>0</v>
-      </c>
-      <c r="N30" s="1">
-        <f ca="1"/>
-        <v>-0.14000000000000001</v>
-      </c>
-      <c r="O30" s="1">
-        <f ca="1"/>
-        <v>6.0000000000000053E-2</v>
-      </c>
-      <c r="P30" s="1">
-        <f ca="1"/>
-        <v>-1.06</v>
-      </c>
       <c r="Q30" s="1">
         <f ca="1"/>
-        <v>-0.94</v>
+        <v>-0.84999999999999987</v>
       </c>
       <c r="R30" s="1">
         <f ca="1"/>
-        <v>0.98</v>
+        <v>1.01</v>
       </c>
       <c r="S30" s="1">
         <f ca="1"/>
-        <v>1.22</v>
+        <v>0.1</v>
       </c>
       <c r="T30" s="1">
         <f ca="1"/>
-        <v>-1.1499999999999999</v>
+        <v>-1.25</v>
       </c>
       <c r="U30" s="1">
         <f ca="1"/>
-        <v>-1.05</v>
+        <v>-0.96999999999999986</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.35">
@@ -2227,7 +2230,7 @@
       </c>
       <c r="B31" s="1">
         <f ca="1"/>
-        <v>1.4</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="C31" s="1">
         <f ca="1"/>
@@ -2235,75 +2238,75 @@
       </c>
       <c r="D31" s="1">
         <f ca="1"/>
-        <v>0.59999999999999987</v>
+        <v>-1</v>
       </c>
       <c r="E31" s="1">
         <f ca="1"/>
-        <v>-0.1000000000000001</v>
+        <v>-0.20000000000000009</v>
       </c>
       <c r="F31" s="1">
         <f ca="1"/>
-        <v>-1</v>
+        <v>-0.60000000000000009</v>
       </c>
       <c r="G31" s="1">
         <f ca="1"/>
-        <v>-1.3</v>
+        <v>-1.2</v>
       </c>
       <c r="H31" s="1">
         <f ca="1"/>
+        <v>1.5</v>
+      </c>
+      <c r="I31" s="1">
+        <f ca="1"/>
+        <v>1.2</v>
+      </c>
+      <c r="J31" s="1">
+        <f ca="1"/>
+        <v>-0.50000000000000011</v>
+      </c>
+      <c r="K31" s="1">
+        <f ca="1"/>
+        <v>-0.79999999999999993</v>
+      </c>
+      <c r="L31" s="1">
+        <f ca="1"/>
+        <v>0.88</v>
+      </c>
+      <c r="M31" s="1">
+        <f ca="1"/>
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="N31" s="1">
+        <f ca="1"/>
+        <v>-0.15</v>
+      </c>
+      <c r="O31" s="1">
+        <f ca="1"/>
+        <v>0.1400000000000001</v>
+      </c>
+      <c r="P31" s="1">
+        <f ca="1"/>
+        <v>-1.1499999999999999</v>
+      </c>
+      <c r="Q31" s="1">
+        <f ca="1"/>
+        <v>-0.87999999999999989</v>
+      </c>
+      <c r="R31" s="1">
+        <f ca="1"/>
         <v>2.1</v>
       </c>
-      <c r="I31" s="1">
-        <f ca="1"/>
-        <v>1.2</v>
-      </c>
-      <c r="J31" s="1">
-        <f ca="1"/>
-        <v>-1.3</v>
-      </c>
-      <c r="K31" s="1">
-        <f ca="1"/>
-        <v>-1.1000000000000001</v>
-      </c>
-      <c r="L31" s="1">
-        <f ca="1"/>
-        <v>0.92</v>
-      </c>
-      <c r="M31" s="1">
-        <f ca="1"/>
-        <v>1.1399999999999999</v>
-      </c>
-      <c r="N31" s="1">
-        <f ca="1"/>
-        <v>-0.11</v>
-      </c>
-      <c r="O31" s="1">
-        <f ca="1"/>
-        <v>8.0000000000000071E-2</v>
-      </c>
-      <c r="P31" s="1">
-        <f ca="1"/>
-        <v>-1.05</v>
-      </c>
-      <c r="Q31" s="1">
-        <f ca="1"/>
-        <v>-0.87999999999999989</v>
-      </c>
-      <c r="R31" s="1">
-        <f ca="1"/>
-        <v>1.01</v>
-      </c>
       <c r="S31" s="1">
         <f ca="1"/>
-        <v>1.1499999999999999</v>
+        <v>1.24</v>
       </c>
       <c r="T31" s="1">
         <f ca="1"/>
-        <v>-1.19</v>
+        <v>-1.22</v>
       </c>
       <c r="U31" s="1">
         <f ca="1"/>
-        <v>-2.1</v>
+        <v>-0.95999999999999985</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.35">
@@ -2312,23 +2315,23 @@
       </c>
       <c r="B32" s="1">
         <f ca="1"/>
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="C32" s="1">
         <f ca="1"/>
-        <v>0.89999999999999991</v>
+        <v>0.99999999999999989</v>
       </c>
       <c r="D32" s="1">
         <f ca="1"/>
-        <v>0.99999999999999978</v>
+        <v>-0.6</v>
       </c>
       <c r="E32" s="1">
         <f ca="1"/>
-        <v>9.9999999999999867E-2</v>
+        <v>0</v>
       </c>
       <c r="F32" s="1">
         <f ca="1"/>
-        <v>0</v>
+        <v>-1.4</v>
       </c>
       <c r="G32" s="1">
         <f ca="1"/>
@@ -2336,59 +2339,59 @@
       </c>
       <c r="H32" s="1">
         <f ca="1"/>
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="I32" s="1">
         <f ca="1"/>
-        <v>0.7</v>
+        <v>0.99999999999999989</v>
       </c>
       <c r="J32" s="1">
         <f ca="1"/>
-        <v>-0.9</v>
+        <v>-1.3</v>
       </c>
       <c r="K32" s="1">
         <f ca="1"/>
-        <v>-1.6</v>
+        <v>-1.3</v>
       </c>
       <c r="L32" s="1">
         <f ca="1"/>
-        <v>0.94000000000000006</v>
+        <v>0.92</v>
       </c>
       <c r="M32" s="1">
         <f ca="1"/>
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N32" s="1">
         <f ca="1"/>
-        <v>-7.999999999999996E-2</v>
+        <v>-4.9999999999999933E-2</v>
       </c>
       <c r="O32" s="1">
         <f ca="1"/>
-        <v>0.13000000000000009</v>
+        <v>7.0000000000000062E-2</v>
       </c>
       <c r="P32" s="1">
         <f ca="1"/>
-        <v>-1.1100000000000001</v>
+        <v>-1.06</v>
       </c>
       <c r="Q32" s="1">
         <f ca="1"/>
-        <v>-0.90999999999999992</v>
+        <v>-0.95</v>
       </c>
       <c r="R32" s="1">
         <f ca="1"/>
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="S32" s="1">
         <f ca="1"/>
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="T32" s="1">
         <f ca="1"/>
-        <v>-1.21</v>
+        <v>-1.24</v>
       </c>
       <c r="U32" s="1">
         <f ca="1"/>
-        <v>-1.02</v>
+        <v>-1.03</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.35">
@@ -2397,47 +2400,47 @@
       </c>
       <c r="B33" s="1">
         <f ca="1"/>
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="C33" s="1">
         <f ca="1"/>
-        <v>1.3</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="D33" s="1">
         <f ca="1"/>
-        <v>0.79999999999999982</v>
+        <v>-0.8</v>
       </c>
       <c r="E33" s="1">
         <f ca="1"/>
-        <v>-0.5</v>
+        <v>-0.1000000000000001</v>
       </c>
       <c r="F33" s="1">
         <f ca="1"/>
-        <v>-0.40000000000000008</v>
+        <v>-0.20000000000000021</v>
       </c>
       <c r="G33" s="1">
         <f ca="1"/>
-        <v>-1.4</v>
+        <v>-0.7</v>
       </c>
       <c r="H33" s="1">
         <f ca="1"/>
-        <v>0.70000000000000007</v>
+        <v>1.9</v>
       </c>
       <c r="I33" s="1">
         <f ca="1"/>
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J33" s="1">
         <f ca="1"/>
-        <v>-1.5</v>
+        <v>-2.1</v>
       </c>
       <c r="K33" s="1">
         <f ca="1"/>
-        <v>-0.79999999999999993</v>
+        <v>-1</v>
       </c>
       <c r="L33" s="1">
         <f ca="1"/>
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="M33" s="1">
         <f ca="1"/>
@@ -2445,35 +2448,35 @@
       </c>
       <c r="N33" s="1">
         <f ca="1"/>
-        <v>-0.13</v>
+        <v>-0.11</v>
       </c>
       <c r="O33" s="1">
         <f ca="1"/>
-        <v>0.12000000000000011</v>
+        <v>8.0000000000000071E-2</v>
       </c>
       <c r="P33" s="1">
         <f ca="1"/>
-        <v>-1.1200000000000001</v>
+        <v>-1.1299999999999999</v>
       </c>
       <c r="Q33" s="1">
         <f ca="1"/>
-        <v>-0.86999999999999988</v>
+        <v>-0.8899999999999999</v>
       </c>
       <c r="R33" s="1">
         <f ca="1"/>
-        <v>0.95</v>
+        <v>1.03</v>
       </c>
       <c r="S33" s="1">
         <f ca="1"/>
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="T33" s="1">
         <f ca="1"/>
-        <v>-1.25</v>
+        <v>-1.23</v>
       </c>
       <c r="U33" s="1">
         <f ca="1"/>
-        <v>-1.01</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.35">
@@ -2482,39 +2485,39 @@
       </c>
       <c r="B34" s="1">
         <f ca="1"/>
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="C34" s="1">
         <f ca="1"/>
-        <v>1.1000000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="D34" s="1">
         <f ca="1"/>
-        <v>-0.39999999999999991</v>
+        <v>0.2</v>
       </c>
       <c r="E34" s="1">
         <f ca="1"/>
-        <v>0.40000000000000008</v>
+        <v>0.3</v>
       </c>
       <c r="F34" s="1">
         <f ca="1"/>
-        <v>-1.2</v>
+        <v>-1.6</v>
       </c>
       <c r="G34" s="1">
         <f ca="1"/>
-        <v>-0.7</v>
+        <v>-1.4</v>
       </c>
       <c r="H34" s="1">
         <f ca="1"/>
-        <v>1.1000000000000001</v>
+        <v>0.70000000000000007</v>
       </c>
       <c r="I34" s="1">
         <f ca="1"/>
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J34" s="1">
         <f ca="1"/>
-        <v>-1.9</v>
+        <v>-1.5</v>
       </c>
       <c r="K34" s="1">
         <f ca="1"/>
@@ -2522,43 +2525,43 @@
       </c>
       <c r="L34" s="1">
         <f ca="1"/>
-        <v>0.93</v>
+        <v>0.95000000000000007</v>
       </c>
       <c r="M34" s="1">
         <f ca="1"/>
-        <v>1.06</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="N34" s="1">
         <f ca="1"/>
-        <v>-4.9999999999999933E-2</v>
+        <v>-0.13</v>
       </c>
       <c r="O34" s="1">
         <f ca="1"/>
-        <v>0.1400000000000001</v>
+        <v>9.000000000000008E-2</v>
       </c>
       <c r="P34" s="1">
         <f ca="1"/>
-        <v>-1.0900000000000001</v>
+        <v>-1.1200000000000001</v>
       </c>
       <c r="Q34" s="1">
         <f ca="1"/>
-        <v>-0.8899999999999999</v>
+        <v>-0.85999999999999988</v>
       </c>
       <c r="R34" s="1">
         <f ca="1"/>
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="S34" s="1">
         <f ca="1"/>
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="T34" s="1">
         <f ca="1"/>
-        <v>-1.24</v>
+        <v>-1.21</v>
       </c>
       <c r="U34" s="1">
         <f ca="1"/>
-        <v>-0.97999999999999987</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.35">
@@ -2567,15 +2570,15 @@
       </c>
       <c r="B35" s="1">
         <f ca="1"/>
-        <v>0.60000000000000009</v>
+        <v>0.2</v>
       </c>
       <c r="C35" s="1">
         <f ca="1"/>
-        <v>0.79999999999999993</v>
+        <v>1.2</v>
       </c>
       <c r="D35" s="1">
         <f ca="1"/>
-        <v>0.39999999999999991</v>
+        <v>0</v>
       </c>
       <c r="E35" s="1">
         <f ca="1"/>
@@ -2583,11 +2586,11 @@
       </c>
       <c r="F35" s="1">
         <f ca="1"/>
-        <v>-1.8</v>
+        <v>-0.8</v>
       </c>
       <c r="G35" s="1">
         <f ca="1"/>
-        <v>-1.5</v>
+        <v>-1.3</v>
       </c>
       <c r="H35" s="1">
         <f ca="1"/>
@@ -2599,27 +2602,27 @@
       </c>
       <c r="J35" s="1">
         <f ca="1"/>
-        <v>-2.1</v>
+        <v>-0.30000000000000021</v>
       </c>
       <c r="K35" s="1">
         <f ca="1"/>
-        <v>-1.3</v>
+        <v>-0.69999999999999984</v>
       </c>
       <c r="L35" s="1">
         <f ca="1"/>
-        <v>0.87</v>
+        <v>0.94000000000000006</v>
       </c>
       <c r="M35" s="1">
         <f ca="1"/>
-        <v>1.0900000000000001</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="N35" s="1">
         <f ca="1"/>
-        <v>-0.15</v>
+        <v>-6.9999999999999951E-2</v>
       </c>
       <c r="O35" s="1">
         <f ca="1"/>
-        <v>9.000000000000008E-2</v>
+        <v>6.0000000000000053E-2</v>
       </c>
       <c r="P35" s="1">
         <f ca="1"/>
@@ -2627,7 +2630,7 @@
       </c>
       <c r="Q35" s="1">
         <f ca="1"/>
-        <v>-0.91999999999999993</v>
+        <v>-0.86999999999999988</v>
       </c>
       <c r="R35" s="1">
         <f ca="1"/>
@@ -2639,11 +2642,11 @@
       </c>
       <c r="T35" s="1">
         <f ca="1"/>
-        <v>-1.18</v>
+        <v>-1.17</v>
       </c>
       <c r="U35" s="1">
         <f ca="1"/>
-        <v>-0.98999999999999988</v>
+        <v>-0.94999999999999984</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.35">
@@ -2652,79 +2655,79 @@
       </c>
       <c r="B36" s="1">
         <f ca="1"/>
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="C36" s="1">
         <f ca="1"/>
-        <v>0.99999999999999989</v>
+        <v>1.4</v>
       </c>
       <c r="D36" s="1">
         <f ca="1"/>
-        <v>-0.8</v>
+        <v>-0.39999999999999991</v>
       </c>
       <c r="E36" s="1">
         <f ca="1"/>
-        <v>-0.3</v>
+        <v>0.50000000000000022</v>
       </c>
       <c r="F36" s="1">
         <f ca="1"/>
-        <v>-2</v>
+        <v>-0.40000000000000008</v>
       </c>
       <c r="G36" s="1">
         <f ca="1"/>
-        <v>-0.49999999999999978</v>
+        <v>-1.1000000000000001</v>
       </c>
       <c r="H36" s="1">
         <f ca="1"/>
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="I36" s="1">
         <f ca="1"/>
-        <v>0.99999999999999989</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="J36" s="1">
         <f ca="1"/>
-        <v>-0.50000000000000011</v>
+        <v>-0.9</v>
       </c>
       <c r="K36" s="1">
         <f ca="1"/>
-        <v>-0.59999999999999976</v>
+        <v>-1.1000000000000001</v>
       </c>
       <c r="L36" s="1">
         <f ca="1"/>
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="M36" s="1">
         <f ca="1"/>
-        <v>1.1100000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="N36" s="1">
         <f ca="1"/>
-        <v>-6.9999999999999951E-2</v>
+        <v>-8.9999999999999969E-2</v>
       </c>
       <c r="O36" s="1">
         <f ca="1"/>
-        <v>5.0000000000000037E-2</v>
+        <v>-1</v>
       </c>
       <c r="P36" s="1">
         <f ca="1"/>
-        <v>-1.1299999999999999</v>
+        <v>-1.1100000000000001</v>
       </c>
       <c r="Q36" s="1">
         <f ca="1"/>
-        <v>-0.85999999999999988</v>
+        <v>-0.90999999999999992</v>
       </c>
       <c r="R36" s="1">
         <f ca="1"/>
-        <v>1.05</v>
+        <v>0.97</v>
       </c>
       <c r="S36" s="1">
         <f ca="1"/>
-        <v>1.24</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="T36" s="1">
         <f ca="1"/>
-        <v>-1.1599999999999999</v>
+        <v>-0.1</v>
       </c>
       <c r="U36" s="1">
         <f ca="1"/>
@@ -2737,7 +2740,7 @@
       </c>
       <c r="B37" s="1">
         <f ca="1"/>
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="C37" s="1">
         <f ca="1"/>
@@ -2745,75 +2748,75 @@
       </c>
       <c r="D37" s="1">
         <f ca="1"/>
+        <v>0.39999999999999991</v>
+      </c>
+      <c r="E37" s="1">
+        <f ca="1"/>
+        <v>-0.3</v>
+      </c>
+      <c r="F37" s="1">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="G37" s="1">
+        <f ca="1"/>
         <v>-1</v>
       </c>
-      <c r="E37" s="1">
-        <f ca="1"/>
-        <v>0</v>
-      </c>
-      <c r="F37" s="1">
-        <f ca="1"/>
-        <v>-0.8</v>
-      </c>
-      <c r="G37" s="1">
-        <f ca="1"/>
-        <v>-1.2</v>
-      </c>
       <c r="H37" s="1">
         <f ca="1"/>
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="I37" s="1">
         <f ca="1"/>
-        <v>0.89999999999999991</v>
+        <v>1.5</v>
       </c>
       <c r="J37" s="1">
         <f ca="1"/>
-        <v>-0.30000000000000021</v>
+        <v>-0.1</v>
       </c>
       <c r="K37" s="1">
         <f ca="1"/>
-        <v>-0.69999999999999984</v>
+        <v>-1.6</v>
       </c>
       <c r="L37" s="1">
         <f ca="1"/>
-        <v>0.95000000000000007</v>
+        <v>2</v>
       </c>
       <c r="M37" s="1">
         <f ca="1"/>
-        <v>1.1200000000000001</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="N37" s="1">
         <f ca="1"/>
-        <v>1</v>
+        <v>-0.14000000000000001</v>
       </c>
       <c r="O37" s="1">
         <f ca="1"/>
-        <v>0.1100000000000001</v>
+        <v>0.15000000000000011</v>
       </c>
       <c r="P37" s="1">
         <f ca="1"/>
-        <v>-1.1399999999999999</v>
+        <v>-1.08</v>
       </c>
       <c r="Q37" s="1">
         <f ca="1"/>
-        <v>-0.95</v>
+        <v>-2</v>
       </c>
       <c r="R37" s="1">
         <f ca="1"/>
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="S37" s="1">
         <f ca="1"/>
-        <v>1.19</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="T37" s="1">
         <f ca="1"/>
-        <v>-1.22</v>
+        <v>-1.18</v>
       </c>
       <c r="U37" s="1">
         <f ca="1"/>
-        <v>-0.96999999999999986</v>
+        <v>-0.98999999999999988</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.35">
@@ -2822,7 +2825,7 @@
       </c>
       <c r="B38" s="1">
         <f ca="1"/>
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="C38" s="1">
         <f ca="1"/>
@@ -2830,31 +2833,31 @@
       </c>
       <c r="D38" s="1">
         <f ca="1"/>
-        <v>-0.2</v>
+        <v>0.59999999999999987</v>
       </c>
       <c r="E38" s="1">
         <f ca="1"/>
-        <v>0.3</v>
+        <v>-0.5</v>
       </c>
       <c r="F38" s="1">
         <f ca="1"/>
-        <v>-0.60000000000000009</v>
+        <v>-1.8</v>
       </c>
       <c r="G38" s="1">
         <f ca="1"/>
-        <v>-1</v>
+        <v>-1.5</v>
       </c>
       <c r="H38" s="1">
         <f ca="1"/>
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="I38" s="1">
         <f ca="1"/>
-        <v>1.1000000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="J38" s="1">
         <f ca="1"/>
-        <v>-0.1</v>
+        <v>-1.1000000000000001</v>
       </c>
       <c r="K38" s="1">
         <f ca="1"/>
@@ -2862,43 +2865,43 @@
       </c>
       <c r="L38" s="1">
         <f ca="1"/>
-        <v>0.88</v>
+        <v>0.93</v>
       </c>
       <c r="M38" s="1">
         <f ca="1"/>
-        <v>1.05</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="N38" s="1">
         <f ca="1"/>
-        <v>-5.9999999999999942E-2</v>
+        <v>-7.999999999999996E-2</v>
       </c>
       <c r="O38" s="1">
         <f ca="1"/>
-        <v>7.0000000000000062E-2</v>
+        <v>0.13000000000000009</v>
       </c>
       <c r="P38" s="1">
         <f ca="1"/>
+        <v>-1.0900000000000001</v>
+      </c>
+      <c r="Q38" s="1">
+        <f ca="1"/>
+        <v>-0.92999999999999994</v>
+      </c>
+      <c r="R38" s="1">
+        <f ca="1"/>
+        <v>1.02</v>
+      </c>
+      <c r="S38" s="1">
+        <f ca="1"/>
+        <v>1.22</v>
+      </c>
+      <c r="T38" s="1">
+        <f ca="1"/>
         <v>-1.1499999999999999</v>
       </c>
-      <c r="Q38" s="1">
-        <f ca="1"/>
-        <v>-0.92999999999999994</v>
-      </c>
-      <c r="R38" s="1">
-        <f ca="1"/>
-        <v>1.03</v>
-      </c>
-      <c r="S38" s="1">
-        <f ca="1"/>
-        <v>0.1</v>
-      </c>
-      <c r="T38" s="1">
-        <f ca="1"/>
-        <v>-1.17</v>
-      </c>
       <c r="U38" s="1">
         <f ca="1"/>
-        <v>-1.03</v>
+        <v>-1.02</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.35">
@@ -2907,31 +2910,31 @@
       </c>
       <c r="B39" s="1">
         <f ca="1"/>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="C39" s="1">
         <f ca="1"/>
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="D39" s="1">
         <f ca="1"/>
-        <v>-0.6</v>
+        <v>0.99999999999999978</v>
       </c>
       <c r="E39" s="1">
         <f ca="1"/>
-        <v>0.50000000000000022</v>
+        <v>-0.4</v>
       </c>
       <c r="F39" s="1">
         <f ca="1"/>
-        <v>-1.6</v>
+        <v>-1.2</v>
       </c>
       <c r="G39" s="1">
         <f ca="1"/>
-        <v>-0.59999999999999987</v>
+        <v>-0.49999999999999978</v>
       </c>
       <c r="H39" s="1">
         <f ca="1"/>
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="I39" s="1">
         <f ca="1"/>
@@ -2943,7 +2946,7 @@
       </c>
       <c r="K39" s="1">
         <f ca="1"/>
-        <v>-1.5</v>
+        <v>-0.9</v>
       </c>
       <c r="L39" s="1">
         <f ca="1"/>
@@ -2951,39 +2954,39 @@
       </c>
       <c r="M39" s="1">
         <f ca="1"/>
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="N39" s="1">
         <f ca="1"/>
-        <v>-8.9999999999999969E-2</v>
+        <v>-5.9999999999999942E-2</v>
       </c>
       <c r="O39" s="1">
         <f ca="1"/>
-        <v>-1</v>
+        <v>0.1100000000000001</v>
       </c>
       <c r="P39" s="1">
         <f ca="1"/>
-        <v>0</v>
+        <v>-1.1399999999999999</v>
       </c>
       <c r="Q39" s="1">
         <f ca="1"/>
-        <v>-0.84999999999999987</v>
+        <v>-0.91999999999999993</v>
       </c>
       <c r="R39" s="1">
         <f ca="1"/>
-        <v>0.96</v>
+        <v>0.99</v>
       </c>
       <c r="S39" s="1">
         <f ca="1"/>
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="T39" s="1">
         <f ca="1"/>
-        <v>-1.23</v>
+        <v>-1.19</v>
       </c>
       <c r="U39" s="1">
         <f ca="1"/>
-        <v>-0.94999999999999984</v>
+        <v>-0.97999999999999987</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.35">
@@ -2992,7 +2995,7 @@
       </c>
       <c r="B41" s="1">
         <f t="shared" ref="B41:U41" ca="1" si="6">AVERAGE(B29:B39)</f>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="C41" s="1">
         <f t="shared" ca="1" si="6"/>
@@ -3012,11 +3015,11 @@
       </c>
       <c r="G41" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>-0.99999999999999989</v>
+        <v>-1</v>
       </c>
       <c r="H41" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>1.1000000000000001</v>
+        <v>1.0999999999999999</v>
       </c>
       <c r="I41" s="1">
         <f t="shared" ca="1" si="6"/>
@@ -3036,7 +3039,7 @@
       </c>
       <c r="M41" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>1.0000000000000002</v>
+        <v>0.99999999999999989</v>
       </c>
       <c r="N41" s="1">
         <f t="shared" ca="1" si="6"/>
@@ -3044,7 +3047,7 @@
       </c>
       <c r="O41" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>7.5697024406260668E-17</v>
       </c>
       <c r="P41" s="1">
         <f t="shared" ca="1" si="6"/>
@@ -3056,7 +3059,7 @@
       </c>
       <c r="R41" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>1.0999999999999999</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="S41" s="1">
         <f t="shared" ca="1" si="6"/>
@@ -3064,7 +3067,7 @@
       </c>
       <c r="T41" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>-1.1000000000000001</v>
+        <v>-1.0999999999999999</v>
       </c>
       <c r="U41" s="1">
         <f t="shared" ca="1" si="6"/>
@@ -3077,11 +3080,11 @@
       </c>
       <c r="B42" s="4">
         <f t="shared" ref="B42:U42" ca="1" si="7">_xlfn.STDEV.P(B29:B39)</f>
-        <v>0.63245553203367566</v>
+        <v>0.63245553203367544</v>
       </c>
       <c r="C42" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>0.31622776601683844</v>
+        <v>0.31622776601683805</v>
       </c>
       <c r="D42" s="4">
         <f t="shared" ca="1" si="7"/>
@@ -3093,19 +3096,19 @@
       </c>
       <c r="F42" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>0.63245553203367588</v>
+        <v>0.6324555320336761</v>
       </c>
       <c r="G42" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>0.31622776601683844</v>
+        <v>0.31622776601683783</v>
       </c>
       <c r="H42" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>0.63245553203367566</v>
+        <v>0.63245553203367588</v>
       </c>
       <c r="I42" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>0.31622776601683783</v>
+        <v>0.31622776601683822</v>
       </c>
       <c r="J42" s="4">
         <f t="shared" ca="1" si="7"/>
@@ -3113,7 +3116,7 @@
       </c>
       <c r="K42" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>0.31622776601683861</v>
+        <v>0.31622776601683822</v>
       </c>
       <c r="L42" s="1">
         <f t="shared" ca="1" si="7"/>
@@ -3121,11 +3124,11 @@
       </c>
       <c r="M42" s="1">
         <f t="shared" ca="1" si="7"/>
-        <v>0.31780497164141358</v>
+        <v>0.31780497164141469</v>
       </c>
       <c r="N42" s="1">
         <f t="shared" ca="1" si="7"/>
-        <v>0.31780497164141408</v>
+        <v>0.31780497164141402</v>
       </c>
       <c r="O42" s="1">
         <f t="shared" ca="1" si="7"/>
@@ -3141,19 +3144,19 @@
       </c>
       <c r="R42" s="1">
         <f t="shared" ca="1" si="7"/>
-        <v>0.31780497164141486</v>
+        <v>0.31780497164141336</v>
       </c>
       <c r="S42" s="1">
         <f t="shared" ca="1" si="7"/>
-        <v>0.31780497164141486</v>
+        <v>0.31780497164141414</v>
       </c>
       <c r="T42" s="1">
         <f t="shared" ca="1" si="7"/>
-        <v>0.31780497164141375</v>
+        <v>0.31780497164141414</v>
       </c>
       <c r="U42" s="1">
         <f t="shared" ca="1" si="7"/>
-        <v>0.31780497164141486</v>
+        <v>0.31780497164141414</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.35">
@@ -3162,35 +3165,35 @@
       </c>
       <c r="B43" s="1">
         <f t="shared" ref="B43:U43" ca="1" si="8">_xlfn.SKEW.P(B29:B39)</f>
-        <v>3.0278809762504267E-17</v>
+        <v>-1.0389416599759277E-15</v>
       </c>
       <c r="C43" s="1">
         <f t="shared" ca="1" si="8"/>
-        <v>8.4780667335011958E-16</v>
+        <v>7.2669143430010251E-16</v>
       </c>
       <c r="D43" s="1">
         <f t="shared" ca="1" si="8"/>
-        <v>-4.339962732625612E-16</v>
+        <v>-5.2483270255007403E-16</v>
       </c>
       <c r="E43" s="1">
         <f t="shared" ca="1" si="8"/>
-        <v>4.0371746350005691E-16</v>
+        <v>4.8446095620006827E-16</v>
       </c>
       <c r="F43" s="1">
         <f t="shared" ca="1" si="8"/>
-        <v>-4.1381040008755832E-16</v>
+        <v>-2.7124767078910076E-16</v>
       </c>
       <c r="G43" s="1">
         <f t="shared" ca="1" si="8"/>
-        <v>-2.4223047810003414E-16</v>
+        <v>7.6706318065010816E-16</v>
       </c>
       <c r="H43" s="1">
         <f t="shared" ca="1" si="8"/>
-        <v>-3.6334571715005125E-16</v>
+        <v>6.4531713306337224E-16</v>
       </c>
       <c r="I43" s="1">
         <f t="shared" ca="1" si="8"/>
-        <v>1.1909665173251679E-15</v>
+        <v>1.1304088978001594E-15</v>
       </c>
       <c r="J43" s="1">
         <f t="shared" ca="1" si="8"/>
@@ -3198,27 +3201,27 @@
       </c>
       <c r="K43" s="1">
         <f t="shared" ca="1" si="8"/>
-        <v>-5.6520444890007968E-16</v>
+        <v>-6.7118028306884468E-16</v>
       </c>
       <c r="L43" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>2.794540334892154</v>
+        <v>2.7945403348921536</v>
       </c>
       <c r="M43" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>-2.794540334892154</v>
+        <v>-2.7945403348921505</v>
       </c>
       <c r="N43" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>2.7945403348921518</v>
+        <v>2.7945403348921531</v>
       </c>
       <c r="O43" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>-2.7945403348921518</v>
+        <v>-2.7945403348921523</v>
       </c>
       <c r="P43" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>2.7945403348921536</v>
+        <v>2.794540334892154</v>
       </c>
       <c r="Q43" s="4">
         <f t="shared" ca="1" si="8"/>
@@ -3226,15 +3229,15 @@
       </c>
       <c r="R43" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>2.794540334892154</v>
+        <v>2.7945403348921518</v>
       </c>
       <c r="S43" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>-2.7945403348921505</v>
+        <v>-2.7945403348921518</v>
       </c>
       <c r="T43" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>2.794540334892154</v>
+        <v>2.7945403348921518</v>
       </c>
       <c r="U43" s="4">
         <f t="shared" ca="1" si="8"/>
@@ -3251,11 +3254,11 @@
       </c>
       <c r="C44" s="1">
         <f t="shared" ca="1" si="9"/>
-        <v>-1.200000000000002</v>
+        <v>-1.2000000000000015</v>
       </c>
       <c r="D44" s="1">
         <f t="shared" ca="1" si="9"/>
-        <v>-1.2000000000000011</v>
+        <v>-1.1999999999999997</v>
       </c>
       <c r="E44" s="1">
         <f t="shared" ca="1" si="9"/>
@@ -3271,11 +3274,11 @@
       </c>
       <c r="H44" s="1">
         <f t="shared" ca="1" si="9"/>
-        <v>-1.200000000000002</v>
+        <v>-1.2000000000000002</v>
       </c>
       <c r="I44" s="1">
         <f t="shared" ca="1" si="9"/>
-        <v>-1.2000000000000011</v>
+        <v>-1.2000000000000002</v>
       </c>
       <c r="J44" s="1">
         <f t="shared" ca="1" si="9"/>
@@ -3287,39 +3290,39 @@
       </c>
       <c r="L44" s="1">
         <f t="shared" ca="1" si="9"/>
-        <v>10.711250530993706</v>
+        <v>10.711250530993702</v>
       </c>
       <c r="M44" s="1">
         <f t="shared" ca="1" si="9"/>
-        <v>10.711250530993706</v>
+        <v>10.711250530993684</v>
       </c>
       <c r="N44" s="1">
         <f t="shared" ca="1" si="9"/>
-        <v>10.711250530993684</v>
+        <v>10.711250530993706</v>
       </c>
       <c r="O44" s="1">
         <f t="shared" ca="1" si="9"/>
-        <v>10.711250530993684</v>
+        <v>10.711250530993688</v>
       </c>
       <c r="P44" s="1">
         <f t="shared" ca="1" si="9"/>
-        <v>10.711250530993702</v>
+        <v>10.711250530993706</v>
       </c>
       <c r="Q44" s="1">
         <f t="shared" ca="1" si="9"/>
-        <v>10.711250530993706</v>
+        <v>10.711250530993702</v>
       </c>
       <c r="R44" s="1">
         <f t="shared" ca="1" si="9"/>
-        <v>10.711250530993706</v>
+        <v>10.711250530993688</v>
       </c>
       <c r="S44" s="1">
         <f t="shared" ca="1" si="9"/>
-        <v>10.711250530993684</v>
+        <v>10.711250530993695</v>
       </c>
       <c r="T44" s="1">
         <f t="shared" ca="1" si="9"/>
-        <v>10.711250530993706</v>
+        <v>10.711250530993691</v>
       </c>
       <c r="U44" s="1">
         <f t="shared" ca="1" si="9"/>
@@ -3502,43 +3505,43 @@
       </c>
       <c r="B47" s="1">
         <f ca="1">CORREL(B29:B39,C29:C39)</f>
-        <v>0.12727272727272737</v>
+        <v>-0.21818181818181812</v>
       </c>
       <c r="D47" s="1">
         <f ca="1">CORREL(D29:D39,E29:E39)</f>
-        <v>-0.29090909090909095</v>
+        <v>-0.30909090909090897</v>
       </c>
       <c r="F47" s="1">
         <f ca="1">CORREL(F29:F39,G29:G39)</f>
-        <v>-0.33636363636363636</v>
+        <v>6.3636363636363588E-2</v>
       </c>
       <c r="H47" s="1">
         <f ca="1">CORREL(H29:H39,I29:I39)</f>
-        <v>0.2</v>
+        <v>6.3636363636363519E-2</v>
       </c>
       <c r="J47" s="1">
         <f ca="1">CORREL(J29:J39,K29:K39)</f>
-        <v>0.46363636363636357</v>
+        <v>-0.28181818181818186</v>
       </c>
       <c r="L47" s="1">
         <f ca="1">CORREL(L29:L39,M29:M39)</f>
-        <v>0.18712871287128705</v>
+        <v>0.10126012601260134</v>
       </c>
       <c r="N47" s="1">
         <f ca="1">CORREL(N29:N39,O29:O39)</f>
-        <v>9.9549954995499568E-2</v>
+        <v>0.10513051305130515</v>
       </c>
       <c r="P47" s="1">
         <f ca="1">CORREL(P29:P39,Q29:Q39)</f>
-        <v>0.12934293429342944</v>
+        <v>0.1245724572457247</v>
       </c>
       <c r="R47" s="1">
         <f ca="1">CORREL(R29:R39,S29:S39)</f>
-        <v>2.8352835283528287E-2</v>
+        <v>0.12763276327632767</v>
       </c>
       <c r="T47" s="1">
         <f ca="1">CORREL(T29:T39,U29:U39)</f>
-        <v>0.1224122412241225</v>
+        <v>2.1062106210620948E-2</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.35">
@@ -3547,27 +3550,27 @@
       </c>
       <c r="B48">
         <f t="array" aca="1" ref="B48" ca="1">SUMPRODUCT((B29:B39&gt;C29:C39)*1)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C48">
         <f t="array" aca="1" ref="C48" ca="1">SUMPRODUCT((B29:B39&lt;C29:C39)*1)</f>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D48">
         <f t="array" aca="1" ref="D48" ca="1">SUMPRODUCT((D29:D39&gt;E29:E39)*1)</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E48">
         <f t="array" aca="1" ref="E48" ca="1">SUMPRODUCT((D29:D39&lt;E29:E39)*1)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F48">
         <f t="array" aca="1" ref="F48" ca="1">SUMPRODUCT((F29:F39&gt;G29:G39)*1)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G48">
         <f t="array" aca="1" ref="G48" ca="1">SUMPRODUCT((F29:F39&lt;G29:G39)*1)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H48">
         <f t="array" aca="1" ref="H48" ca="1">SUMPRODUCT((H29:H39&gt;I29:I39)*1)</f>
@@ -3575,15 +3578,15 @@
       </c>
       <c r="I48">
         <f t="array" aca="1" ref="I48" ca="1">SUMPRODUCT((H29:H39&lt;I29:I39)*1)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J48">
         <f t="array" aca="1" ref="J48" ca="1">SUMPRODUCT((J29:J39&gt;K29:K39)*1)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K48">
         <f t="array" aca="1" ref="K48" ca="1">SUMPRODUCT((J29:J39&lt;K29:K39)*1)</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L48">
         <f t="array" aca="1" ref="L48" ca="1">SUMPRODUCT((L29:L39&gt;M29:M39)*1)</f>
@@ -3632,15 +3635,15 @@
       </c>
       <c r="B49" s="6" t="str">
         <f ca="1">IF(B48&gt;C48,"A",IF(C48&gt;B48,"B","Equal"))</f>
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="D49" s="6" t="str">
         <f ca="1">IF(D48&gt;E48,"A",IF(E48&gt;D48,"B","Equal"))</f>
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="F49" s="6" t="str">
         <f ca="1">IF(F48&gt;G48,"A",IF(G48&gt;F48,"B","Equal"))</f>
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="H49" s="6" t="str">
         <f ca="1">IF(H48&gt;I48,"A",IF(I48&gt;H48,"B","Equal"))</f>
@@ -3648,7 +3651,7 @@
       </c>
       <c r="J49" s="6" t="str">
         <f ca="1">IF(J48&gt;K48,"A",IF(K48&gt;J48,"B","Equal"))</f>
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="L49" s="6" t="str">
         <f ca="1">IF(L48&gt;M48,"A",IF(M48&gt;L48,"B","Equal"))</f>
@@ -3681,7 +3684,7 @@
       </c>
       <c r="D50">
         <f ca="1">MAX(D48:E48)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F50">
         <f ca="1">MAX(F48:G48)</f>
@@ -6743,8 +6746,11 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A104" s="8" t="s">
-        <v>24</v>
-      </c>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="105" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A105" s="8"/>
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.35">
       <c r="B106" s="8" t="s">
@@ -6780,7 +6786,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A107" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B107" s="10">
         <v>0.8</v>
@@ -6815,7 +6821,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A108" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B108" s="10">
         <v>0.6</v>
@@ -6850,7 +6856,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A109" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B109" s="10">
         <v>1.4</v>
@@ -6881,6 +6887,41 @@
       </c>
       <c r="T109" s="10">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A110" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B110" s="10">
+        <v>1.2</v>
+      </c>
+      <c r="D110" s="10">
+        <v>1.2</v>
+      </c>
+      <c r="F110" s="10">
+        <v>1.2</v>
+      </c>
+      <c r="H110" s="10">
+        <v>1.2</v>
+      </c>
+      <c r="J110" s="10">
+        <v>1.2</v>
+      </c>
+      <c r="L110" s="10">
+        <v>1.2</v>
+      </c>
+      <c r="N110" s="10">
+        <v>1.2</v>
+      </c>
+      <c r="P110" s="10">
+        <v>1.2</v>
+      </c>
+      <c r="R110" s="10">
+        <v>1.2</v>
+      </c>
+      <c r="T110" s="10">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>
@@ -6890,7 +6931,6 @@
     <mergeCell ref="D54:E54"/>
     <mergeCell ref="P54:Q54"/>
     <mergeCell ref="T54:U54"/>
-    <mergeCell ref="D2:E2"/>
     <mergeCell ref="F80:G80"/>
     <mergeCell ref="N2:O2"/>
     <mergeCell ref="P2:Q2"/>
@@ -6905,14 +6945,15 @@
     <mergeCell ref="L54:M54"/>
     <mergeCell ref="R54:S54"/>
     <mergeCell ref="N28:O28"/>
+    <mergeCell ref="F28:G28"/>
     <mergeCell ref="R28:S28"/>
     <mergeCell ref="J28:K28"/>
     <mergeCell ref="D80:E80"/>
     <mergeCell ref="L28:M28"/>
     <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:G28"/>
     <mergeCell ref="P28:Q28"/>
     <mergeCell ref="H28:I28"/>
     <mergeCell ref="H80:I80"/>

--- a/Distributions.xlsx
+++ b/Distributions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aaltofi-my.sharepoint.com/personal/samuel_salin_aalto_fi/Documents/Desktop/Risk Elicitation/RE/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/svsalin/Desktop/Risk Elicitation/RE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_BA4D2FB74CA8045DC74C1AC6005315D59D888FE4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E53CF80-D76A-45FC-B8D4-F6B92E7F8969}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4561273A-B9FF-774F-B9CF-5D9C1A4A8399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-5160" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21160" yWindow="-28800" windowWidth="68800" windowHeight="28800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All" sheetId="1" r:id="rId1"/>
@@ -544,12 +544,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:AB110"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="198.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="198.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" s="2"/>
       <c r="B2" s="11" t="s">
         <v>0</v>
@@ -592,7 +592,7 @@
       </c>
       <c r="U2" s="12"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B3" s="1">
         <v>0</v>
       </c>
@@ -654,7 +654,7 @@
         <v>-1.05</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B4" s="1">
         <v>0.2</v>
       </c>
@@ -716,7 +716,7 @@
         <v>-1.04</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B5" s="1">
         <v>0.4</v>
       </c>
@@ -778,7 +778,7 @@
         <v>-1.03</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1">
         <v>0.60000000000000009</v>
       </c>
@@ -840,7 +840,7 @@
         <v>-1.02</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B7" s="1">
         <v>0.8</v>
       </c>
@@ -902,7 +902,7 @@
         <v>-1.01</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B8" s="1">
         <v>1</v>
       </c>
@@ -964,7 +964,7 @@
         <v>-0.98999999999999988</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B9" s="1">
         <v>1.2</v>
       </c>
@@ -1026,7 +1026,7 @@
         <v>-0.97999999999999987</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B10" s="1">
         <v>1.4</v>
       </c>
@@ -1088,7 +1088,7 @@
         <v>-0.96999999999999986</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B11" s="1">
         <v>1.6</v>
       </c>
@@ -1150,7 +1150,7 @@
         <v>-0.95999999999999985</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B12" s="1">
         <v>1.8</v>
       </c>
@@ -1212,7 +1212,7 @@
         <v>-0.94999999999999984</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B13" s="1">
         <v>2</v>
       </c>
@@ -1274,7 +1274,7 @@
         <v>-2.1</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -1359,7 +1359,7 @@
         <v>-1.0999999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>11</v>
       </c>
@@ -1444,7 +1444,7 @@
         <v>0.31780497164141486</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>12</v>
       </c>
@@ -1529,7 +1529,7 @@
         <v>-2.7945403348921518</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -1614,7 +1614,7 @@
         <v>10.711250530993691</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>14</v>
       </c>
@@ -1699,7 +1699,7 @@
         <v>-2.1</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>15</v>
       </c>
@@ -1784,7 +1784,7 @@
         <v>-0.94999999999999984</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>16</v>
       </c>
@@ -1829,7 +1829,7 @@
         <v>-0.98019801980197996</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>17</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
         <v>18</v>
       </c>
@@ -1959,7 +1959,7 @@
         <v>B</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>19</v>
       </c>
@@ -2004,12 +2004,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A26" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>21</v>
       </c>
@@ -2054,17 +2054,17 @@
       </c>
       <c r="U28" s="12"/>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>1</v>
       </c>
       <c r="B29" s="1">
         <f t="array" aca="1" ref="B29:B39" ca="1">_xlfn.SORTBY(B3:B13,_xlfn.RANDARRAY(ROWS(B3:B13)))</f>
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="C29" s="1">
         <f t="array" aca="1" ref="C29:C39" ca="1">_xlfn.SORTBY(C3:C13,_xlfn.RANDARRAY(ROWS(C3:C13)))</f>
-        <v>0.79999999999999993</v>
+        <v>1.4</v>
       </c>
       <c r="D29" s="1">
         <f t="array" aca="1" ref="D29:D39" ca="1">_xlfn.SORTBY(D3:D13,_xlfn.RANDARRAY(ROWS(D3:D13)))</f>
@@ -2072,51 +2072,51 @@
       </c>
       <c r="E29" s="1">
         <f t="array" aca="1" ref="E29:E39" ca="1">_xlfn.SORTBY(E3:E13,_xlfn.RANDARRAY(ROWS(E3:E13)))</f>
-        <v>9.9999999999999867E-2</v>
+        <v>-0.4</v>
       </c>
       <c r="F29" s="1">
         <f t="array" aca="1" ref="F29:F39" ca="1">_xlfn.SORTBY(F3:F13,_xlfn.RANDARRAY(ROWS(F3:F13)))</f>
-        <v>-2</v>
+        <v>-0.60000000000000009</v>
       </c>
       <c r="G29" s="1">
         <f t="array" aca="1" ref="G29:G39" ca="1">_xlfn.SORTBY(G3:G13,_xlfn.RANDARRAY(ROWS(G3:G13)))</f>
-        <v>-0.59999999999999987</v>
+        <v>-0.90000000000000013</v>
       </c>
       <c r="H29" s="1">
         <f t="array" aca="1" ref="H29:H39" ca="1">_xlfn.SORTBY(H3:H13,_xlfn.RANDARRAY(ROWS(H3:H13)))</f>
-        <v>1.1000000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="I29" s="1">
         <f t="array" aca="1" ref="I29:I39" ca="1">_xlfn.SORTBY(I3:I13,_xlfn.RANDARRAY(ROWS(I3:I13)))</f>
-        <v>0.79999999999999993</v>
+        <v>0.7</v>
       </c>
       <c r="J29" s="1">
         <f t="array" aca="1" ref="J29:J39" ca="1">_xlfn.SORTBY(J3:J13,_xlfn.RANDARRAY(ROWS(J3:J13)))</f>
-        <v>-1.9</v>
+        <v>-0.9</v>
       </c>
       <c r="K29" s="1">
         <f t="array" aca="1" ref="K29:K39" ca="1">_xlfn.SORTBY(K3:K13,_xlfn.RANDARRAY(ROWS(K3:K13)))</f>
-        <v>-0.59999999999999976</v>
+        <v>-1.5</v>
       </c>
       <c r="L29" s="1">
         <f t="array" aca="1" ref="L29:L39" ca="1">_xlfn.SORTBY(L3:L13,_xlfn.RANDARRAY(ROWS(L3:L13)))</f>
-        <v>0.89</v>
+        <v>0.95000000000000007</v>
       </c>
       <c r="M29" s="1">
         <f t="array" aca="1" ref="M29:M39" ca="1">_xlfn.SORTBY(M3:M13,_xlfn.RANDARRAY(ROWS(M3:M13)))</f>
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N29" s="1">
         <f t="array" aca="1" ref="N29:N39" ca="1">_xlfn.SORTBY(N3:N13,_xlfn.RANDARRAY(ROWS(N3:N13)))</f>
-        <v>1</v>
+        <v>-5.9999999999999942E-2</v>
       </c>
       <c r="O29" s="1">
         <f t="array" aca="1" ref="O29:O39" ca="1">_xlfn.SORTBY(O3:O13,_xlfn.RANDARRAY(ROWS(O3:O13)))</f>
-        <v>0.12000000000000011</v>
+        <v>9.000000000000008E-2</v>
       </c>
       <c r="P29" s="1">
         <f t="array" aca="1" ref="P29:P39" ca="1">_xlfn.SORTBY(P3:P13,_xlfn.RANDARRAY(ROWS(P3:P13)))</f>
-        <v>-1.05</v>
+        <v>-1.07</v>
       </c>
       <c r="Q29" s="1">
         <f t="array" aca="1" ref="Q29:Q39" ca="1">_xlfn.SORTBY(Q3:Q13,_xlfn.RANDARRAY(ROWS(Q3:Q13)))</f>
@@ -2124,22 +2124,22 @@
       </c>
       <c r="R29" s="1">
         <f t="array" aca="1" ref="R29:R39" ca="1">_xlfn.SORTBY(R3:R13,_xlfn.RANDARRAY(ROWS(R3:R13)))</f>
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="S29" s="1">
         <f t="array" aca="1" ref="S29:S39" ca="1">_xlfn.SORTBY(S3:S13,_xlfn.RANDARRAY(ROWS(S3:S13)))</f>
-        <v>1.23</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="T29" s="1">
         <f t="array" aca="1" ref="T29:T39" ca="1">_xlfn.SORTBY(T3:T13,_xlfn.RANDARRAY(ROWS(T3:T13)))</f>
-        <v>-1.1599999999999999</v>
+        <v>-1.18</v>
       </c>
       <c r="U29" s="1">
         <f t="array" aca="1" ref="U29:U39" ca="1">_xlfn.SORTBY(U3:U13,_xlfn.RANDARRAY(ROWS(U3:U13)))</f>
-        <v>-2.1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.35">
+        <v>-0.95999999999999985</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>2</v>
       </c>
@@ -2149,59 +2149,59 @@
       </c>
       <c r="C30" s="1">
         <f ca="1"/>
+        <v>1.2</v>
+      </c>
+      <c r="D30" s="1">
+        <f ca="1"/>
+        <v>-0.39999999999999991</v>
+      </c>
+      <c r="E30" s="1">
+        <f ca="1"/>
+        <v>-0.1000000000000001</v>
+      </c>
+      <c r="F30" s="1">
+        <f ca="1"/>
+        <v>-0.8</v>
+      </c>
+      <c r="G30" s="1">
+        <f ca="1"/>
+        <v>-0.59999999999999987</v>
+      </c>
+      <c r="H30" s="1">
+        <f ca="1"/>
+        <v>1.9</v>
+      </c>
+      <c r="I30" s="1">
+        <f ca="1"/>
         <v>1.1000000000000001</v>
       </c>
-      <c r="D30" s="1">
-        <f ca="1"/>
-        <v>-0.2</v>
-      </c>
-      <c r="E30" s="1">
-        <f ca="1"/>
-        <v>0.40000000000000008</v>
-      </c>
-      <c r="F30" s="1">
-        <f ca="1"/>
-        <v>-1</v>
-      </c>
-      <c r="G30" s="1">
-        <f ca="1"/>
-        <v>-0.8</v>
-      </c>
-      <c r="H30" s="1">
-        <f ca="1"/>
-        <v>0.5</v>
-      </c>
-      <c r="I30" s="1">
-        <f ca="1"/>
-        <v>1.1000000000000001</v>
-      </c>
       <c r="J30" s="1">
         <f ca="1"/>
-        <v>-0.70000000000000007</v>
+        <v>-0.30000000000000021</v>
       </c>
       <c r="K30" s="1">
         <f ca="1"/>
-        <v>-1.5</v>
+        <v>-0.79999999999999993</v>
       </c>
       <c r="L30" s="1">
         <f ca="1"/>
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="M30" s="1">
         <f ca="1"/>
-        <v>1.08</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="N30" s="1">
         <f ca="1"/>
-        <v>-0.12</v>
+        <v>-7.999999999999996E-2</v>
       </c>
       <c r="O30" s="1">
         <f ca="1"/>
-        <v>5.0000000000000037E-2</v>
+        <v>6.0000000000000053E-2</v>
       </c>
       <c r="P30" s="1">
         <f ca="1"/>
-        <v>0</v>
+        <v>-1.05</v>
       </c>
       <c r="Q30" s="1">
         <f ca="1"/>
@@ -2209,28 +2209,28 @@
       </c>
       <c r="R30" s="1">
         <f ca="1"/>
-        <v>1.01</v>
+        <v>0.96</v>
       </c>
       <c r="S30" s="1">
         <f ca="1"/>
-        <v>0.1</v>
+        <v>1.17</v>
       </c>
       <c r="T30" s="1">
         <f ca="1"/>
-        <v>-1.25</v>
+        <v>-1.22</v>
       </c>
       <c r="U30" s="1">
         <f ca="1"/>
         <v>-0.96999999999999986</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>3</v>
       </c>
       <c r="B31" s="1">
         <f ca="1"/>
-        <v>0.60000000000000009</v>
+        <v>0.4</v>
       </c>
       <c r="C31" s="1">
         <f ca="1"/>
@@ -2238,43 +2238,43 @@
       </c>
       <c r="D31" s="1">
         <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="E31" s="1">
+        <f ca="1"/>
+        <v>0.50000000000000022</v>
+      </c>
+      <c r="F31" s="1">
+        <f ca="1"/>
+        <v>-0.40000000000000008</v>
+      </c>
+      <c r="G31" s="1">
+        <f ca="1"/>
+        <v>-0.8</v>
+      </c>
+      <c r="H31" s="1">
+        <f ca="1"/>
+        <v>0.70000000000000007</v>
+      </c>
+      <c r="I31" s="1">
+        <f ca="1"/>
+        <v>0.99999999999999989</v>
+      </c>
+      <c r="J31" s="1">
+        <f ca="1"/>
+        <v>-1.3</v>
+      </c>
+      <c r="K31" s="1">
+        <f ca="1"/>
         <v>-1</v>
       </c>
-      <c r="E31" s="1">
-        <f ca="1"/>
-        <v>-0.20000000000000009</v>
-      </c>
-      <c r="F31" s="1">
-        <f ca="1"/>
-        <v>-0.60000000000000009</v>
-      </c>
-      <c r="G31" s="1">
-        <f ca="1"/>
-        <v>-1.2</v>
-      </c>
-      <c r="H31" s="1">
-        <f ca="1"/>
-        <v>1.5</v>
-      </c>
-      <c r="I31" s="1">
-        <f ca="1"/>
-        <v>1.2</v>
-      </c>
-      <c r="J31" s="1">
-        <f ca="1"/>
-        <v>-0.50000000000000011</v>
-      </c>
-      <c r="K31" s="1">
-        <f ca="1"/>
-        <v>-0.79999999999999993</v>
-      </c>
       <c r="L31" s="1">
         <f ca="1"/>
         <v>0.88</v>
       </c>
       <c r="M31" s="1">
         <f ca="1"/>
-        <v>1.1399999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="N31" s="1">
         <f ca="1"/>
@@ -2290,36 +2290,36 @@
       </c>
       <c r="Q31" s="1">
         <f ca="1"/>
-        <v>-0.87999999999999989</v>
+        <v>-0.85999999999999988</v>
       </c>
       <c r="R31" s="1">
         <f ca="1"/>
-        <v>2.1</v>
+        <v>1.03</v>
       </c>
       <c r="S31" s="1">
         <f ca="1"/>
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="T31" s="1">
         <f ca="1"/>
-        <v>-1.22</v>
+        <v>-1.21</v>
       </c>
       <c r="U31" s="1">
         <f ca="1"/>
-        <v>-0.95999999999999985</v>
-      </c>
-    </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.35">
+        <v>-0.98999999999999988</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>4</v>
       </c>
       <c r="B32" s="1">
         <f ca="1"/>
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="C32" s="1">
         <f ca="1"/>
-        <v>0.99999999999999989</v>
+        <v>0.6</v>
       </c>
       <c r="D32" s="1">
         <f ca="1"/>
@@ -2327,159 +2327,159 @@
       </c>
       <c r="E32" s="1">
         <f ca="1"/>
+        <v>9.9999999999999867E-2</v>
+      </c>
+      <c r="F32" s="1">
+        <f ca="1"/>
+        <v>-1.8</v>
+      </c>
+      <c r="G32" s="1">
+        <f ca="1"/>
+        <v>-1</v>
+      </c>
+      <c r="H32" s="1">
+        <f ca="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="I32" s="1">
+        <f ca="1"/>
+        <v>1.2</v>
+      </c>
+      <c r="J32" s="1">
+        <f ca="1"/>
+        <v>-1.1000000000000001</v>
+      </c>
+      <c r="K32" s="1">
+        <f ca="1"/>
+        <v>-0.59999999999999976</v>
+      </c>
+      <c r="L32" s="1">
+        <f ca="1"/>
+        <v>0.89</v>
+      </c>
+      <c r="M32" s="1">
+        <f ca="1"/>
+        <v>1.07</v>
+      </c>
+      <c r="N32" s="1">
+        <f ca="1"/>
+        <v>-4.9999999999999933E-2</v>
+      </c>
+      <c r="O32" s="1">
+        <f ca="1"/>
+        <v>0.15000000000000011</v>
+      </c>
+      <c r="P32" s="1">
+        <f ca="1"/>
         <v>0</v>
       </c>
-      <c r="F32" s="1">
-        <f ca="1"/>
-        <v>-1.4</v>
-      </c>
-      <c r="G32" s="1">
-        <f ca="1"/>
-        <v>-0.90000000000000013</v>
-      </c>
-      <c r="H32" s="1">
-        <f ca="1"/>
-        <v>0.3</v>
-      </c>
-      <c r="I32" s="1">
-        <f ca="1"/>
-        <v>0.99999999999999989</v>
-      </c>
-      <c r="J32" s="1">
-        <f ca="1"/>
-        <v>-1.3</v>
-      </c>
-      <c r="K32" s="1">
-        <f ca="1"/>
-        <v>-1.3</v>
-      </c>
-      <c r="L32" s="1">
-        <f ca="1"/>
-        <v>0.92</v>
-      </c>
-      <c r="M32" s="1">
-        <f ca="1"/>
-        <v>1.05</v>
-      </c>
-      <c r="N32" s="1">
-        <f ca="1"/>
-        <v>-4.9999999999999933E-2</v>
-      </c>
-      <c r="O32" s="1">
-        <f ca="1"/>
-        <v>7.0000000000000062E-2</v>
-      </c>
-      <c r="P32" s="1">
-        <f ca="1"/>
-        <v>-1.06</v>
-      </c>
       <c r="Q32" s="1">
         <f ca="1"/>
-        <v>-0.95</v>
+        <v>-0.87999999999999989</v>
       </c>
       <c r="R32" s="1">
         <f ca="1"/>
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="S32" s="1">
         <f ca="1"/>
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="T32" s="1">
         <f ca="1"/>
-        <v>-1.24</v>
+        <v>-1.23</v>
       </c>
       <c r="U32" s="1">
         <f ca="1"/>
         <v>-1.03</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>5</v>
       </c>
       <c r="B33" s="1">
         <f ca="1"/>
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="C33" s="1">
         <f ca="1"/>
+        <v>0.99999999999999989</v>
+      </c>
+      <c r="D33" s="1">
+        <f ca="1"/>
+        <v>-0.8</v>
+      </c>
+      <c r="E33" s="1">
+        <f ca="1"/>
+        <v>-0.3</v>
+      </c>
+      <c r="F33" s="1">
+        <f ca="1"/>
+        <v>-0.20000000000000021</v>
+      </c>
+      <c r="G33" s="1">
+        <f ca="1"/>
+        <v>-1.5</v>
+      </c>
+      <c r="H33" s="1">
+        <f ca="1"/>
+        <v>0.3</v>
+      </c>
+      <c r="I33" s="1">
+        <f ca="1"/>
         <v>0.89999999999999991</v>
       </c>
-      <c r="D33" s="1">
-        <f ca="1"/>
-        <v>-0.8</v>
-      </c>
-      <c r="E33" s="1">
-        <f ca="1"/>
-        <v>-0.1000000000000001</v>
-      </c>
-      <c r="F33" s="1">
-        <f ca="1"/>
-        <v>-0.20000000000000021</v>
-      </c>
-      <c r="G33" s="1">
-        <f ca="1"/>
-        <v>-0.7</v>
-      </c>
-      <c r="H33" s="1">
-        <f ca="1"/>
-        <v>1.9</v>
-      </c>
-      <c r="I33" s="1">
-        <f ca="1"/>
-        <v>1.4</v>
-      </c>
       <c r="J33" s="1">
         <f ca="1"/>
-        <v>-2.1</v>
+        <v>-0.50000000000000011</v>
       </c>
       <c r="K33" s="1">
         <f ca="1"/>
-        <v>-1</v>
+        <v>-1.6</v>
       </c>
       <c r="L33" s="1">
         <f ca="1"/>
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="M33" s="1">
         <f ca="1"/>
-        <v>1.1299999999999999</v>
+        <v>1.08</v>
       </c>
       <c r="N33" s="1">
         <f ca="1"/>
-        <v>-0.11</v>
+        <v>1</v>
       </c>
       <c r="O33" s="1">
         <f ca="1"/>
-        <v>8.0000000000000071E-2</v>
+        <v>5.0000000000000037E-2</v>
       </c>
       <c r="P33" s="1">
         <f ca="1"/>
-        <v>-1.1299999999999999</v>
+        <v>-1.0900000000000001</v>
       </c>
       <c r="Q33" s="1">
         <f ca="1"/>
-        <v>-0.8899999999999999</v>
+        <v>-0.90999999999999992</v>
       </c>
       <c r="R33" s="1">
         <f ca="1"/>
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="S33" s="1">
         <f ca="1"/>
-        <v>1.25</v>
+        <v>0.1</v>
       </c>
       <c r="T33" s="1">
         <f ca="1"/>
-        <v>-1.23</v>
+        <v>-1.25</v>
       </c>
       <c r="U33" s="1">
         <f ca="1"/>
-        <v>-1.05</v>
-      </c>
-    </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.35">
+        <v>-1.01</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>6</v>
       </c>
@@ -2493,15 +2493,15 @@
       </c>
       <c r="D34" s="1">
         <f ca="1"/>
-        <v>0.2</v>
+        <v>0.59999999999999987</v>
       </c>
       <c r="E34" s="1">
         <f ca="1"/>
-        <v>0.3</v>
+        <v>-0.5</v>
       </c>
       <c r="F34" s="1">
         <f ca="1"/>
-        <v>-1.6</v>
+        <v>-2</v>
       </c>
       <c r="G34" s="1">
         <f ca="1"/>
@@ -2509,11 +2509,11 @@
       </c>
       <c r="H34" s="1">
         <f ca="1"/>
-        <v>0.70000000000000007</v>
+        <v>0.1</v>
       </c>
       <c r="I34" s="1">
         <f ca="1"/>
-        <v>0.6</v>
+        <v>0.79999999999999993</v>
       </c>
       <c r="J34" s="1">
         <f ca="1"/>
@@ -2521,15 +2521,15 @@
       </c>
       <c r="K34" s="1">
         <f ca="1"/>
-        <v>-1.4</v>
+        <v>-0.9</v>
       </c>
       <c r="L34" s="1">
         <f ca="1"/>
-        <v>0.95000000000000007</v>
+        <v>0.92</v>
       </c>
       <c r="M34" s="1">
         <f ca="1"/>
-        <v>1.1499999999999999</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="N34" s="1">
         <f ca="1"/>
@@ -2537,80 +2537,80 @@
       </c>
       <c r="O34" s="1">
         <f ca="1"/>
-        <v>9.000000000000008E-2</v>
+        <v>7.0000000000000062E-2</v>
       </c>
       <c r="P34" s="1">
         <f ca="1"/>
-        <v>-1.1200000000000001</v>
+        <v>-1.1100000000000001</v>
       </c>
       <c r="Q34" s="1">
         <f ca="1"/>
-        <v>-0.85999999999999988</v>
+        <v>-2</v>
       </c>
       <c r="R34" s="1">
         <f ca="1"/>
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="S34" s="1">
         <f ca="1"/>
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="T34" s="1">
         <f ca="1"/>
-        <v>-1.21</v>
+        <v>-1.17</v>
       </c>
       <c r="U34" s="1">
         <f ca="1"/>
-        <v>-1.01</v>
-      </c>
-    </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.35">
+        <v>-0.97999999999999987</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>7</v>
       </c>
       <c r="B35" s="1">
         <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="C35" s="1">
+        <f ca="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="D35" s="1">
+        <f ca="1"/>
+        <v>-1</v>
+      </c>
+      <c r="E35" s="1">
+        <f ca="1"/>
         <v>0.2</v>
       </c>
-      <c r="C35" s="1">
-        <f ca="1"/>
-        <v>1.2</v>
-      </c>
-      <c r="D35" s="1">
-        <f ca="1"/>
-        <v>0</v>
-      </c>
-      <c r="E35" s="1">
-        <f ca="1"/>
-        <v>0.2</v>
-      </c>
       <c r="F35" s="1">
         <f ca="1"/>
-        <v>-0.8</v>
+        <v>-1</v>
       </c>
       <c r="G35" s="1">
         <f ca="1"/>
-        <v>-1.3</v>
+        <v>-1.1000000000000001</v>
       </c>
       <c r="H35" s="1">
         <f ca="1"/>
-        <v>1.7</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="I35" s="1">
         <f ca="1"/>
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J35" s="1">
         <f ca="1"/>
-        <v>-0.30000000000000021</v>
+        <v>-1.7</v>
       </c>
       <c r="K35" s="1">
         <f ca="1"/>
-        <v>-0.69999999999999984</v>
+        <v>-1.1000000000000001</v>
       </c>
       <c r="L35" s="1">
         <f ca="1"/>
-        <v>0.94000000000000006</v>
+        <v>0.86</v>
       </c>
       <c r="M35" s="1">
         <f ca="1"/>
@@ -2618,38 +2618,38 @@
       </c>
       <c r="N35" s="1">
         <f ca="1"/>
-        <v>-6.9999999999999951E-2</v>
+        <v>-0.12</v>
       </c>
       <c r="O35" s="1">
         <f ca="1"/>
-        <v>6.0000000000000053E-2</v>
+        <v>8.0000000000000071E-2</v>
       </c>
       <c r="P35" s="1">
         <f ca="1"/>
-        <v>-1.07</v>
+        <v>-1.1299999999999999</v>
       </c>
       <c r="Q35" s="1">
         <f ca="1"/>
-        <v>-0.86999999999999988</v>
+        <v>-0.8899999999999999</v>
       </c>
       <c r="R35" s="1">
         <f ca="1"/>
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="S35" s="1">
         <f ca="1"/>
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T35" s="1">
         <f ca="1"/>
-        <v>-1.17</v>
+        <v>-1.1499999999999999</v>
       </c>
       <c r="U35" s="1">
         <f ca="1"/>
-        <v>-0.94999999999999984</v>
-      </c>
-    </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.35">
+        <v>-2.1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>8</v>
       </c>
@@ -2659,92 +2659,92 @@
       </c>
       <c r="C36" s="1">
         <f ca="1"/>
-        <v>1.4</v>
+        <v>0.79999999999999993</v>
       </c>
       <c r="D36" s="1">
         <f ca="1"/>
-        <v>-0.39999999999999991</v>
+        <v>0.99999999999999978</v>
       </c>
       <c r="E36" s="1">
         <f ca="1"/>
-        <v>0.50000000000000022</v>
+        <v>-0.20000000000000009</v>
       </c>
       <c r="F36" s="1">
         <f ca="1"/>
-        <v>-0.40000000000000008</v>
+        <v>0</v>
       </c>
       <c r="G36" s="1">
         <f ca="1"/>
-        <v>-1.1000000000000001</v>
+        <v>-0.7</v>
       </c>
       <c r="H36" s="1">
         <f ca="1"/>
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="I36" s="1">
         <f ca="1"/>
-        <v>0.89999999999999991</v>
+        <v>1.6</v>
       </c>
       <c r="J36" s="1">
         <f ca="1"/>
-        <v>-0.9</v>
+        <v>-2.1</v>
       </c>
       <c r="K36" s="1">
         <f ca="1"/>
-        <v>-1.1000000000000001</v>
+        <v>-1.2</v>
       </c>
       <c r="L36" s="1">
         <f ca="1"/>
-        <v>0.87</v>
+        <v>0.94000000000000006</v>
       </c>
       <c r="M36" s="1">
         <f ca="1"/>
-        <v>1.06</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="N36" s="1">
         <f ca="1"/>
-        <v>-8.9999999999999969E-2</v>
+        <v>-0.11</v>
       </c>
       <c r="O36" s="1">
         <f ca="1"/>
-        <v>-1</v>
+        <v>0.12000000000000011</v>
       </c>
       <c r="P36" s="1">
         <f ca="1"/>
-        <v>-1.1100000000000001</v>
+        <v>-1.1200000000000001</v>
       </c>
       <c r="Q36" s="1">
         <f ca="1"/>
-        <v>-0.90999999999999992</v>
+        <v>-0.91999999999999993</v>
       </c>
       <c r="R36" s="1">
         <f ca="1"/>
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="S36" s="1">
         <f ca="1"/>
-        <v>1.1499999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="T36" s="1">
         <f ca="1"/>
-        <v>-0.1</v>
+        <v>-1.19</v>
       </c>
       <c r="U36" s="1">
         <f ca="1"/>
-        <v>-1.04</v>
-      </c>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.35">
+        <v>-1.05</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>9</v>
       </c>
       <c r="B37" s="1">
         <f ca="1"/>
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="C37" s="1">
         <f ca="1"/>
-        <v>0.5</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="D37" s="1">
         <f ca="1"/>
@@ -2752,128 +2752,128 @@
       </c>
       <c r="E37" s="1">
         <f ca="1"/>
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="F37" s="1">
         <f ca="1"/>
-        <v>0</v>
+        <v>-1.2</v>
       </c>
       <c r="G37" s="1">
         <f ca="1"/>
+        <v>-0.49999999999999978</v>
+      </c>
+      <c r="H37" s="1">
+        <f ca="1"/>
+        <v>1.5</v>
+      </c>
+      <c r="I37" s="1">
+        <f ca="1"/>
+        <v>1.5</v>
+      </c>
+      <c r="J37" s="1">
+        <f ca="1"/>
+        <v>-0.1</v>
+      </c>
+      <c r="K37" s="1">
+        <f ca="1"/>
+        <v>-1.3</v>
+      </c>
+      <c r="L37" s="1">
+        <f ca="1"/>
+        <v>0.87</v>
+      </c>
+      <c r="M37" s="1">
+        <f ca="1"/>
+        <v>1.05</v>
+      </c>
+      <c r="N37" s="1">
+        <f ca="1"/>
+        <v>-0.14000000000000001</v>
+      </c>
+      <c r="O37" s="1">
+        <f ca="1"/>
         <v>-1</v>
       </c>
-      <c r="H37" s="1">
-        <f ca="1"/>
-        <v>0.1</v>
-      </c>
-      <c r="I37" s="1">
-        <f ca="1"/>
-        <v>1.5</v>
-      </c>
-      <c r="J37" s="1">
+      <c r="P37" s="1">
+        <f ca="1"/>
+        <v>-1.08</v>
+      </c>
+      <c r="Q37" s="1">
+        <f ca="1"/>
+        <v>-0.95</v>
+      </c>
+      <c r="R37" s="1">
+        <f ca="1"/>
+        <v>2.1</v>
+      </c>
+      <c r="S37" s="1">
+        <f ca="1"/>
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="T37" s="1">
         <f ca="1"/>
         <v>-0.1</v>
       </c>
-      <c r="K37" s="1">
-        <f ca="1"/>
-        <v>-1.6</v>
-      </c>
-      <c r="L37" s="1">
-        <f ca="1"/>
-        <v>2</v>
-      </c>
-      <c r="M37" s="1">
-        <f ca="1"/>
-        <v>1.1100000000000001</v>
-      </c>
-      <c r="N37" s="1">
-        <f ca="1"/>
-        <v>-0.14000000000000001</v>
-      </c>
-      <c r="O37" s="1">
-        <f ca="1"/>
-        <v>0.15000000000000011</v>
-      </c>
-      <c r="P37" s="1">
-        <f ca="1"/>
-        <v>-1.08</v>
-      </c>
-      <c r="Q37" s="1">
-        <f ca="1"/>
-        <v>-2</v>
-      </c>
-      <c r="R37" s="1">
-        <f ca="1"/>
-        <v>1.05</v>
-      </c>
-      <c r="S37" s="1">
-        <f ca="1"/>
-        <v>1.1599999999999999</v>
-      </c>
-      <c r="T37" s="1">
-        <f ca="1"/>
-        <v>-1.18</v>
-      </c>
       <c r="U37" s="1">
         <f ca="1"/>
-        <v>-0.98999999999999988</v>
-      </c>
-    </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.35">
+        <v>-1.04</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>10</v>
       </c>
       <c r="B38" s="1">
         <f ca="1"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="C38" s="1">
+        <f ca="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="D38" s="1">
+        <f ca="1"/>
+        <v>0.2</v>
+      </c>
+      <c r="E38" s="1">
+        <f ca="1"/>
+        <v>0.40000000000000008</v>
+      </c>
+      <c r="F38" s="1">
+        <f ca="1"/>
+        <v>-1.4</v>
+      </c>
+      <c r="G38" s="1">
+        <f ca="1"/>
+        <v>-1.2</v>
+      </c>
+      <c r="H38" s="1">
+        <f ca="1"/>
+        <v>0.9</v>
+      </c>
+      <c r="I38" s="1">
+        <f ca="1"/>
         <v>1.4</v>
       </c>
-      <c r="C38" s="1">
-        <f ca="1"/>
-        <v>0.7</v>
-      </c>
-      <c r="D38" s="1">
-        <f ca="1"/>
-        <v>0.59999999999999987</v>
-      </c>
-      <c r="E38" s="1">
-        <f ca="1"/>
-        <v>-0.5</v>
-      </c>
-      <c r="F38" s="1">
-        <f ca="1"/>
-        <v>-1.8</v>
-      </c>
-      <c r="G38" s="1">
-        <f ca="1"/>
-        <v>-1.5</v>
-      </c>
-      <c r="H38" s="1">
-        <f ca="1"/>
-        <v>2.1</v>
-      </c>
-      <c r="I38" s="1">
-        <f ca="1"/>
-        <v>0.7</v>
-      </c>
       <c r="J38" s="1">
         <f ca="1"/>
-        <v>-1.1000000000000001</v>
+        <v>-0.70000000000000007</v>
       </c>
       <c r="K38" s="1">
         <f ca="1"/>
-        <v>-1.2</v>
+        <v>-1.4</v>
       </c>
       <c r="L38" s="1">
         <f ca="1"/>
-        <v>0.93</v>
+        <v>2</v>
       </c>
       <c r="M38" s="1">
         <f ca="1"/>
-        <v>1.0900000000000001</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="N38" s="1">
         <f ca="1"/>
-        <v>-7.999999999999996E-2</v>
+        <v>-8.9999999999999969E-2</v>
       </c>
       <c r="O38" s="1">
         <f ca="1"/>
@@ -2881,15 +2881,15 @@
       </c>
       <c r="P38" s="1">
         <f ca="1"/>
-        <v>-1.0900000000000001</v>
+        <v>-1.06</v>
       </c>
       <c r="Q38" s="1">
         <f ca="1"/>
-        <v>-0.92999999999999994</v>
+        <v>-0.86999999999999988</v>
       </c>
       <c r="R38" s="1">
         <f ca="1"/>
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="S38" s="1">
         <f ca="1"/>
@@ -2897,56 +2897,56 @@
       </c>
       <c r="T38" s="1">
         <f ca="1"/>
-        <v>-1.1499999999999999</v>
+        <v>-1.1599999999999999</v>
       </c>
       <c r="U38" s="1">
         <f ca="1"/>
-        <v>-1.02</v>
-      </c>
-    </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.35">
+        <v>-0.94999999999999984</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>11</v>
       </c>
       <c r="B39" s="1">
         <f ca="1"/>
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="C39" s="1">
         <f ca="1"/>
+        <v>0.89999999999999991</v>
+      </c>
+      <c r="D39" s="1">
+        <f ca="1"/>
+        <v>-0.2</v>
+      </c>
+      <c r="E39" s="1">
+        <f ca="1"/>
+        <v>0.3</v>
+      </c>
+      <c r="F39" s="1">
+        <f ca="1"/>
+        <v>-1.6</v>
+      </c>
+      <c r="G39" s="1">
+        <f ca="1"/>
+        <v>-1.3</v>
+      </c>
+      <c r="H39" s="1">
+        <f ca="1"/>
+        <v>2.1</v>
+      </c>
+      <c r="I39" s="1">
+        <f ca="1"/>
         <v>0.6</v>
       </c>
-      <c r="D39" s="1">
-        <f ca="1"/>
-        <v>0.99999999999999978</v>
-      </c>
-      <c r="E39" s="1">
-        <f ca="1"/>
-        <v>-0.4</v>
-      </c>
-      <c r="F39" s="1">
-        <f ca="1"/>
-        <v>-1.2</v>
-      </c>
-      <c r="G39" s="1">
-        <f ca="1"/>
-        <v>-0.49999999999999978</v>
-      </c>
-      <c r="H39" s="1">
-        <f ca="1"/>
-        <v>1.3</v>
-      </c>
-      <c r="I39" s="1">
-        <f ca="1"/>
-        <v>1.3</v>
-      </c>
       <c r="J39" s="1">
         <f ca="1"/>
-        <v>-1.7</v>
+        <v>-1.9</v>
       </c>
       <c r="K39" s="1">
         <f ca="1"/>
-        <v>-0.9</v>
+        <v>-0.69999999999999984</v>
       </c>
       <c r="L39" s="1">
         <f ca="1"/>
@@ -2954,11 +2954,11 @@
       </c>
       <c r="M39" s="1">
         <f ca="1"/>
-        <v>0</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="N39" s="1">
         <f ca="1"/>
-        <v>-5.9999999999999942E-2</v>
+        <v>-6.9999999999999951E-2</v>
       </c>
       <c r="O39" s="1">
         <f ca="1"/>
@@ -2970,11 +2970,11 @@
       </c>
       <c r="Q39" s="1">
         <f ca="1"/>
-        <v>-0.91999999999999993</v>
+        <v>-0.92999999999999994</v>
       </c>
       <c r="R39" s="1">
         <f ca="1"/>
-        <v>0.99</v>
+        <v>1.04</v>
       </c>
       <c r="S39" s="1">
         <f ca="1"/>
@@ -2982,20 +2982,20 @@
       </c>
       <c r="T39" s="1">
         <f ca="1"/>
-        <v>-1.19</v>
+        <v>-1.24</v>
       </c>
       <c r="U39" s="1">
         <f ca="1"/>
-        <v>-0.97999999999999987</v>
-      </c>
-    </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.35">
+        <v>-1.02</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>10</v>
       </c>
       <c r="B41" s="1">
         <f t="shared" ref="B41:U41" ca="1" si="6">AVERAGE(B29:B39)</f>
-        <v>1.0000000000000002</v>
+        <v>1</v>
       </c>
       <c r="C41" s="1">
         <f t="shared" ca="1" si="6"/>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="D41" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>-4.0371746350005693E-17</v>
       </c>
       <c r="E41" s="1">
         <f t="shared" ca="1" si="6"/>
@@ -3015,11 +3015,11 @@
       </c>
       <c r="G41" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>-1</v>
+        <v>-0.99999999999999989</v>
       </c>
       <c r="H41" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>1.0999999999999999</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="I41" s="1">
         <f t="shared" ca="1" si="6"/>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="M41" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>0.99999999999999989</v>
+        <v>1</v>
       </c>
       <c r="N41" s="1">
         <f t="shared" ca="1" si="6"/>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="O41" s="1">
         <f t="shared" ca="1" si="6"/>
-        <v>7.5697024406260668E-17</v>
+        <v>7.8220258553136033E-17</v>
       </c>
       <c r="P41" s="1">
         <f t="shared" ca="1" si="6"/>
@@ -3074,17 +3074,17 @@
         <v>-1.0999999999999999</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B42" s="4">
         <f t="shared" ref="B42:U42" ca="1" si="7">_xlfn.STDEV.P(B29:B39)</f>
-        <v>0.63245553203367544</v>
+        <v>0.63245553203367588</v>
       </c>
       <c r="C42" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>0.31622776601683805</v>
+        <v>0.31622776601683877</v>
       </c>
       <c r="D42" s="4">
         <f t="shared" ca="1" si="7"/>
@@ -3096,19 +3096,19 @@
       </c>
       <c r="F42" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>0.6324555320336761</v>
+        <v>0.63245553203367588</v>
       </c>
       <c r="G42" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>0.31622776601683783</v>
+        <v>0.31622776601683844</v>
       </c>
       <c r="H42" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>0.63245553203367588</v>
+        <v>0.63245553203367566</v>
       </c>
       <c r="I42" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>0.31622776601683822</v>
+        <v>0.31622776601683783</v>
       </c>
       <c r="J42" s="4">
         <f t="shared" ca="1" si="7"/>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="K42" s="4">
         <f t="shared" ca="1" si="7"/>
-        <v>0.31622776601683822</v>
+        <v>0.31622776601683783</v>
       </c>
       <c r="L42" s="1">
         <f t="shared" ca="1" si="7"/>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="M42" s="1">
         <f t="shared" ca="1" si="7"/>
-        <v>0.31780497164141469</v>
+        <v>0.31780497164141414</v>
       </c>
       <c r="N42" s="1">
         <f t="shared" ca="1" si="7"/>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="P42" s="1">
         <f t="shared" ca="1" si="7"/>
-        <v>0.31780497164141358</v>
+        <v>0.31780497164141319</v>
       </c>
       <c r="Q42" s="1">
         <f t="shared" ca="1" si="7"/>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="R42" s="1">
         <f t="shared" ca="1" si="7"/>
-        <v>0.31780497164141336</v>
+        <v>0.31780497164141375</v>
       </c>
       <c r="S42" s="1">
         <f t="shared" ca="1" si="7"/>
@@ -3152,64 +3152,64 @@
       </c>
       <c r="T42" s="1">
         <f t="shared" ca="1" si="7"/>
-        <v>0.31780497164141414</v>
+        <v>0.31780497164141375</v>
       </c>
       <c r="U42" s="1">
         <f t="shared" ca="1" si="7"/>
-        <v>0.31780497164141414</v>
-      </c>
-    </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.35">
+        <v>0.31780497164141486</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>12</v>
       </c>
       <c r="B43" s="1">
         <f t="shared" ref="B43:U43" ca="1" si="8">_xlfn.SKEW.P(B29:B39)</f>
-        <v>-1.0389416599759277E-15</v>
+        <v>4.0371746350005693E-17</v>
       </c>
       <c r="C43" s="1">
         <f t="shared" ca="1" si="8"/>
-        <v>7.2669143430010251E-16</v>
+        <v>8.1878948066105295E-16</v>
       </c>
       <c r="D43" s="1">
         <f t="shared" ca="1" si="8"/>
-        <v>-5.2483270255007403E-16</v>
+        <v>-4.0056342081646272E-16</v>
       </c>
       <c r="E43" s="1">
         <f t="shared" ca="1" si="8"/>
-        <v>4.8446095620006827E-16</v>
+        <v>4.6427508302506544E-16</v>
       </c>
       <c r="F43" s="1">
         <f t="shared" ca="1" si="8"/>
-        <v>-2.7124767078910076E-16</v>
+        <v>-2.8260222445003984E-16</v>
       </c>
       <c r="G43" s="1">
         <f t="shared" ca="1" si="8"/>
-        <v>7.6706318065010816E-16</v>
+        <v>-2.6241635127503701E-16</v>
       </c>
       <c r="H43" s="1">
         <f t="shared" ca="1" si="8"/>
-        <v>6.4531713306337224E-16</v>
+        <v>-3.6334571715005125E-16</v>
       </c>
       <c r="I43" s="1">
         <f t="shared" ca="1" si="8"/>
-        <v>1.1304088978001594E-15</v>
+        <v>1.2515241368501765E-15</v>
       </c>
       <c r="J43" s="1">
         <f t="shared" ca="1" si="8"/>
-        <v>-7.5697024406260675E-16</v>
+        <v>-8.0743492700011382E-16</v>
       </c>
       <c r="K43" s="1">
         <f t="shared" ca="1" si="8"/>
-        <v>-6.7118028306884468E-16</v>
+        <v>-5.2483270255007403E-16</v>
       </c>
       <c r="L43" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>2.7945403348921536</v>
+        <v>2.7945403348921523</v>
       </c>
       <c r="M43" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>-2.7945403348921505</v>
+        <v>-2.7945403348921536</v>
       </c>
       <c r="N43" s="4">
         <f t="shared" ca="1" si="8"/>
@@ -3229,22 +3229,22 @@
       </c>
       <c r="R43" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>2.7945403348921518</v>
+        <v>2.7945403348921514</v>
       </c>
       <c r="S43" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>-2.7945403348921518</v>
+        <v>-2.7945403348921505</v>
       </c>
       <c r="T43" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>2.7945403348921518</v>
+        <v>2.79454033489215</v>
       </c>
       <c r="U43" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>-2.794540334892154</v>
-      </c>
-    </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.35">
+        <v>-2.7945403348921518</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>13</v>
       </c>
@@ -3254,15 +3254,15 @@
       </c>
       <c r="C44" s="1">
         <f t="shared" ca="1" si="9"/>
-        <v>-1.2000000000000015</v>
+        <v>-1.2000000000000002</v>
       </c>
       <c r="D44" s="1">
         <f t="shared" ca="1" si="9"/>
-        <v>-1.1999999999999997</v>
+        <v>-1.2000000000000002</v>
       </c>
       <c r="E44" s="1">
         <f t="shared" ca="1" si="9"/>
-        <v>-1.1999999999999997</v>
+        <v>-1.200000000000002</v>
       </c>
       <c r="F44" s="1">
         <f t="shared" ca="1" si="9"/>
@@ -3274,11 +3274,11 @@
       </c>
       <c r="H44" s="1">
         <f t="shared" ca="1" si="9"/>
-        <v>-1.2000000000000002</v>
+        <v>-1.1999999999999997</v>
       </c>
       <c r="I44" s="1">
         <f t="shared" ca="1" si="9"/>
-        <v>-1.2000000000000002</v>
+        <v>-1.2000000000000011</v>
       </c>
       <c r="J44" s="1">
         <f t="shared" ca="1" si="9"/>
@@ -3290,11 +3290,11 @@
       </c>
       <c r="L44" s="1">
         <f t="shared" ca="1" si="9"/>
-        <v>10.711250530993702</v>
+        <v>10.711250530993684</v>
       </c>
       <c r="M44" s="1">
         <f t="shared" ca="1" si="9"/>
-        <v>10.711250530993684</v>
+        <v>10.711250530993706</v>
       </c>
       <c r="N44" s="1">
         <f t="shared" ca="1" si="9"/>
@@ -3302,7 +3302,7 @@
       </c>
       <c r="O44" s="1">
         <f t="shared" ca="1" si="9"/>
-        <v>10.711250530993688</v>
+        <v>10.711250530993684</v>
       </c>
       <c r="P44" s="1">
         <f t="shared" ca="1" si="9"/>
@@ -3310,26 +3310,26 @@
       </c>
       <c r="Q44" s="1">
         <f t="shared" ca="1" si="9"/>
-        <v>10.711250530993702</v>
+        <v>10.711250530993706</v>
       </c>
       <c r="R44" s="1">
         <f t="shared" ca="1" si="9"/>
-        <v>10.711250530993688</v>
+        <v>10.711250530993684</v>
       </c>
       <c r="S44" s="1">
         <f t="shared" ca="1" si="9"/>
-        <v>10.711250530993695</v>
+        <v>10.711250530993688</v>
       </c>
       <c r="T44" s="1">
         <f t="shared" ca="1" si="9"/>
-        <v>10.711250530993691</v>
+        <v>10.711250530993684</v>
       </c>
       <c r="U44" s="1">
         <f t="shared" ca="1" si="9"/>
-        <v>10.711250530993706</v>
-      </c>
-    </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.35">
+        <v>10.711250530993691</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>14</v>
       </c>
@@ -3414,7 +3414,7 @@
         <v>-2.1</v>
       </c>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>15</v>
       </c>
@@ -3499,62 +3499,62 @@
         <v>-0.94999999999999984</v>
       </c>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>16</v>
       </c>
       <c r="B47" s="1">
         <f ca="1">CORREL(B29:B39,C29:C39)</f>
-        <v>-0.21818181818181812</v>
+        <v>-0.10000000000000006</v>
       </c>
       <c r="D47" s="1">
         <f ca="1">CORREL(D29:D39,E29:E39)</f>
-        <v>-0.30909090909090897</v>
+        <v>-0.35454545454545439</v>
       </c>
       <c r="F47" s="1">
         <f ca="1">CORREL(F29:F39,G29:G39)</f>
-        <v>6.3636363636363588E-2</v>
+        <v>0.31818181818181807</v>
       </c>
       <c r="H47" s="1">
         <f ca="1">CORREL(H29:H39,I29:I39)</f>
-        <v>6.3636363636363519E-2</v>
+        <v>0.11818181818181828</v>
       </c>
       <c r="J47" s="1">
         <f ca="1">CORREL(J29:J39,K29:K39)</f>
-        <v>-0.28181818181818186</v>
+        <v>-0.3545454545454545</v>
       </c>
       <c r="L47" s="1">
         <f ca="1">CORREL(L29:L39,M29:M39)</f>
-        <v>0.10126012601260134</v>
+        <v>6.4356435643564386E-2</v>
       </c>
       <c r="N47" s="1">
         <f ca="1">CORREL(N29:N39,O29:O39)</f>
-        <v>0.10513051305130515</v>
+        <v>9.0009000900090022E-2</v>
       </c>
       <c r="P47" s="1">
         <f ca="1">CORREL(P29:P39,Q29:Q39)</f>
-        <v>0.1245724572457247</v>
+        <v>0.12934293429342944</v>
       </c>
       <c r="R47" s="1">
         <f ca="1">CORREL(R29:R39,S29:S39)</f>
-        <v>0.12763276327632767</v>
+        <v>3.8703870387038646E-2</v>
       </c>
       <c r="T47" s="1">
         <f ca="1">CORREL(T29:T39,U29:U39)</f>
-        <v>2.1062106210620948E-2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.35">
+        <v>1.3861386138613749E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>17</v>
       </c>
       <c r="B48">
         <f t="array" aca="1" ref="B48" ca="1">SUMPRODUCT((B29:B39&gt;C29:C39)*1)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C48">
         <f t="array" aca="1" ref="C48" ca="1">SUMPRODUCT((B29:B39&lt;C29:C39)*1)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D48">
         <f t="array" aca="1" ref="D48" ca="1">SUMPRODUCT((D29:D39&gt;E29:E39)*1)</f>
@@ -3574,19 +3574,19 @@
       </c>
       <c r="H48">
         <f t="array" aca="1" ref="H48" ca="1">SUMPRODUCT((H29:H39&gt;I29:I39)*1)</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I48">
         <f t="array" aca="1" ref="I48" ca="1">SUMPRODUCT((H29:H39&lt;I29:I39)*1)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J48">
         <f t="array" aca="1" ref="J48" ca="1">SUMPRODUCT((J29:J39&gt;K29:K39)*1)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K48">
         <f t="array" aca="1" ref="K48" ca="1">SUMPRODUCT((J29:J39&lt;K29:K39)*1)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L48">
         <f t="array" aca="1" ref="L48" ca="1">SUMPRODUCT((L29:L39&gt;M29:M39)*1)</f>
@@ -3629,7 +3629,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
         <v>18</v>
       </c>
@@ -3647,11 +3647,11 @@
       </c>
       <c r="H49" s="6" t="str">
         <f ca="1">IF(H48&gt;I48,"A",IF(I48&gt;H48,"B","Equal"))</f>
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="J49" s="6" t="str">
         <f ca="1">IF(J48&gt;K48,"A",IF(K48&gt;J48,"B","Equal"))</f>
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="L49" s="6" t="str">
         <f ca="1">IF(L48&gt;M48,"A",IF(M48&gt;L48,"B","Equal"))</f>
@@ -3674,13 +3674,13 @@
         <v>B</v>
       </c>
     </row>
-    <row r="50" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>19</v>
       </c>
       <c r="B50">
         <f ca="1">MAX(B48:C48)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D50">
         <f ca="1">MAX(D48:E48)</f>
@@ -3719,12 +3719,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A52" s="7" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="54" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A54" s="2"/>
       <c r="B54" s="11" t="s">
         <v>0</v>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="U54" s="12"/>
     </row>
-    <row r="55" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B55" s="1">
         <v>0</v>
       </c>
@@ -3835,7 +3835,7 @@
       <c r="Z55" s="1"/>
       <c r="AB55" s="1"/>
     </row>
-    <row r="56" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B56" s="1">
         <v>0.2</v>
       </c>
@@ -3903,7 +3903,7 @@
       <c r="Z56" s="1"/>
       <c r="AB56" s="1"/>
     </row>
-    <row r="57" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B57" s="1">
         <v>0.4</v>
       </c>
@@ -3971,7 +3971,7 @@
       <c r="Z57" s="1"/>
       <c r="AB57" s="1"/>
     </row>
-    <row r="58" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B58" s="1">
         <v>0.60000000000000009</v>
       </c>
@@ -4039,7 +4039,7 @@
       <c r="Z58" s="1"/>
       <c r="AB58" s="1"/>
     </row>
-    <row r="59" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B59" s="1">
         <v>0.8</v>
       </c>
@@ -4107,7 +4107,7 @@
       <c r="Z59" s="1"/>
       <c r="AB59" s="1"/>
     </row>
-    <row r="60" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B60" s="1">
         <v>1</v>
       </c>
@@ -4175,7 +4175,7 @@
       <c r="Z60" s="1"/>
       <c r="AB60" s="1"/>
     </row>
-    <row r="61" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B61" s="1">
         <v>1.2</v>
       </c>
@@ -4243,7 +4243,7 @@
       <c r="Z61" s="1"/>
       <c r="AB61" s="1"/>
     </row>
-    <row r="62" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B62" s="1">
         <v>1.4</v>
       </c>
@@ -4311,7 +4311,7 @@
       <c r="Z62" s="1"/>
       <c r="AB62" s="1"/>
     </row>
-    <row r="63" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B63" s="1">
         <v>1.6</v>
       </c>
@@ -4379,7 +4379,7 @@
       <c r="Z63" s="1"/>
       <c r="AB63" s="1"/>
     </row>
-    <row r="64" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B64" s="1">
         <v>1.8</v>
       </c>
@@ -4447,7 +4447,7 @@
       <c r="Z64" s="1"/>
       <c r="AB64" s="1"/>
     </row>
-    <row r="65" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B65" s="1">
         <v>2</v>
       </c>
@@ -4515,7 +4515,7 @@
       <c r="Z65" s="1"/>
       <c r="AB65" s="1"/>
     </row>
-    <row r="67" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>10</v>
       </c>
@@ -4604,7 +4604,7 @@
       <c r="Y67" s="1"/>
       <c r="Z67" s="1"/>
     </row>
-    <row r="68" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
         <v>11</v>
       </c>
@@ -4693,7 +4693,7 @@
       <c r="Y68" s="1"/>
       <c r="Z68" s="1"/>
     </row>
-    <row r="69" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>12</v>
       </c>
@@ -4782,7 +4782,7 @@
       <c r="Y69" s="1"/>
       <c r="Z69" s="1"/>
     </row>
-    <row r="70" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>13</v>
       </c>
@@ -4871,7 +4871,7 @@
       <c r="Y70" s="1"/>
       <c r="Z70" s="1"/>
     </row>
-    <row r="71" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>14</v>
       </c>
@@ -4960,7 +4960,7 @@
       <c r="Y71" s="1"/>
       <c r="Z71" s="1"/>
     </row>
-    <row r="72" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>15</v>
       </c>
@@ -5049,7 +5049,7 @@
       <c r="Y72" s="1"/>
       <c r="Z72" s="1"/>
     </row>
-    <row r="73" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>16</v>
       </c>
@@ -5096,7 +5096,7 @@
       <c r="W73" s="1"/>
       <c r="Y73" s="1"/>
     </row>
-    <row r="74" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A74" s="3" t="s">
         <v>17</v>
       </c>
@@ -5181,7 +5181,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="75" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A75" s="5" t="s">
         <v>18</v>
       </c>
@@ -5228,7 +5228,7 @@
       <c r="W75" s="6"/>
       <c r="Y75" s="6"/>
     </row>
-    <row r="76" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>19</v>
       </c>
@@ -5273,12 +5273,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="78" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A78" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="80" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A80" s="2"/>
       <c r="B80" s="11" t="s">
         <v>0</v>
@@ -5321,7 +5321,7 @@
       </c>
       <c r="U80" s="12"/>
     </row>
-    <row r="81" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B81" s="1">
         <v>0.60000000000000009</v>
       </c>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="V81" s="1"/>
     </row>
-    <row r="82" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B82" s="1">
         <v>0.8</v>
       </c>
@@ -5447,7 +5447,7 @@
       </c>
       <c r="V82" s="1"/>
     </row>
-    <row r="83" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B83" s="1">
         <v>1</v>
       </c>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="V83" s="1"/>
     </row>
-    <row r="84" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B84" s="1">
         <v>1.2</v>
       </c>
@@ -5573,7 +5573,7 @@
       </c>
       <c r="V84" s="1"/>
     </row>
-    <row r="85" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B85" s="1">
         <v>1.4</v>
       </c>
@@ -5636,7 +5636,7 @@
       </c>
       <c r="V85" s="1"/>
     </row>
-    <row r="86" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B86" s="1">
         <v>1.6</v>
       </c>
@@ -5699,7 +5699,7 @@
       </c>
       <c r="V86" s="1"/>
     </row>
-    <row r="87" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B87" s="1">
         <v>1.8</v>
       </c>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="V87" s="1"/>
     </row>
-    <row r="88" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B88" s="1">
         <v>2</v>
       </c>
@@ -5825,7 +5825,7 @@
       </c>
       <c r="V88" s="1"/>
     </row>
-    <row r="89" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B89" s="1">
         <v>0</v>
       </c>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="V89" s="1"/>
     </row>
-    <row r="90" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B90" s="1">
         <v>0.2</v>
       </c>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="V90" s="1"/>
     </row>
-    <row r="91" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B91" s="1">
         <v>0.4</v>
       </c>
@@ -6014,7 +6014,7 @@
       </c>
       <c r="V91" s="1"/>
     </row>
-    <row r="93" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>10</v>
       </c>
@@ -6099,7 +6099,7 @@
         <v>-1.0999999999999999</v>
       </c>
     </row>
-    <row r="94" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A94" s="3" t="s">
         <v>11</v>
       </c>
@@ -6184,7 +6184,7 @@
         <v>0.31780497164141375</v>
       </c>
     </row>
-    <row r="95" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>12</v>
       </c>
@@ -6269,7 +6269,7 @@
         <v>-2.794540334892154</v>
       </c>
     </row>
-    <row r="96" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>13</v>
       </c>
@@ -6354,7 +6354,7 @@
         <v>10.711250530993706</v>
       </c>
     </row>
-    <row r="97" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>14</v>
       </c>
@@ -6439,7 +6439,7 @@
         <v>-2.1</v>
       </c>
     </row>
-    <row r="98" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>15</v>
       </c>
@@ -6524,7 +6524,7 @@
         <v>-0.94999999999999984</v>
       </c>
     </row>
-    <row r="99" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>16</v>
       </c>
@@ -6569,7 +6569,7 @@
         <v>0.20513051305130531</v>
       </c>
     </row>
-    <row r="100" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
         <v>17</v>
       </c>
@@ -6654,7 +6654,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A101" s="5" t="s">
         <v>18</v>
       </c>
@@ -6699,7 +6699,7 @@
         <v>B</v>
       </c>
     </row>
-    <row r="102" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>19</v>
       </c>
@@ -6744,15 +6744,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="104" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A104" s="8" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="105" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A105" s="8"/>
     </row>
-    <row r="106" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B106" s="8" t="s">
         <v>0</v>
       </c>
@@ -6784,7 +6784,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A107" s="9" t="s">
         <v>24</v>
       </c>
@@ -6819,77 +6819,77 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="108" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A108" s="9" t="s">
         <v>25</v>
       </c>
       <c r="B108" s="10">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="D108" s="10">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="F108" s="10">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="H108" s="10">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J108" s="10">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="L108" s="10">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="N108" s="10">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="P108" s="10">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="R108" s="10">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="T108" s="10">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="109" spans="1:21" x14ac:dyDescent="0.35">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="109" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A109" s="9" t="s">
         <v>26</v>
       </c>
       <c r="B109" s="10">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="D109" s="10">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="F109" s="10">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="H109" s="10">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J109" s="10">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="L109" s="10">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="N109" s="10">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="P109" s="10">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="R109" s="10">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="T109" s="10">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="110" spans="1:21" x14ac:dyDescent="0.35">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A110" s="9" t="s">
         <v>27</v>
       </c>
@@ -6926,18 +6926,21 @@
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="T28:U28"/>
-    <mergeCell ref="N80:O80"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="P54:Q54"/>
-    <mergeCell ref="T54:U54"/>
-    <mergeCell ref="F80:G80"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="J80:K80"/>
-    <mergeCell ref="P80:Q80"/>
-    <mergeCell ref="R80:S80"/>
-    <mergeCell ref="T80:U80"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="L80:M80"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="H54:I54"/>
+    <mergeCell ref="N54:O54"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="P28:Q28"/>
+    <mergeCell ref="H28:I28"/>
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="T2:U2"/>
@@ -6948,24 +6951,21 @@
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="R28:S28"/>
     <mergeCell ref="J28:K28"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="J80:K80"/>
+    <mergeCell ref="P80:Q80"/>
+    <mergeCell ref="R80:S80"/>
+    <mergeCell ref="T28:U28"/>
+    <mergeCell ref="N80:O80"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="P54:Q54"/>
+    <mergeCell ref="T54:U54"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="T80:U80"/>
     <mergeCell ref="D80:E80"/>
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="P28:Q28"/>
-    <mergeCell ref="H28:I28"/>
     <mergeCell ref="H80:I80"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="R2:S2"/>
-    <mergeCell ref="L80:M80"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="F54:G54"/>
-    <mergeCell ref="H54:I54"/>
-    <mergeCell ref="N54:O54"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6974,9 +6974,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A2:K21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B2" s="11" t="s">
         <v>0</v>
       </c>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="K2" s="12"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B3" s="1">
         <v>0</v>
       </c>
@@ -7038,7 +7038,7 @@
         <v>-1.6</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B4" s="1">
         <v>0.2</v>
       </c>
@@ -7078,7 +7078,7 @@
         <v>-1.5</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B5" s="1">
         <v>0.4</v>
       </c>
@@ -7118,7 +7118,7 @@
         <v>-1.4000000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B6" s="1">
         <v>0.60000000000000009</v>
       </c>
@@ -7158,7 +7158,7 @@
         <v>-1.3000000000000003</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B7" s="1">
         <v>0.8</v>
       </c>
@@ -7198,7 +7198,7 @@
         <v>-1.2000000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B8" s="1">
         <v>1</v>
       </c>
@@ -7238,7 +7238,7 @@
         <v>-1.1000000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B9" s="1">
         <v>1.2</v>
       </c>
@@ -7278,7 +7278,7 @@
         <v>-0.99999999999999989</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B10" s="1">
         <v>1.4</v>
       </c>
@@ -7318,7 +7318,7 @@
         <v>-0.9</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B11" s="1">
         <v>1.6</v>
       </c>
@@ -7358,7 +7358,7 @@
         <v>-0.79999999999999993</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B12" s="1">
         <v>1.8</v>
       </c>
@@ -7398,7 +7398,7 @@
         <v>-0.70000000000000007</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B13" s="1">
         <v>2</v>
       </c>
@@ -7438,7 +7438,7 @@
         <v>-0.6</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -7483,7 +7483,7 @@
         <v>-1.1000000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>11</v>
       </c>
@@ -7528,7 +7528,7 @@
         <v>0.31622776601683822</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>12</v>
       </c>
@@ -7573,7 +7573,7 @@
         <v>5.2483270255007403E-16</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -7618,7 +7618,7 @@
         <v>-1.2000000000000011</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>14</v>
       </c>
@@ -7663,7 +7663,7 @@
         <v>-1.6</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>15</v>
       </c>
@@ -7708,7 +7708,7 @@
         <v>-0.6</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>16</v>
       </c>
@@ -7748,9 +7748,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A2:K21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B2" s="11" t="s">
         <v>5</v>
       </c>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="K2" s="12"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B3" s="1">
         <v>0.85</v>
       </c>
@@ -7812,7 +7812,7 @@
         <v>-1.05</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B4" s="1">
         <v>0.86</v>
       </c>
@@ -7852,7 +7852,7 @@
         <v>-1.04</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B5" s="1">
         <v>0.87</v>
       </c>
@@ -7892,7 +7892,7 @@
         <v>-1.03</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B6" s="1">
         <v>0.88</v>
       </c>
@@ -7932,7 +7932,7 @@
         <v>-1.02</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B7" s="1">
         <v>0.89</v>
       </c>
@@ -7972,7 +7972,7 @@
         <v>-1.01</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B8" s="1">
         <v>0.91</v>
       </c>
@@ -8012,7 +8012,7 @@
         <v>-0.98999999999999988</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B9" s="1">
         <v>0.92</v>
       </c>
@@ -8052,7 +8052,7 @@
         <v>-0.97999999999999987</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B10" s="1">
         <v>0.93</v>
       </c>
@@ -8092,7 +8092,7 @@
         <v>-0.97000000000000008</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B11" s="1">
         <v>0.94000000000000006</v>
       </c>
@@ -8132,7 +8132,7 @@
         <v>-0.96000000000000008</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B12" s="1">
         <v>0.95000000000000007</v>
       </c>
@@ -8172,7 +8172,7 @@
         <v>-0.95000000000000007</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B13" s="1">
         <v>2</v>
       </c>
@@ -8212,7 +8212,7 @@
         <v>-2.1</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -8257,7 +8257,7 @@
         <v>-1.0999999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>11</v>
       </c>
@@ -8302,7 +8302,7 @@
         <v>0.31780497164141414</v>
       </c>
     </row>
-    <row r="17" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>12</v>
       </c>
@@ -8347,7 +8347,7 @@
         <v>-2.7945403348921536</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -8392,7 +8392,7 @@
         <v>10.711250530993702</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>14</v>
       </c>
@@ -8437,7 +8437,7 @@
         <v>-2.1</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>15</v>
       </c>
@@ -8482,7 +8482,7 @@
         <v>-0.95000000000000007</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>16</v>
       </c>
